--- a/InputData/bldgs/CiDESCTY/Change in Distribued Electricity Source Capacities This Year.xlsx
+++ b/InputData/bldgs/CiDESCTY/Change in Distribued Electricity Source Capacities This Year.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\bldgs\CiDESCTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B380D71F-535A-4C10-A987-C1C11F047F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A542FA98-D38D-4BE8-BD86-992741501B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="905" activeTab="5" xr2:uid="{EAFC2935-000E-413A-B5D2-814429F7674A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="905" activeTab="3" xr2:uid="{EAFC2935-000E-413A-B5D2-814429F7674A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Table 21" sheetId="19" r:id="rId2"/>
-    <sheet name="Calculations" sheetId="21" r:id="rId3"/>
-    <sheet name="CiDESCTY-urban-residential" sheetId="6" r:id="rId4"/>
-    <sheet name="CiDESCTY-rural-residential" sheetId="10" r:id="rId5"/>
-    <sheet name="CiDESCTY-commercial" sheetId="7" r:id="rId6"/>
+    <sheet name="Table_21._Residential_Sector_Eq" sheetId="22" r:id="rId3"/>
+    <sheet name="Calculations" sheetId="21" r:id="rId4"/>
+    <sheet name="CiDESCTY-urban-residential" sheetId="6" r:id="rId5"/>
+    <sheet name="CiDESCTY-rural-residential" sheetId="10" r:id="rId6"/>
+    <sheet name="CiDESCTY-commercial" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="billion_kw_to_MW">About!$B$35</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="613">
   <si>
     <t>Energy Information Administration</t>
   </si>
@@ -1466,6 +1467,420 @@
   </si>
   <si>
     <t>IRA credits end in 2026</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.CNSM_NA_COMM_CHP_TOT_NA_NA_TRLBTU.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Energy Input: Total: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.CNSM_NA_COMM_CHP_WND_NA_NA_TRLBTU.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Energy Input: Wind: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.CNSM_NA_COMM_CHP_SLR_PHTVL_NA_TRLBTU.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Energy Input: Solar Photovoltaic: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.CNSM_NA_COMM_CHP_FCL_NA_NA_TRLBTU.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Energy Input: Fuel Cells: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.GEN_NA_COMM_CHP_GFO_NA_NA_MILLKWH.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Net Generation: Generation for Own Use: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.GEN_NA_COMM_CHP_STG_NA_NA_MILLKWH.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Net Generation: Sales to the Grid: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.GEN_NA_COMM_CHP_TOT_NA_NA_MILLKWH.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Net Generation: Total: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.GEN_NA_COMM_CHP_WND_NA_NA_MILLKWH.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Net Generation: Wind: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.GEN_NA_COMM_CHP_SLR_PHTVL_NA_MILLKWH.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Net Generation: Solar Photovoltaic: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.GEN_NA_COMM_CHP_FCL_NA_NA_MILLKWH.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Net Generation: Fuel Cells: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.CAP_NA_RESD_CHP_TOT_NA_NA_MW.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Generating Capacity: Total: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.CAP_NA_RESD_CHP_WND_NA_NA_MW.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Generating Capacity: Wind: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.CAP_NA_RESD_CHP_SLR_PHTVL_NA_MW.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Generating Capacity: Solar Photovoltaic: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.CAP_NA_COMM_CHP_FCL_NA_NA_MW.A</t>
+  </si>
+  <si>
+    <t>Residential: Combined Heat and Power: Generating Capacity: Fuel Cells: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_BSE_RESD_SPC_AHM_NA_NA_Y15EQ1.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Building Shell Efficiency Index: Space Cooling: All Homes: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_BSE_RESD_SPC_NCO_NA_NA_Y15EQ1.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Building Shell Efficiency Index: Space Cooling: New Construction: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_BSE_RESD_SPC_OLD_NA_NA_Y15EQ1.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Building Shell Efficiency Index: Space Cooling: Pre-2015 Homes: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>Pre-2020 Homes</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_BSE_RESD_SPH_AHM_NA_NA_Y15EQ1.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Building Shell Efficiency Index: Space Heating: All Homes: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_BSE_RESD_SPH_NCO_NA_NA_Y15EQ1.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Building Shell Efficiency Index: Space Heating: New Construction: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_BSE_RESD_SPH_OLD_NA_NA_Y15EQ1.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Building Shell Efficiency Index: Space Heating: Pre-2015 Homes: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_OTAR_FRZ_NA_NA_KWH.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Other Appliances: Freezers: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_OTAR_RFG_NA_NA_KWH.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Other Appliances: Refrigerators: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_WHT_PROP_NA_NA_EF.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Water Heaters: Propane: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_WHT_DFO_NA_NA_EF.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Water Heaters: Distillate Fuel Oil: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_WHT_NG_NA_NA_EF.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Water Heaters: Natural Gas: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_WHT_ELE_NA_NA_EF.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Water Heaters: Electric: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPC_RAC_NA_NA_EER.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Space Cooling: Room Air Conditioners: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPC_CAC_NA_NA_SEER.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Space Cooling: Central Air Conditioners: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPC_GEHP_NA_NA_EER.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Space Cooling: Geothermal Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPC_NHU_NA_NA_GCOP.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Space Cooling: Natural Gas Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPC_EHP_NA_NA_SEER.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Space Cooling: Electric Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPHR_DFR_NA_NA_AFUE.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Main Space Heaters: Distillate Furnace: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPHR_NFR_NA_NA_AFUE.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Main Space Heaters: Natural Gas Furnace: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPHR_GEHP_NA_NA_COP.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Main Space Heaters: Geothermal Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPHR_NHU_NA_NA_GCOP.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Main Space Heaters: Natural Gas Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EFI_STK_RESD_SPHR_EHP_NA_NA_HSPF.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Stock Average Efficiency: Main Space Heaters: Electric Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_OTAR_FRZ_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Other Appliances: Freezers: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_OTAR_RFG_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Other Appliances: Refrigerators: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_CDR_TOT_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Clothes Dryers: Total: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_CDR_NG_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Clothes Dryers: Natural Gas: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_CDR_ELE_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Clothes Dryers: Electric: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_CER_TOT_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Cooking Equipment: Total: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_CER_PROP_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Cooking Equipment: Propane: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_CER_NG_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Cooking Equipment: Natural Gas: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_CER_ELE_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Cooking Equipment: Electric: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_WHT_TOT_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Water Heaters: Total: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_WHT_SLR_THERM_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Water Heaters: Solar Thermal: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_WHT_PROP_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Water Heaters: Propane: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_WHT_DFO_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Water Heaters: Distillate Fuel Oil: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_WHT_NG_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Water Heaters: Natural Gas: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_WHT_ELE_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Water Heaters: Electric: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_SPC_TOT_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Space Cooling: Total: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_SPC_RAC_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Space Cooling: Room Air Conditioners: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_SPC_CAC_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Space Cooling: Central Air Conditioners: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_SPC_GEHP_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Space Cooling: Geothermal Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_SPC_NHU_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Space Cooling: Natural Gas Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_SPC_EHP_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Space Cooling: Electric Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_TOT_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Total: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_GEHP_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Geothermal Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_WDS_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Wood Stoves: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_KRS_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Kerosene: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_PROP_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Propane: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_DFO_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Distillate Fuel Oil: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_NGO_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Natural Gas Other: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_NHU_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Natural Gas Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_ELO_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Electric Other: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>AEO.2025.HIGHZTC.EQNR_STK_RESD_MSHR_EHP_NA_NA_MILL.A</t>
+  </si>
+  <si>
+    <t>Residential Equipment: Equipment Stock: Main Space Heaters: Electric Heat Pumps: High Zero-Carbon Technology Cost</t>
+  </si>
+  <si>
+    <t>Growth (2024-2050)</t>
+  </si>
+  <si>
+    <t>Tue Dec 02 2025 13:21:44 GMT-0800 (Pacific Standard Time)</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/outlooks/aeo/data/browser/#/?id=30-AEO2025&amp;cases=highZTC&amp;sourcekey=0</t>
   </si>
 </sst>
 </file>
@@ -1670,7 +2085,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1854,6 +2269,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2090,7 +2517,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2113,6 +2540,9 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="54">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -2670,6 +3100,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B74F30-E57B-4412-9A61-7D098BFC4C5D}">
   <dimension ref="A1:AI227"/>
   <sheetFormatPr defaultColWidth="27.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="112.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -14722,107 +15155,107 @@
         <v>95</v>
       </c>
     </row>
-    <row r="187" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+    <row r="187" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D187" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F187">
+      <c r="F187" s="14">
         <v>25.940821</v>
       </c>
-      <c r="G187">
+      <c r="G187" s="14">
         <v>28.426915999999999</v>
       </c>
-      <c r="H187">
+      <c r="H187" s="14">
         <v>31.317519999999998</v>
       </c>
-      <c r="I187">
+      <c r="I187" s="14">
         <v>34.213085</v>
       </c>
-      <c r="J187">
+      <c r="J187" s="14">
         <v>37.102398000000001</v>
       </c>
-      <c r="K187">
+      <c r="K187" s="14">
         <v>40.088000999999998</v>
       </c>
-      <c r="L187">
+      <c r="L187" s="14">
         <v>43.162284999999997</v>
       </c>
-      <c r="M187">
+      <c r="M187" s="14">
         <v>46.379024999999999</v>
       </c>
-      <c r="N187">
+      <c r="N187" s="14">
         <v>49.715114999999997</v>
       </c>
-      <c r="O187">
+      <c r="O187" s="14">
         <v>53.221054000000002</v>
       </c>
-      <c r="P187">
+      <c r="P187" s="14">
         <v>56.974155000000003</v>
       </c>
-      <c r="Q187">
+      <c r="Q187" s="14">
         <v>60.782733999999998</v>
       </c>
-      <c r="R187">
+      <c r="R187" s="14">
         <v>64.698020999999997</v>
       </c>
-      <c r="S187">
+      <c r="S187" s="14">
         <v>68.113708000000003</v>
       </c>
-      <c r="T187">
+      <c r="T187" s="14">
         <v>71.713645999999997</v>
       </c>
-      <c r="U187">
+      <c r="U187" s="14">
         <v>75.468543999999994</v>
       </c>
-      <c r="V187">
+      <c r="V187" s="14">
         <v>79.508544999999998</v>
       </c>
-      <c r="W187">
+      <c r="W187" s="14">
         <v>83.846107000000003</v>
       </c>
-      <c r="X187">
+      <c r="X187" s="14">
         <v>88.482719000000003</v>
       </c>
-      <c r="Y187">
+      <c r="Y187" s="14">
         <v>93.406563000000006</v>
       </c>
-      <c r="Z187">
+      <c r="Z187" s="14">
         <v>98.617553999999998</v>
       </c>
-      <c r="AA187">
+      <c r="AA187" s="14">
         <v>104.15289300000001</v>
       </c>
-      <c r="AB187">
+      <c r="AB187" s="14">
         <v>109.907883</v>
       </c>
-      <c r="AC187">
+      <c r="AC187" s="14">
         <v>115.976173</v>
       </c>
-      <c r="AD187">
+      <c r="AD187" s="14">
         <v>122.272903</v>
       </c>
-      <c r="AE187">
+      <c r="AE187" s="14">
         <v>128.79647800000001</v>
       </c>
-      <c r="AF187">
+      <c r="AF187" s="14">
         <v>135.66493199999999</v>
       </c>
-      <c r="AG187">
+      <c r="AG187" s="14">
         <v>142.69435100000001</v>
       </c>
-      <c r="AH187">
+      <c r="AH187" s="14">
         <v>149.97357199999999</v>
       </c>
-      <c r="AI187" s="9">
+      <c r="AI187" s="15">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17579,6 +18012,6808 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6679B6B0-A902-48AC-9A71-59F110D5EE0F}">
+  <dimension ref="A1:AG93"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5">
+        <v>2023</v>
+      </c>
+      <c r="F5">
+        <v>2024</v>
+      </c>
+      <c r="G5">
+        <v>2025</v>
+      </c>
+      <c r="H5">
+        <v>2026</v>
+      </c>
+      <c r="I5">
+        <v>2027</v>
+      </c>
+      <c r="J5">
+        <v>2028</v>
+      </c>
+      <c r="K5">
+        <v>2029</v>
+      </c>
+      <c r="L5">
+        <v>2030</v>
+      </c>
+      <c r="M5">
+        <v>2031</v>
+      </c>
+      <c r="N5">
+        <v>2032</v>
+      </c>
+      <c r="O5">
+        <v>2033</v>
+      </c>
+      <c r="P5">
+        <v>2034</v>
+      </c>
+      <c r="Q5">
+        <v>2035</v>
+      </c>
+      <c r="R5">
+        <v>2036</v>
+      </c>
+      <c r="S5">
+        <v>2037</v>
+      </c>
+      <c r="T5">
+        <v>2038</v>
+      </c>
+      <c r="U5">
+        <v>2039</v>
+      </c>
+      <c r="V5">
+        <v>2040</v>
+      </c>
+      <c r="W5">
+        <v>2041</v>
+      </c>
+      <c r="X5">
+        <v>2042</v>
+      </c>
+      <c r="Y5">
+        <v>2043</v>
+      </c>
+      <c r="Z5">
+        <v>2044</v>
+      </c>
+      <c r="AA5">
+        <v>2045</v>
+      </c>
+      <c r="AB5">
+        <v>2046</v>
+      </c>
+      <c r="AC5">
+        <v>2047</v>
+      </c>
+      <c r="AD5">
+        <v>2048</v>
+      </c>
+      <c r="AE5">
+        <v>2049</v>
+      </c>
+      <c r="AF5">
+        <v>2050</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>609</v>
+      </c>
+      <c r="C8" t="s">
+        <v>608</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>16.645529</v>
+      </c>
+      <c r="G8">
+        <v>16.962237999999999</v>
+      </c>
+      <c r="H8">
+        <v>17.297937000000001</v>
+      </c>
+      <c r="I8">
+        <v>17.637350000000001</v>
+      </c>
+      <c r="J8">
+        <v>17.975957999999999</v>
+      </c>
+      <c r="K8">
+        <v>18.323191000000001</v>
+      </c>
+      <c r="L8">
+        <v>18.671122</v>
+      </c>
+      <c r="M8">
+        <v>19.020292000000001</v>
+      </c>
+      <c r="N8">
+        <v>19.366976000000001</v>
+      </c>
+      <c r="O8">
+        <v>19.701832</v>
+      </c>
+      <c r="P8">
+        <v>20.022341000000001</v>
+      </c>
+      <c r="Q8">
+        <v>20.338335000000001</v>
+      </c>
+      <c r="R8">
+        <v>20.648126999999999</v>
+      </c>
+      <c r="S8">
+        <v>20.945910000000001</v>
+      </c>
+      <c r="T8">
+        <v>21.232154999999999</v>
+      </c>
+      <c r="U8">
+        <v>21.506626000000001</v>
+      </c>
+      <c r="V8">
+        <v>21.772038999999999</v>
+      </c>
+      <c r="W8">
+        <v>22.026168999999999</v>
+      </c>
+      <c r="X8">
+        <v>22.271370000000001</v>
+      </c>
+      <c r="Y8">
+        <v>22.506741000000002</v>
+      </c>
+      <c r="Z8">
+        <v>22.737044999999998</v>
+      </c>
+      <c r="AA8">
+        <v>22.966515999999999</v>
+      </c>
+      <c r="AB8">
+        <v>23.194811000000001</v>
+      </c>
+      <c r="AC8">
+        <v>23.422667000000001</v>
+      </c>
+      <c r="AD8">
+        <v>23.650106000000001</v>
+      </c>
+      <c r="AE8">
+        <v>23.877323000000001</v>
+      </c>
+      <c r="AF8">
+        <v>24.103532999999999</v>
+      </c>
+      <c r="AG8" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>607</v>
+      </c>
+      <c r="C9" t="s">
+        <v>606</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9">
+        <v>26.605318</v>
+      </c>
+      <c r="G9">
+        <v>26.781590000000001</v>
+      </c>
+      <c r="H9">
+        <v>26.987282</v>
+      </c>
+      <c r="I9">
+        <v>27.200581</v>
+      </c>
+      <c r="J9">
+        <v>27.420453999999999</v>
+      </c>
+      <c r="K9">
+        <v>27.653373999999999</v>
+      </c>
+      <c r="L9">
+        <v>27.889208</v>
+      </c>
+      <c r="M9">
+        <v>28.127293000000002</v>
+      </c>
+      <c r="N9">
+        <v>28.362696</v>
+      </c>
+      <c r="O9">
+        <v>28.587047999999999</v>
+      </c>
+      <c r="P9">
+        <v>28.798484999999999</v>
+      </c>
+      <c r="Q9">
+        <v>29.005108</v>
+      </c>
+      <c r="R9">
+        <v>29.206934</v>
+      </c>
+      <c r="S9">
+        <v>29.397682</v>
+      </c>
+      <c r="T9">
+        <v>29.579087999999999</v>
+      </c>
+      <c r="U9">
+        <v>29.751591000000001</v>
+      </c>
+      <c r="V9">
+        <v>29.918130999999999</v>
+      </c>
+      <c r="W9">
+        <v>30.076429000000001</v>
+      </c>
+      <c r="X9">
+        <v>30.228321000000001</v>
+      </c>
+      <c r="Y9">
+        <v>30.375741999999999</v>
+      </c>
+      <c r="Z9">
+        <v>30.522755</v>
+      </c>
+      <c r="AA9">
+        <v>30.670508999999999</v>
+      </c>
+      <c r="AB9">
+        <v>30.818306</v>
+      </c>
+      <c r="AC9">
+        <v>30.966200000000001</v>
+      </c>
+      <c r="AD9">
+        <v>31.114232999999999</v>
+      </c>
+      <c r="AE9">
+        <v>31.262747000000001</v>
+      </c>
+      <c r="AF9">
+        <v>31.41095</v>
+      </c>
+      <c r="AG9" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>605</v>
+      </c>
+      <c r="C10" t="s">
+        <v>604</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10">
+        <v>1.3358559999999999</v>
+      </c>
+      <c r="G10">
+        <v>1.335485</v>
+      </c>
+      <c r="H10">
+        <v>1.335121</v>
+      </c>
+      <c r="I10">
+        <v>1.3347629999999999</v>
+      </c>
+      <c r="J10">
+        <v>1.334411</v>
+      </c>
+      <c r="K10">
+        <v>1.3340669999999999</v>
+      </c>
+      <c r="L10">
+        <v>1.333728</v>
+      </c>
+      <c r="M10">
+        <v>1.333394</v>
+      </c>
+      <c r="N10">
+        <v>1.333067</v>
+      </c>
+      <c r="O10">
+        <v>1.332746</v>
+      </c>
+      <c r="P10">
+        <v>1.3324309999999999</v>
+      </c>
+      <c r="Q10">
+        <v>1.33212</v>
+      </c>
+      <c r="R10">
+        <v>1.3318160000000001</v>
+      </c>
+      <c r="S10">
+        <v>1.3315170000000001</v>
+      </c>
+      <c r="T10">
+        <v>1.331223</v>
+      </c>
+      <c r="U10">
+        <v>1.3309340000000001</v>
+      </c>
+      <c r="V10">
+        <v>1.330651</v>
+      </c>
+      <c r="W10">
+        <v>1.330373</v>
+      </c>
+      <c r="X10">
+        <v>1.3300989999999999</v>
+      </c>
+      <c r="Y10">
+        <v>1.329831</v>
+      </c>
+      <c r="Z10">
+        <v>1.3295669999999999</v>
+      </c>
+      <c r="AA10">
+        <v>1.3293079999999999</v>
+      </c>
+      <c r="AB10">
+        <v>1.329053</v>
+      </c>
+      <c r="AC10">
+        <v>1.3288040000000001</v>
+      </c>
+      <c r="AD10">
+        <v>1.3285579999999999</v>
+      </c>
+      <c r="AE10">
+        <v>1.3283160000000001</v>
+      </c>
+      <c r="AF10">
+        <v>1.328079</v>
+      </c>
+      <c r="AG10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>603</v>
+      </c>
+      <c r="C11" t="s">
+        <v>602</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11">
+        <v>65.614693000000003</v>
+      </c>
+      <c r="G11">
+        <v>66.503310999999997</v>
+      </c>
+      <c r="H11">
+        <v>67.422646</v>
+      </c>
+      <c r="I11">
+        <v>68.347206</v>
+      </c>
+      <c r="J11">
+        <v>69.275345000000002</v>
+      </c>
+      <c r="K11">
+        <v>70.215851000000001</v>
+      </c>
+      <c r="L11">
+        <v>71.155624000000003</v>
+      </c>
+      <c r="M11">
+        <v>72.095222000000007</v>
+      </c>
+      <c r="N11">
+        <v>73.022018000000003</v>
+      </c>
+      <c r="O11">
+        <v>73.917961000000005</v>
+      </c>
+      <c r="P11">
+        <v>74.776138000000003</v>
+      </c>
+      <c r="Q11">
+        <v>75.619468999999995</v>
+      </c>
+      <c r="R11">
+        <v>76.443016</v>
+      </c>
+      <c r="S11">
+        <v>77.232451999999995</v>
+      </c>
+      <c r="T11">
+        <v>77.991675999999998</v>
+      </c>
+      <c r="U11">
+        <v>78.71611</v>
+      </c>
+      <c r="V11">
+        <v>79.412209000000004</v>
+      </c>
+      <c r="W11">
+        <v>80.076683000000003</v>
+      </c>
+      <c r="X11">
+        <v>80.717903000000007</v>
+      </c>
+      <c r="Y11">
+        <v>81.333213999999998</v>
+      </c>
+      <c r="Z11">
+        <v>81.934601000000001</v>
+      </c>
+      <c r="AA11">
+        <v>82.534103000000002</v>
+      </c>
+      <c r="AB11">
+        <v>83.129738000000003</v>
+      </c>
+      <c r="AC11">
+        <v>83.726119999999995</v>
+      </c>
+      <c r="AD11">
+        <v>84.322975</v>
+      </c>
+      <c r="AE11">
+        <v>84.920402999999993</v>
+      </c>
+      <c r="AF11">
+        <v>85.516907000000003</v>
+      </c>
+      <c r="AG11" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>601</v>
+      </c>
+      <c r="C12" t="s">
+        <v>600</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12">
+        <v>4.7679400000000003</v>
+      </c>
+      <c r="G12">
+        <v>4.7259000000000002</v>
+      </c>
+      <c r="H12">
+        <v>4.6848210000000003</v>
+      </c>
+      <c r="I12">
+        <v>4.6445790000000002</v>
+      </c>
+      <c r="J12">
+        <v>4.6050199999999997</v>
+      </c>
+      <c r="K12">
+        <v>4.5659689999999999</v>
+      </c>
+      <c r="L12">
+        <v>4.5268259999999998</v>
+      </c>
+      <c r="M12">
+        <v>4.4876120000000004</v>
+      </c>
+      <c r="N12">
+        <v>4.4495209999999998</v>
+      </c>
+      <c r="O12">
+        <v>4.412687</v>
+      </c>
+      <c r="P12">
+        <v>4.3773140000000001</v>
+      </c>
+      <c r="Q12">
+        <v>4.3434270000000001</v>
+      </c>
+      <c r="R12">
+        <v>4.3103170000000004</v>
+      </c>
+      <c r="S12">
+        <v>4.2779480000000003</v>
+      </c>
+      <c r="T12">
+        <v>4.246086</v>
+      </c>
+      <c r="U12">
+        <v>4.2144880000000002</v>
+      </c>
+      <c r="V12">
+        <v>4.1831740000000002</v>
+      </c>
+      <c r="W12">
+        <v>4.1520609999999998</v>
+      </c>
+      <c r="X12">
+        <v>4.1220239999999997</v>
+      </c>
+      <c r="Y12">
+        <v>4.0930540000000004</v>
+      </c>
+      <c r="Z12">
+        <v>4.0651210000000004</v>
+      </c>
+      <c r="AA12">
+        <v>4.0385</v>
+      </c>
+      <c r="AB12">
+        <v>4.0128209999999997</v>
+      </c>
+      <c r="AC12">
+        <v>3.9867460000000001</v>
+      </c>
+      <c r="AD12">
+        <v>3.9604469999999998</v>
+      </c>
+      <c r="AE12">
+        <v>3.9341620000000002</v>
+      </c>
+      <c r="AF12">
+        <v>3.908093</v>
+      </c>
+      <c r="AG12" s="9">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>599</v>
+      </c>
+      <c r="C13" t="s">
+        <v>598</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13">
+        <v>5.242597</v>
+      </c>
+      <c r="G13">
+        <v>5.231007</v>
+      </c>
+      <c r="H13">
+        <v>5.2227259999999998</v>
+      </c>
+      <c r="I13">
+        <v>5.2138559999999998</v>
+      </c>
+      <c r="J13">
+        <v>5.2017620000000004</v>
+      </c>
+      <c r="K13">
+        <v>5.1923170000000001</v>
+      </c>
+      <c r="L13">
+        <v>5.1804410000000001</v>
+      </c>
+      <c r="M13">
+        <v>5.1671880000000003</v>
+      </c>
+      <c r="N13">
+        <v>5.1553120000000003</v>
+      </c>
+      <c r="O13">
+        <v>5.1438940000000004</v>
+      </c>
+      <c r="P13">
+        <v>5.1323730000000003</v>
+      </c>
+      <c r="Q13">
+        <v>5.1213470000000001</v>
+      </c>
+      <c r="R13">
+        <v>5.111237</v>
+      </c>
+      <c r="S13">
+        <v>5.1019629999999996</v>
+      </c>
+      <c r="T13">
+        <v>5.0929900000000004</v>
+      </c>
+      <c r="U13">
+        <v>5.0845039999999999</v>
+      </c>
+      <c r="V13">
+        <v>5.0773279999999996</v>
+      </c>
+      <c r="W13">
+        <v>5.0708909999999996</v>
+      </c>
+      <c r="X13">
+        <v>5.0646820000000004</v>
+      </c>
+      <c r="Y13">
+        <v>5.0585370000000003</v>
+      </c>
+      <c r="Z13">
+        <v>5.0526479999999996</v>
+      </c>
+      <c r="AA13">
+        <v>5.0474759999999996</v>
+      </c>
+      <c r="AB13">
+        <v>5.0432449999999998</v>
+      </c>
+      <c r="AC13">
+        <v>5.0376599999999998</v>
+      </c>
+      <c r="AD13">
+        <v>5.0307449999999996</v>
+      </c>
+      <c r="AE13">
+        <v>5.0227019999999998</v>
+      </c>
+      <c r="AF13">
+        <v>5.0133200000000002</v>
+      </c>
+      <c r="AG13" s="9">
+        <v>-2E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>597</v>
+      </c>
+      <c r="C14" t="s">
+        <v>596</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14">
+        <v>4.9249999999999997E-3</v>
+      </c>
+      <c r="G14">
+        <v>7.8969999999999995E-3</v>
+      </c>
+      <c r="H14">
+        <v>1.1523E-2</v>
+      </c>
+      <c r="I14">
+        <v>1.5072E-2</v>
+      </c>
+      <c r="J14">
+        <v>1.8269000000000001E-2</v>
+      </c>
+      <c r="K14">
+        <v>2.1329999999999998E-2</v>
+      </c>
+      <c r="L14">
+        <v>2.419E-2</v>
+      </c>
+      <c r="M14">
+        <v>2.7018E-2</v>
+      </c>
+      <c r="N14">
+        <v>2.9863000000000001E-2</v>
+      </c>
+      <c r="O14">
+        <v>3.2679E-2</v>
+      </c>
+      <c r="P14">
+        <v>3.5394000000000002E-2</v>
+      </c>
+      <c r="Q14">
+        <v>3.8012999999999998E-2</v>
+      </c>
+      <c r="R14">
+        <v>4.0598000000000002E-2</v>
+      </c>
+      <c r="S14">
+        <v>4.3115000000000001E-2</v>
+      </c>
+      <c r="T14">
+        <v>4.5557E-2</v>
+      </c>
+      <c r="U14">
+        <v>4.7931000000000001E-2</v>
+      </c>
+      <c r="V14">
+        <v>5.0323E-2</v>
+      </c>
+      <c r="W14">
+        <v>5.2707999999999998E-2</v>
+      </c>
+      <c r="X14">
+        <v>5.5048E-2</v>
+      </c>
+      <c r="Y14">
+        <v>5.7336999999999999E-2</v>
+      </c>
+      <c r="Z14">
+        <v>5.9591999999999999E-2</v>
+      </c>
+      <c r="AA14">
+        <v>6.182E-2</v>
+      </c>
+      <c r="AB14">
+        <v>6.3983999999999999E-2</v>
+      </c>
+      <c r="AC14">
+        <v>6.6125000000000003E-2</v>
+      </c>
+      <c r="AD14">
+        <v>6.8224000000000007E-2</v>
+      </c>
+      <c r="AE14">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="AF14">
+        <v>7.2325E-2</v>
+      </c>
+      <c r="AG14" s="9">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>595</v>
+      </c>
+      <c r="C15" t="s">
+        <v>594</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15">
+        <v>2.220637</v>
+      </c>
+      <c r="G15">
+        <v>2.2126389999999998</v>
+      </c>
+      <c r="H15">
+        <v>2.2048290000000001</v>
+      </c>
+      <c r="I15">
+        <v>2.1970589999999999</v>
+      </c>
+      <c r="J15">
+        <v>2.1893750000000001</v>
+      </c>
+      <c r="K15">
+        <v>2.1817530000000001</v>
+      </c>
+      <c r="L15">
+        <v>2.1741869999999999</v>
+      </c>
+      <c r="M15">
+        <v>2.1666919999999998</v>
+      </c>
+      <c r="N15">
+        <v>2.1590280000000002</v>
+      </c>
+      <c r="O15">
+        <v>2.1512479999999998</v>
+      </c>
+      <c r="P15">
+        <v>2.1434000000000002</v>
+      </c>
+      <c r="Q15">
+        <v>2.135421</v>
+      </c>
+      <c r="R15">
+        <v>2.1273569999999999</v>
+      </c>
+      <c r="S15">
+        <v>2.1191689999999999</v>
+      </c>
+      <c r="T15">
+        <v>2.1109499999999999</v>
+      </c>
+      <c r="U15">
+        <v>2.102684</v>
+      </c>
+      <c r="V15">
+        <v>2.0943290000000001</v>
+      </c>
+      <c r="W15">
+        <v>2.085804</v>
+      </c>
+      <c r="X15">
+        <v>2.0775749999999999</v>
+      </c>
+      <c r="Y15">
+        <v>2.0696460000000001</v>
+      </c>
+      <c r="Z15">
+        <v>2.062065</v>
+      </c>
+      <c r="AA15">
+        <v>2.054862</v>
+      </c>
+      <c r="AB15">
+        <v>2.0480360000000002</v>
+      </c>
+      <c r="AC15">
+        <v>2.0416629999999998</v>
+      </c>
+      <c r="AD15">
+        <v>2.0357189999999998</v>
+      </c>
+      <c r="AE15">
+        <v>2.030173</v>
+      </c>
+      <c r="AF15">
+        <v>2.0250210000000002</v>
+      </c>
+      <c r="AG15" s="9">
+        <v>-4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>593</v>
+      </c>
+      <c r="C16" t="s">
+        <v>592</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16">
+        <v>1.3606750000000001</v>
+      </c>
+      <c r="G16">
+        <v>1.4081809999999999</v>
+      </c>
+      <c r="H16">
+        <v>1.455492</v>
+      </c>
+      <c r="I16">
+        <v>1.5027200000000001</v>
+      </c>
+      <c r="J16">
+        <v>1.5491330000000001</v>
+      </c>
+      <c r="K16">
+        <v>1.595817</v>
+      </c>
+      <c r="L16">
+        <v>1.642325</v>
+      </c>
+      <c r="M16">
+        <v>1.688836</v>
+      </c>
+      <c r="N16">
+        <v>1.7355499999999999</v>
+      </c>
+      <c r="O16">
+        <v>1.7816719999999999</v>
+      </c>
+      <c r="P16">
+        <v>1.826767</v>
+      </c>
+      <c r="Q16">
+        <v>1.8719479999999999</v>
+      </c>
+      <c r="R16">
+        <v>1.9167529999999999</v>
+      </c>
+      <c r="S16">
+        <v>1.9607570000000001</v>
+      </c>
+      <c r="T16">
+        <v>2.0037910000000001</v>
+      </c>
+      <c r="U16">
+        <v>2.0454750000000002</v>
+      </c>
+      <c r="V16">
+        <v>2.0861049999999999</v>
+      </c>
+      <c r="W16">
+        <v>2.1256249999999999</v>
+      </c>
+      <c r="X16">
+        <v>2.1640130000000002</v>
+      </c>
+      <c r="Y16">
+        <v>2.2007629999999998</v>
+      </c>
+      <c r="Z16">
+        <v>2.2363569999999999</v>
+      </c>
+      <c r="AA16">
+        <v>2.271668</v>
+      </c>
+      <c r="AB16">
+        <v>2.306613</v>
+      </c>
+      <c r="AC16">
+        <v>2.34118</v>
+      </c>
+      <c r="AD16">
+        <v>2.3753600000000001</v>
+      </c>
+      <c r="AE16">
+        <v>2.4091840000000002</v>
+      </c>
+      <c r="AF16">
+        <v>2.4425819999999998</v>
+      </c>
+      <c r="AG16" s="9">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
+        <v>591</v>
+      </c>
+      <c r="C17" t="s">
+        <v>590</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17">
+        <v>123.798164</v>
+      </c>
+      <c r="G17">
+        <v>125.168251</v>
+      </c>
+      <c r="H17">
+        <v>126.62236799999999</v>
+      </c>
+      <c r="I17">
+        <v>128.09318500000001</v>
+      </c>
+      <c r="J17">
+        <v>129.569717</v>
+      </c>
+      <c r="K17">
+        <v>131.083664</v>
+      </c>
+      <c r="L17">
+        <v>132.59764100000001</v>
+      </c>
+      <c r="M17">
+        <v>134.11355599999999</v>
+      </c>
+      <c r="N17">
+        <v>135.61402899999999</v>
+      </c>
+      <c r="O17">
+        <v>137.061768</v>
+      </c>
+      <c r="P17">
+        <v>138.44465600000001</v>
+      </c>
+      <c r="Q17">
+        <v>139.80519100000001</v>
+      </c>
+      <c r="R17">
+        <v>141.13613900000001</v>
+      </c>
+      <c r="S17">
+        <v>142.41052199999999</v>
+      </c>
+      <c r="T17">
+        <v>143.633499</v>
+      </c>
+      <c r="U17">
+        <v>144.800354</v>
+      </c>
+      <c r="V17">
+        <v>145.92430100000001</v>
+      </c>
+      <c r="W17">
+        <v>146.996735</v>
+      </c>
+      <c r="X17">
+        <v>148.03105199999999</v>
+      </c>
+      <c r="Y17">
+        <v>149.024857</v>
+      </c>
+      <c r="Z17">
+        <v>149.99975599999999</v>
+      </c>
+      <c r="AA17">
+        <v>150.97473099999999</v>
+      </c>
+      <c r="AB17">
+        <v>151.946594</v>
+      </c>
+      <c r="AC17">
+        <v>152.91716</v>
+      </c>
+      <c r="AD17">
+        <v>153.886368</v>
+      </c>
+      <c r="AE17">
+        <v>154.855301</v>
+      </c>
+      <c r="AF17">
+        <v>155.82081600000001</v>
+      </c>
+      <c r="AG17" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>589</v>
+      </c>
+      <c r="C19" t="s">
+        <v>588</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19">
+        <v>16.645529</v>
+      </c>
+      <c r="G19">
+        <v>16.962236000000001</v>
+      </c>
+      <c r="H19">
+        <v>17.297931999999999</v>
+      </c>
+      <c r="I19">
+        <v>17.637352</v>
+      </c>
+      <c r="J19">
+        <v>17.975957999999999</v>
+      </c>
+      <c r="K19">
+        <v>18.323191000000001</v>
+      </c>
+      <c r="L19">
+        <v>18.671116000000001</v>
+      </c>
+      <c r="M19">
+        <v>19.020289999999999</v>
+      </c>
+      <c r="N19">
+        <v>19.366969999999998</v>
+      </c>
+      <c r="O19">
+        <v>19.701841000000002</v>
+      </c>
+      <c r="P19">
+        <v>20.022338999999999</v>
+      </c>
+      <c r="Q19">
+        <v>20.338339000000001</v>
+      </c>
+      <c r="R19">
+        <v>20.648116999999999</v>
+      </c>
+      <c r="S19">
+        <v>20.945914999999999</v>
+      </c>
+      <c r="T19">
+        <v>21.232161000000001</v>
+      </c>
+      <c r="U19">
+        <v>21.506636</v>
+      </c>
+      <c r="V19">
+        <v>21.772034000000001</v>
+      </c>
+      <c r="W19">
+        <v>22.026174999999999</v>
+      </c>
+      <c r="X19">
+        <v>22.271376</v>
+      </c>
+      <c r="Y19">
+        <v>22.506746</v>
+      </c>
+      <c r="Z19">
+        <v>22.737047</v>
+      </c>
+      <c r="AA19">
+        <v>22.966528</v>
+      </c>
+      <c r="AB19">
+        <v>23.194814999999998</v>
+      </c>
+      <c r="AC19">
+        <v>23.422671999999999</v>
+      </c>
+      <c r="AD19">
+        <v>23.650103000000001</v>
+      </c>
+      <c r="AE19">
+        <v>23.87734</v>
+      </c>
+      <c r="AF19">
+        <v>24.103531</v>
+      </c>
+      <c r="AG19" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>587</v>
+      </c>
+      <c r="C20" t="s">
+        <v>586</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20">
+        <v>1.3358559999999999</v>
+      </c>
+      <c r="G20">
+        <v>1.335485</v>
+      </c>
+      <c r="H20">
+        <v>1.335121</v>
+      </c>
+      <c r="I20">
+        <v>1.3347629999999999</v>
+      </c>
+      <c r="J20">
+        <v>1.3344119999999999</v>
+      </c>
+      <c r="K20">
+        <v>1.334066</v>
+      </c>
+      <c r="L20">
+        <v>1.3337270000000001</v>
+      </c>
+      <c r="M20">
+        <v>1.333394</v>
+      </c>
+      <c r="N20">
+        <v>1.333067</v>
+      </c>
+      <c r="O20">
+        <v>1.332746</v>
+      </c>
+      <c r="P20">
+        <v>1.33243</v>
+      </c>
+      <c r="Q20">
+        <v>1.33212</v>
+      </c>
+      <c r="R20">
+        <v>1.3318160000000001</v>
+      </c>
+      <c r="S20">
+        <v>1.3315170000000001</v>
+      </c>
+      <c r="T20">
+        <v>1.331223</v>
+      </c>
+      <c r="U20">
+        <v>1.3309340000000001</v>
+      </c>
+      <c r="V20">
+        <v>1.330651</v>
+      </c>
+      <c r="W20">
+        <v>1.3303720000000001</v>
+      </c>
+      <c r="X20">
+        <v>1.3300989999999999</v>
+      </c>
+      <c r="Y20">
+        <v>1.329831</v>
+      </c>
+      <c r="Z20">
+        <v>1.3295669999999999</v>
+      </c>
+      <c r="AA20">
+        <v>1.3293079999999999</v>
+      </c>
+      <c r="AB20">
+        <v>1.329053</v>
+      </c>
+      <c r="AC20">
+        <v>1.328803</v>
+      </c>
+      <c r="AD20">
+        <v>1.3285579999999999</v>
+      </c>
+      <c r="AE20">
+        <v>1.3283160000000001</v>
+      </c>
+      <c r="AF20">
+        <v>1.3280799999999999</v>
+      </c>
+      <c r="AG20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>585</v>
+      </c>
+      <c r="C21" t="s">
+        <v>584</v>
+      </c>
+      <c r="D21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21">
+        <v>1.3606750000000001</v>
+      </c>
+      <c r="G21">
+        <v>1.40818</v>
+      </c>
+      <c r="H21">
+        <v>1.4554910000000001</v>
+      </c>
+      <c r="I21">
+        <v>1.5027200000000001</v>
+      </c>
+      <c r="J21">
+        <v>1.549134</v>
+      </c>
+      <c r="K21">
+        <v>1.595817</v>
+      </c>
+      <c r="L21">
+        <v>1.642326</v>
+      </c>
+      <c r="M21">
+        <v>1.688836</v>
+      </c>
+      <c r="N21">
+        <v>1.7355499999999999</v>
+      </c>
+      <c r="O21">
+        <v>1.781671</v>
+      </c>
+      <c r="P21">
+        <v>1.8267679999999999</v>
+      </c>
+      <c r="Q21">
+        <v>1.8719479999999999</v>
+      </c>
+      <c r="R21">
+        <v>1.9167529999999999</v>
+      </c>
+      <c r="S21">
+        <v>1.9607559999999999</v>
+      </c>
+      <c r="T21">
+        <v>2.00379</v>
+      </c>
+      <c r="U21">
+        <v>2.0454750000000002</v>
+      </c>
+      <c r="V21">
+        <v>2.0861049999999999</v>
+      </c>
+      <c r="W21">
+        <v>2.125626</v>
+      </c>
+      <c r="X21">
+        <v>2.1640130000000002</v>
+      </c>
+      <c r="Y21">
+        <v>2.2007639999999999</v>
+      </c>
+      <c r="Z21">
+        <v>2.2363559999999998</v>
+      </c>
+      <c r="AA21">
+        <v>2.2716669999999999</v>
+      </c>
+      <c r="AB21">
+        <v>2.306613</v>
+      </c>
+      <c r="AC21">
+        <v>2.3411789999999999</v>
+      </c>
+      <c r="AD21">
+        <v>2.3753600000000001</v>
+      </c>
+      <c r="AE21">
+        <v>2.4091849999999999</v>
+      </c>
+      <c r="AF21">
+        <v>2.4425810000000001</v>
+      </c>
+      <c r="AG21" s="9">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>583</v>
+      </c>
+      <c r="C22" t="s">
+        <v>582</v>
+      </c>
+      <c r="D22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22">
+        <v>79.649451999999997</v>
+      </c>
+      <c r="G22">
+        <v>80.900047000000001</v>
+      </c>
+      <c r="H22">
+        <v>82.197365000000005</v>
+      </c>
+      <c r="I22">
+        <v>83.504149999999996</v>
+      </c>
+      <c r="J22">
+        <v>84.811256</v>
+      </c>
+      <c r="K22">
+        <v>86.135658000000006</v>
+      </c>
+      <c r="L22">
+        <v>87.457458000000003</v>
+      </c>
+      <c r="M22">
+        <v>88.779007000000007</v>
+      </c>
+      <c r="N22">
+        <v>90.091567999999995</v>
+      </c>
+      <c r="O22">
+        <v>91.374115000000003</v>
+      </c>
+      <c r="P22">
+        <v>92.619193999999993</v>
+      </c>
+      <c r="Q22">
+        <v>93.851294999999993</v>
+      </c>
+      <c r="R22">
+        <v>95.065894999999998</v>
+      </c>
+      <c r="S22">
+        <v>96.248183999999995</v>
+      </c>
+      <c r="T22">
+        <v>97.400749000000005</v>
+      </c>
+      <c r="U22">
+        <v>98.520065000000002</v>
+      </c>
+      <c r="V22">
+        <v>99.614029000000002</v>
+      </c>
+      <c r="W22">
+        <v>100.677948</v>
+      </c>
+      <c r="X22">
+        <v>101.719604</v>
+      </c>
+      <c r="Y22">
+        <v>102.736504</v>
+      </c>
+      <c r="Z22">
+        <v>103.740959</v>
+      </c>
+      <c r="AA22">
+        <v>104.74514000000001</v>
+      </c>
+      <c r="AB22">
+        <v>105.747086</v>
+      </c>
+      <c r="AC22">
+        <v>106.748116</v>
+      </c>
+      <c r="AD22">
+        <v>107.748085</v>
+      </c>
+      <c r="AE22">
+        <v>108.747696</v>
+      </c>
+      <c r="AF22">
+        <v>109.74496499999999</v>
+      </c>
+      <c r="AG22" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>581</v>
+      </c>
+      <c r="C23" t="s">
+        <v>580</v>
+      </c>
+      <c r="D23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23">
+        <v>43.140506999999999</v>
+      </c>
+      <c r="G23">
+        <v>43.232368000000001</v>
+      </c>
+      <c r="H23">
+        <v>43.345275999999998</v>
+      </c>
+      <c r="I23">
+        <v>43.463279999999997</v>
+      </c>
+      <c r="J23">
+        <v>43.586711999999999</v>
+      </c>
+      <c r="K23">
+        <v>43.719509000000002</v>
+      </c>
+      <c r="L23">
+        <v>43.854377999999997</v>
+      </c>
+      <c r="M23">
+        <v>43.990794999999999</v>
+      </c>
+      <c r="N23">
+        <v>44.124844000000003</v>
+      </c>
+      <c r="O23">
+        <v>44.250751000000001</v>
+      </c>
+      <c r="P23">
+        <v>44.367279000000003</v>
+      </c>
+      <c r="Q23">
+        <v>44.480221</v>
+      </c>
+      <c r="R23">
+        <v>44.589432000000002</v>
+      </c>
+      <c r="S23">
+        <v>44.690407</v>
+      </c>
+      <c r="T23">
+        <v>44.784587999999999</v>
+      </c>
+      <c r="U23">
+        <v>44.872436999999998</v>
+      </c>
+      <c r="V23">
+        <v>44.956017000000003</v>
+      </c>
+      <c r="W23">
+        <v>45.033755999999997</v>
+      </c>
+      <c r="X23">
+        <v>45.107017999999997</v>
+      </c>
+      <c r="Y23">
+        <v>45.177340999999998</v>
+      </c>
+      <c r="Z23">
+        <v>45.247604000000003</v>
+      </c>
+      <c r="AA23">
+        <v>45.318492999999997</v>
+      </c>
+      <c r="AB23">
+        <v>45.389637</v>
+      </c>
+      <c r="AC23">
+        <v>45.461101999999997</v>
+      </c>
+      <c r="AD23">
+        <v>45.532989999999998</v>
+      </c>
+      <c r="AE23">
+        <v>45.605553</v>
+      </c>
+      <c r="AF23">
+        <v>45.678272</v>
+      </c>
+      <c r="AG23" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>579</v>
+      </c>
+      <c r="C24" t="s">
+        <v>578</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24">
+        <v>142.13201900000001</v>
+      </c>
+      <c r="G24">
+        <v>143.83831799999999</v>
+      </c>
+      <c r="H24">
+        <v>145.63118</v>
+      </c>
+      <c r="I24">
+        <v>147.442261</v>
+      </c>
+      <c r="J24">
+        <v>149.25747699999999</v>
+      </c>
+      <c r="K24">
+        <v>151.10824600000001</v>
+      </c>
+      <c r="L24">
+        <v>152.95901499999999</v>
+      </c>
+      <c r="M24">
+        <v>154.812332</v>
+      </c>
+      <c r="N24">
+        <v>156.651993</v>
+      </c>
+      <c r="O24">
+        <v>158.44113200000001</v>
+      </c>
+      <c r="P24">
+        <v>160.168015</v>
+      </c>
+      <c r="Q24">
+        <v>161.873932</v>
+      </c>
+      <c r="R24">
+        <v>163.55201700000001</v>
+      </c>
+      <c r="S24">
+        <v>165.17678799999999</v>
+      </c>
+      <c r="T24">
+        <v>166.75251800000001</v>
+      </c>
+      <c r="U24">
+        <v>168.275543</v>
+      </c>
+      <c r="V24">
+        <v>169.758835</v>
+      </c>
+      <c r="W24">
+        <v>171.19387800000001</v>
+      </c>
+      <c r="X24">
+        <v>172.59210200000001</v>
+      </c>
+      <c r="Y24">
+        <v>173.951187</v>
+      </c>
+      <c r="Z24">
+        <v>175.29153400000001</v>
+      </c>
+      <c r="AA24">
+        <v>176.631134</v>
+      </c>
+      <c r="AB24">
+        <v>177.96719400000001</v>
+      </c>
+      <c r="AC24">
+        <v>179.30188000000001</v>
+      </c>
+      <c r="AD24">
+        <v>180.63510099999999</v>
+      </c>
+      <c r="AE24">
+        <v>181.96807899999999</v>
+      </c>
+      <c r="AF24">
+        <v>183.29742400000001</v>
+      </c>
+      <c r="AG24" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>577</v>
+      </c>
+      <c r="C26" t="s">
+        <v>576</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26">
+        <v>62.064090999999998</v>
+      </c>
+      <c r="G26">
+        <v>62.296463000000003</v>
+      </c>
+      <c r="H26">
+        <v>62.600315000000002</v>
+      </c>
+      <c r="I26">
+        <v>62.926879999999997</v>
+      </c>
+      <c r="J26">
+        <v>63.228167999999997</v>
+      </c>
+      <c r="K26">
+        <v>64.053841000000006</v>
+      </c>
+      <c r="L26">
+        <v>64.829207999999994</v>
+      </c>
+      <c r="M26">
+        <v>65.567513000000005</v>
+      </c>
+      <c r="N26">
+        <v>66.280677999999995</v>
+      </c>
+      <c r="O26">
+        <v>66.984313999999998</v>
+      </c>
+      <c r="P26">
+        <v>67.653503000000001</v>
+      </c>
+      <c r="Q26">
+        <v>68.314453</v>
+      </c>
+      <c r="R26">
+        <v>68.978340000000003</v>
+      </c>
+      <c r="S26">
+        <v>69.632026999999994</v>
+      </c>
+      <c r="T26">
+        <v>70.273940999999994</v>
+      </c>
+      <c r="U26">
+        <v>70.902107000000001</v>
+      </c>
+      <c r="V26">
+        <v>71.522514000000001</v>
+      </c>
+      <c r="W26">
+        <v>72.129929000000004</v>
+      </c>
+      <c r="X26">
+        <v>72.728317000000004</v>
+      </c>
+      <c r="Y26">
+        <v>73.317879000000005</v>
+      </c>
+      <c r="Z26">
+        <v>73.899185000000003</v>
+      </c>
+      <c r="AA26">
+        <v>74.478476999999998</v>
+      </c>
+      <c r="AB26">
+        <v>75.054726000000002</v>
+      </c>
+      <c r="AC26">
+        <v>75.626357999999996</v>
+      </c>
+      <c r="AD26">
+        <v>76.193161000000003</v>
+      </c>
+      <c r="AE26">
+        <v>76.757141000000004</v>
+      </c>
+      <c r="AF26">
+        <v>77.316254000000001</v>
+      </c>
+      <c r="AG26" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>575</v>
+      </c>
+      <c r="C27" t="s">
+        <v>574</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27">
+        <v>64.896248</v>
+      </c>
+      <c r="G27">
+        <v>65.896964999999994</v>
+      </c>
+      <c r="H27">
+        <v>66.916297999999998</v>
+      </c>
+      <c r="I27">
+        <v>67.939789000000005</v>
+      </c>
+      <c r="J27">
+        <v>68.981887999999998</v>
+      </c>
+      <c r="K27">
+        <v>69.718718999999993</v>
+      </c>
+      <c r="L27">
+        <v>70.479590999999999</v>
+      </c>
+      <c r="M27">
+        <v>71.256225999999998</v>
+      </c>
+      <c r="N27">
+        <v>72.025870999999995</v>
+      </c>
+      <c r="O27">
+        <v>72.786704999999998</v>
+      </c>
+      <c r="P27">
+        <v>73.528267</v>
+      </c>
+      <c r="Q27">
+        <v>74.274551000000002</v>
+      </c>
+      <c r="R27">
+        <v>74.990111999999996</v>
+      </c>
+      <c r="S27">
+        <v>75.663230999999996</v>
+      </c>
+      <c r="T27">
+        <v>76.299582999999998</v>
+      </c>
+      <c r="U27">
+        <v>76.895554000000004</v>
+      </c>
+      <c r="V27">
+        <v>77.456969999999998</v>
+      </c>
+      <c r="W27">
+        <v>77.980125000000001</v>
+      </c>
+      <c r="X27">
+        <v>78.474029999999999</v>
+      </c>
+      <c r="Y27">
+        <v>78.935935999999998</v>
+      </c>
+      <c r="Z27">
+        <v>79.385979000000006</v>
+      </c>
+      <c r="AA27">
+        <v>79.836296000000004</v>
+      </c>
+      <c r="AB27">
+        <v>80.284760000000006</v>
+      </c>
+      <c r="AC27">
+        <v>80.734145999999996</v>
+      </c>
+      <c r="AD27">
+        <v>81.184737999999996</v>
+      </c>
+      <c r="AE27">
+        <v>81.635727000000003</v>
+      </c>
+      <c r="AF27">
+        <v>82.086112999999997</v>
+      </c>
+      <c r="AG27" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>573</v>
+      </c>
+      <c r="C28" t="s">
+        <v>572</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28">
+        <v>2.3288120000000001</v>
+      </c>
+      <c r="G28">
+        <v>2.2297609999999999</v>
+      </c>
+      <c r="H28">
+        <v>2.1372330000000002</v>
+      </c>
+      <c r="I28">
+        <v>2.0504609999999999</v>
+      </c>
+      <c r="J28">
+        <v>1.970477</v>
+      </c>
+      <c r="K28">
+        <v>1.8960379999999999</v>
+      </c>
+      <c r="L28">
+        <v>1.8306039999999999</v>
+      </c>
+      <c r="M28">
+        <v>1.773455</v>
+      </c>
+      <c r="N28">
+        <v>1.7249589999999999</v>
+      </c>
+      <c r="O28">
+        <v>1.6851780000000001</v>
+      </c>
+      <c r="P28">
+        <v>1.6544099999999999</v>
+      </c>
+      <c r="Q28">
+        <v>1.632862</v>
+      </c>
+      <c r="R28">
+        <v>1.6100810000000001</v>
+      </c>
+      <c r="S28">
+        <v>1.586346</v>
+      </c>
+      <c r="T28">
+        <v>1.561976</v>
+      </c>
+      <c r="U28">
+        <v>1.537204</v>
+      </c>
+      <c r="V28">
+        <v>1.5122819999999999</v>
+      </c>
+      <c r="W28">
+        <v>1.4873860000000001</v>
+      </c>
+      <c r="X28">
+        <v>1.4626790000000001</v>
+      </c>
+      <c r="Y28">
+        <v>1.4382870000000001</v>
+      </c>
+      <c r="Z28">
+        <v>1.4143269999999999</v>
+      </c>
+      <c r="AA28">
+        <v>1.390946</v>
+      </c>
+      <c r="AB28">
+        <v>1.368182</v>
+      </c>
+      <c r="AC28">
+        <v>1.346109</v>
+      </c>
+      <c r="AD28">
+        <v>1.3247599999999999</v>
+      </c>
+      <c r="AE28">
+        <v>1.3041579999999999</v>
+      </c>
+      <c r="AF28">
+        <v>1.284297</v>
+      </c>
+      <c r="AG28" s="9">
+        <v>-2.3E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>571</v>
+      </c>
+      <c r="C29" t="s">
+        <v>570</v>
+      </c>
+      <c r="D29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29">
+        <v>3.9946730000000001</v>
+      </c>
+      <c r="G29">
+        <v>3.890314</v>
+      </c>
+      <c r="H29">
+        <v>3.7962470000000001</v>
+      </c>
+      <c r="I29">
+        <v>3.7080109999999999</v>
+      </c>
+      <c r="J29">
+        <v>3.6263679999999998</v>
+      </c>
+      <c r="K29">
+        <v>3.5316860000000001</v>
+      </c>
+      <c r="L29">
+        <v>3.4475519999999999</v>
+      </c>
+      <c r="M29">
+        <v>3.3742220000000001</v>
+      </c>
+      <c r="N29">
+        <v>3.3114400000000002</v>
+      </c>
+      <c r="O29">
+        <v>3.2595969999999999</v>
+      </c>
+      <c r="P29">
+        <v>3.218467</v>
+      </c>
+      <c r="Q29">
+        <v>3.1894399999999998</v>
+      </c>
+      <c r="R29">
+        <v>3.1571709999999999</v>
+      </c>
+      <c r="S29">
+        <v>3.1220840000000001</v>
+      </c>
+      <c r="T29">
+        <v>3.0848930000000001</v>
+      </c>
+      <c r="U29">
+        <v>3.04617</v>
+      </c>
+      <c r="V29">
+        <v>3.0071240000000001</v>
+      </c>
+      <c r="W29">
+        <v>2.9679280000000001</v>
+      </c>
+      <c r="X29">
+        <v>2.9288409999999998</v>
+      </c>
+      <c r="Y29">
+        <v>2.889926</v>
+      </c>
+      <c r="Z29">
+        <v>2.8518140000000001</v>
+      </c>
+      <c r="AA29">
+        <v>2.814927</v>
+      </c>
+      <c r="AB29">
+        <v>2.7792430000000001</v>
+      </c>
+      <c r="AC29">
+        <v>2.7452239999999999</v>
+      </c>
+      <c r="AD29">
+        <v>2.7127650000000001</v>
+      </c>
+      <c r="AE29">
+        <v>2.6819009999999999</v>
+      </c>
+      <c r="AF29">
+        <v>2.6522920000000001</v>
+      </c>
+      <c r="AG29" s="9">
+        <v>-1.6E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>569</v>
+      </c>
+      <c r="C30" t="s">
+        <v>568</v>
+      </c>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30">
+        <v>1.564945</v>
+      </c>
+      <c r="G30">
+        <v>1.899681</v>
+      </c>
+      <c r="H30">
+        <v>2.211646</v>
+      </c>
+      <c r="I30">
+        <v>2.5019809999999998</v>
+      </c>
+      <c r="J30">
+        <v>2.7914560000000002</v>
+      </c>
+      <c r="K30">
+        <v>2.9067609999999999</v>
+      </c>
+      <c r="L30">
+        <v>3.0289009999999998</v>
+      </c>
+      <c r="M30">
+        <v>3.1553260000000001</v>
+      </c>
+      <c r="N30">
+        <v>3.279312</v>
+      </c>
+      <c r="O30">
+        <v>3.349281</v>
+      </c>
+      <c r="P30">
+        <v>3.3885100000000001</v>
+      </c>
+      <c r="Q30">
+        <v>3.3877120000000001</v>
+      </c>
+      <c r="R30">
+        <v>3.389602</v>
+      </c>
+      <c r="S30">
+        <v>3.3914620000000002</v>
+      </c>
+      <c r="T30">
+        <v>3.3933059999999999</v>
+      </c>
+      <c r="U30">
+        <v>3.395105</v>
+      </c>
+      <c r="V30">
+        <v>3.3968569999999998</v>
+      </c>
+      <c r="W30">
+        <v>3.398571</v>
+      </c>
+      <c r="X30">
+        <v>3.4002330000000001</v>
+      </c>
+      <c r="Y30">
+        <v>3.4018389999999998</v>
+      </c>
+      <c r="Z30">
+        <v>3.4034949999999999</v>
+      </c>
+      <c r="AA30">
+        <v>3.405192</v>
+      </c>
+      <c r="AB30">
+        <v>3.40693</v>
+      </c>
+      <c r="AC30">
+        <v>3.4087040000000002</v>
+      </c>
+      <c r="AD30">
+        <v>3.410507</v>
+      </c>
+      <c r="AE30">
+        <v>3.4123410000000001</v>
+      </c>
+      <c r="AF30">
+        <v>3.4142049999999999</v>
+      </c>
+      <c r="AG30" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" t="s">
+        <v>567</v>
+      </c>
+      <c r="C31" t="s">
+        <v>566</v>
+      </c>
+      <c r="D31" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31">
+        <v>134.84877</v>
+      </c>
+      <c r="G31">
+        <v>136.21318099999999</v>
+      </c>
+      <c r="H31">
+        <v>137.661743</v>
+      </c>
+      <c r="I31">
+        <v>139.12712099999999</v>
+      </c>
+      <c r="J31">
+        <v>140.59835799999999</v>
+      </c>
+      <c r="K31">
+        <v>142.107056</v>
+      </c>
+      <c r="L31">
+        <v>143.61586</v>
+      </c>
+      <c r="M31">
+        <v>145.126724</v>
+      </c>
+      <c r="N31">
+        <v>146.62226899999999</v>
+      </c>
+      <c r="O31">
+        <v>148.065079</v>
+      </c>
+      <c r="P31">
+        <v>149.44313</v>
+      </c>
+      <c r="Q31">
+        <v>150.79901100000001</v>
+      </c>
+      <c r="R31">
+        <v>152.12529000000001</v>
+      </c>
+      <c r="S31">
+        <v>153.39515700000001</v>
+      </c>
+      <c r="T31">
+        <v>154.613708</v>
+      </c>
+      <c r="U31">
+        <v>155.77615399999999</v>
+      </c>
+      <c r="V31">
+        <v>156.89575199999999</v>
+      </c>
+      <c r="W31">
+        <v>157.96392800000001</v>
+      </c>
+      <c r="X31">
+        <v>158.99411000000001</v>
+      </c>
+      <c r="Y31">
+        <v>159.98387099999999</v>
+      </c>
+      <c r="Z31">
+        <v>160.95477299999999</v>
+      </c>
+      <c r="AA31">
+        <v>161.92584199999999</v>
+      </c>
+      <c r="AB31">
+        <v>162.893845</v>
+      </c>
+      <c r="AC31">
+        <v>163.86054999999999</v>
+      </c>
+      <c r="AD31">
+        <v>164.825928</v>
+      </c>
+      <c r="AE31">
+        <v>165.79125999999999</v>
+      </c>
+      <c r="AF31">
+        <v>166.753174</v>
+      </c>
+      <c r="AG31" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
+        <v>565</v>
+      </c>
+      <c r="C33" t="s">
+        <v>564</v>
+      </c>
+      <c r="D33" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33">
+        <v>100.278122</v>
+      </c>
+      <c r="G33">
+        <v>101.102592</v>
+      </c>
+      <c r="H33">
+        <v>101.98053</v>
+      </c>
+      <c r="I33">
+        <v>102.86320499999999</v>
+      </c>
+      <c r="J33">
+        <v>103.745369</v>
+      </c>
+      <c r="K33">
+        <v>104.65044399999999</v>
+      </c>
+      <c r="L33">
+        <v>105.550758</v>
+      </c>
+      <c r="M33">
+        <v>106.44516</v>
+      </c>
+      <c r="N33">
+        <v>107.318939</v>
+      </c>
+      <c r="O33">
+        <v>108.14340199999999</v>
+      </c>
+      <c r="P33">
+        <v>108.88472</v>
+      </c>
+      <c r="Q33">
+        <v>109.571144</v>
+      </c>
+      <c r="R33">
+        <v>110.186699</v>
+      </c>
+      <c r="S33">
+        <v>110.704346</v>
+      </c>
+      <c r="T33">
+        <v>111.208107</v>
+      </c>
+      <c r="U33">
+        <v>111.71865099999999</v>
+      </c>
+      <c r="V33">
+        <v>112.249855</v>
+      </c>
+      <c r="W33">
+        <v>112.808708</v>
+      </c>
+      <c r="X33">
+        <v>113.413826</v>
+      </c>
+      <c r="Y33">
+        <v>113.983414</v>
+      </c>
+      <c r="Z33">
+        <v>114.533653</v>
+      </c>
+      <c r="AA33">
+        <v>115.07654599999999</v>
+      </c>
+      <c r="AB33">
+        <v>115.60882599999999</v>
+      </c>
+      <c r="AC33">
+        <v>116.130173</v>
+      </c>
+      <c r="AD33">
+        <v>116.639099</v>
+      </c>
+      <c r="AE33">
+        <v>117.134621</v>
+      </c>
+      <c r="AF33">
+        <v>117.61185500000001</v>
+      </c>
+      <c r="AG33" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" t="s">
+        <v>563</v>
+      </c>
+      <c r="C34" t="s">
+        <v>562</v>
+      </c>
+      <c r="D34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34">
+        <v>53.972369999999998</v>
+      </c>
+      <c r="G34">
+        <v>54.503726999999998</v>
+      </c>
+      <c r="H34">
+        <v>55.061763999999997</v>
+      </c>
+      <c r="I34">
+        <v>55.632815999999998</v>
+      </c>
+      <c r="J34">
+        <v>56.213551000000002</v>
+      </c>
+      <c r="K34">
+        <v>56.809649999999998</v>
+      </c>
+      <c r="L34">
+        <v>57.412582</v>
+      </c>
+      <c r="M34">
+        <v>58.024859999999997</v>
+      </c>
+      <c r="N34">
+        <v>58.644409000000003</v>
+      </c>
+      <c r="O34">
+        <v>59.262939000000003</v>
+      </c>
+      <c r="P34">
+        <v>59.903132999999997</v>
+      </c>
+      <c r="Q34">
+        <v>60.579704</v>
+      </c>
+      <c r="R34">
+        <v>61.301079000000001</v>
+      </c>
+      <c r="S34">
+        <v>62.067855999999999</v>
+      </c>
+      <c r="T34">
+        <v>62.795506000000003</v>
+      </c>
+      <c r="U34">
+        <v>63.458030999999998</v>
+      </c>
+      <c r="V34">
+        <v>64.053505000000001</v>
+      </c>
+      <c r="W34">
+        <v>64.565849</v>
+      </c>
+      <c r="X34">
+        <v>64.989624000000006</v>
+      </c>
+      <c r="Y34">
+        <v>65.410422999999994</v>
+      </c>
+      <c r="Z34">
+        <v>65.833290000000005</v>
+      </c>
+      <c r="AA34">
+        <v>66.264915000000002</v>
+      </c>
+      <c r="AB34">
+        <v>66.705817999999994</v>
+      </c>
+      <c r="AC34">
+        <v>67.157866999999996</v>
+      </c>
+      <c r="AD34">
+        <v>67.622642999999997</v>
+      </c>
+      <c r="AE34">
+        <v>68.102385999999996</v>
+      </c>
+      <c r="AF34">
+        <v>68.598465000000004</v>
+      </c>
+      <c r="AG34" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>561</v>
+      </c>
+      <c r="C35" t="s">
+        <v>560</v>
+      </c>
+      <c r="D35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35">
+        <v>6.2497920000000002</v>
+      </c>
+      <c r="G35">
+        <v>6.2491399999999997</v>
+      </c>
+      <c r="H35">
+        <v>6.2527059999999999</v>
+      </c>
+      <c r="I35">
+        <v>6.2554980000000002</v>
+      </c>
+      <c r="J35">
+        <v>6.2551610000000002</v>
+      </c>
+      <c r="K35">
+        <v>6.2540430000000002</v>
+      </c>
+      <c r="L35">
+        <v>6.2512809999999996</v>
+      </c>
+      <c r="M35">
+        <v>6.2471810000000003</v>
+      </c>
+      <c r="N35">
+        <v>6.2412419999999997</v>
+      </c>
+      <c r="O35">
+        <v>6.2331770000000004</v>
+      </c>
+      <c r="P35">
+        <v>6.2218739999999997</v>
+      </c>
+      <c r="Q35">
+        <v>6.2071079999999998</v>
+      </c>
+      <c r="R35">
+        <v>6.1889000000000003</v>
+      </c>
+      <c r="S35">
+        <v>6.166887</v>
+      </c>
+      <c r="T35">
+        <v>6.1467599999999996</v>
+      </c>
+      <c r="U35">
+        <v>6.1289179999999996</v>
+      </c>
+      <c r="V35">
+        <v>6.1148509999999998</v>
+      </c>
+      <c r="W35">
+        <v>6.1049769999999999</v>
+      </c>
+      <c r="X35">
+        <v>6.099405</v>
+      </c>
+      <c r="Y35">
+        <v>6.0921519999999996</v>
+      </c>
+      <c r="Z35">
+        <v>6.0834679999999999</v>
+      </c>
+      <c r="AA35">
+        <v>6.0735400000000004</v>
+      </c>
+      <c r="AB35">
+        <v>6.0620159999999998</v>
+      </c>
+      <c r="AC35">
+        <v>6.049131</v>
+      </c>
+      <c r="AD35">
+        <v>6.0346979999999997</v>
+      </c>
+      <c r="AE35">
+        <v>6.0188639999999998</v>
+      </c>
+      <c r="AF35">
+        <v>6.0015609999999997</v>
+      </c>
+      <c r="AG35" s="9">
+        <v>-2E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" t="s">
+        <v>559</v>
+      </c>
+      <c r="C36" t="s">
+        <v>558</v>
+      </c>
+      <c r="D36" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36">
+        <v>160.50027499999999</v>
+      </c>
+      <c r="G36">
+        <v>161.855469</v>
+      </c>
+      <c r="H36">
+        <v>163.29499799999999</v>
+      </c>
+      <c r="I36">
+        <v>164.75151099999999</v>
+      </c>
+      <c r="J36">
+        <v>166.21408099999999</v>
+      </c>
+      <c r="K36">
+        <v>167.71414200000001</v>
+      </c>
+      <c r="L36">
+        <v>169.21463</v>
+      </c>
+      <c r="M36">
+        <v>170.71719400000001</v>
+      </c>
+      <c r="N36">
+        <v>172.20459</v>
+      </c>
+      <c r="O36">
+        <v>173.63952599999999</v>
+      </c>
+      <c r="P36">
+        <v>175.00973500000001</v>
+      </c>
+      <c r="Q36">
+        <v>176.357956</v>
+      </c>
+      <c r="R36">
+        <v>177.676682</v>
+      </c>
+      <c r="S36">
+        <v>178.939087</v>
+      </c>
+      <c r="T36">
+        <v>180.150375</v>
+      </c>
+      <c r="U36">
+        <v>181.30560299999999</v>
+      </c>
+      <c r="V36">
+        <v>182.41821300000001</v>
+      </c>
+      <c r="W36">
+        <v>183.47953799999999</v>
+      </c>
+      <c r="X36">
+        <v>184.50285299999999</v>
+      </c>
+      <c r="Y36">
+        <v>185.48597699999999</v>
+      </c>
+      <c r="Z36">
+        <v>186.45040900000001</v>
+      </c>
+      <c r="AA36">
+        <v>187.415009</v>
+      </c>
+      <c r="AB36">
+        <v>188.37664799999999</v>
+      </c>
+      <c r="AC36">
+        <v>189.33717300000001</v>
+      </c>
+      <c r="AD36">
+        <v>190.296448</v>
+      </c>
+      <c r="AE36">
+        <v>191.25585899999999</v>
+      </c>
+      <c r="AF36">
+        <v>192.211884</v>
+      </c>
+      <c r="AG36" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" t="s">
+        <v>557</v>
+      </c>
+      <c r="C38" t="s">
+        <v>556</v>
+      </c>
+      <c r="D38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38">
+        <v>92.221107000000003</v>
+      </c>
+      <c r="G38">
+        <v>94.908974000000001</v>
+      </c>
+      <c r="H38">
+        <v>97.661568000000003</v>
+      </c>
+      <c r="I38">
+        <v>100.444298</v>
+      </c>
+      <c r="J38">
+        <v>103.246483</v>
+      </c>
+      <c r="K38">
+        <v>106.05999</v>
+      </c>
+      <c r="L38">
+        <v>108.873177</v>
+      </c>
+      <c r="M38">
+        <v>111.66229199999999</v>
+      </c>
+      <c r="N38">
+        <v>114.413849</v>
+      </c>
+      <c r="O38">
+        <v>117.12387099999999</v>
+      </c>
+      <c r="P38">
+        <v>119.780914</v>
+      </c>
+      <c r="Q38">
+        <v>122.4272</v>
+      </c>
+      <c r="R38">
+        <v>125.052719</v>
+      </c>
+      <c r="S38">
+        <v>127.63446</v>
+      </c>
+      <c r="T38">
+        <v>130.176163</v>
+      </c>
+      <c r="U38">
+        <v>132.67475899999999</v>
+      </c>
+      <c r="V38">
+        <v>135.14604199999999</v>
+      </c>
+      <c r="W38">
+        <v>137.59196499999999</v>
+      </c>
+      <c r="X38">
+        <v>139.98710600000001</v>
+      </c>
+      <c r="Y38">
+        <v>142.33012400000001</v>
+      </c>
+      <c r="Z38">
+        <v>144.64094499999999</v>
+      </c>
+      <c r="AA38">
+        <v>146.94053600000001</v>
+      </c>
+      <c r="AB38">
+        <v>149.23036200000001</v>
+      </c>
+      <c r="AC38">
+        <v>151.51019299999999</v>
+      </c>
+      <c r="AD38">
+        <v>153.78225699999999</v>
+      </c>
+      <c r="AE38">
+        <v>156.04994199999999</v>
+      </c>
+      <c r="AF38">
+        <v>158.30891399999999</v>
+      </c>
+      <c r="AG38" s="9">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" t="s">
+        <v>555</v>
+      </c>
+      <c r="C39" t="s">
+        <v>554</v>
+      </c>
+      <c r="D39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39">
+        <v>20.353802000000002</v>
+      </c>
+      <c r="G39">
+        <v>20.727464999999999</v>
+      </c>
+      <c r="H39">
+        <v>21.108975999999998</v>
+      </c>
+      <c r="I39">
+        <v>21.498467999999999</v>
+      </c>
+      <c r="J39">
+        <v>21.905369</v>
+      </c>
+      <c r="K39">
+        <v>22.331651999999998</v>
+      </c>
+      <c r="L39">
+        <v>22.776668999999998</v>
+      </c>
+      <c r="M39">
+        <v>23.246670000000002</v>
+      </c>
+      <c r="N39">
+        <v>23.740404000000002</v>
+      </c>
+      <c r="O39">
+        <v>24.225313</v>
+      </c>
+      <c r="P39">
+        <v>24.699818</v>
+      </c>
+      <c r="Q39">
+        <v>25.166246000000001</v>
+      </c>
+      <c r="R39">
+        <v>25.623446000000001</v>
+      </c>
+      <c r="S39">
+        <v>26.068548</v>
+      </c>
+      <c r="T39">
+        <v>26.501984</v>
+      </c>
+      <c r="U39">
+        <v>26.919896999999999</v>
+      </c>
+      <c r="V39">
+        <v>27.319825999999999</v>
+      </c>
+      <c r="W39">
+        <v>27.699757000000002</v>
+      </c>
+      <c r="X39">
+        <v>28.090371999999999</v>
+      </c>
+      <c r="Y39">
+        <v>28.489045999999998</v>
+      </c>
+      <c r="Z39">
+        <v>28.897078</v>
+      </c>
+      <c r="AA39">
+        <v>29.315380000000001</v>
+      </c>
+      <c r="AB39">
+        <v>29.741956999999999</v>
+      </c>
+      <c r="AC39">
+        <v>30.175975999999999</v>
+      </c>
+      <c r="AD39">
+        <v>30.615866</v>
+      </c>
+      <c r="AE39">
+        <v>31.060276000000002</v>
+      </c>
+      <c r="AF39">
+        <v>31.508205</v>
+      </c>
+      <c r="AG39" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
+        <v>553</v>
+      </c>
+      <c r="C40" t="s">
+        <v>552</v>
+      </c>
+      <c r="D40" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40">
+        <v>112.574905</v>
+      </c>
+      <c r="G40">
+        <v>115.636436</v>
+      </c>
+      <c r="H40">
+        <v>118.770546</v>
+      </c>
+      <c r="I40">
+        <v>121.942764</v>
+      </c>
+      <c r="J40">
+        <v>125.151855</v>
+      </c>
+      <c r="K40">
+        <v>128.39164700000001</v>
+      </c>
+      <c r="L40">
+        <v>131.64984100000001</v>
+      </c>
+      <c r="M40">
+        <v>134.90896599999999</v>
+      </c>
+      <c r="N40">
+        <v>138.15425099999999</v>
+      </c>
+      <c r="O40">
+        <v>141.34918200000001</v>
+      </c>
+      <c r="P40">
+        <v>144.480728</v>
+      </c>
+      <c r="Q40">
+        <v>147.593445</v>
+      </c>
+      <c r="R40">
+        <v>150.676163</v>
+      </c>
+      <c r="S40">
+        <v>153.703003</v>
+      </c>
+      <c r="T40">
+        <v>156.678146</v>
+      </c>
+      <c r="U40">
+        <v>159.59465</v>
+      </c>
+      <c r="V40">
+        <v>162.46586600000001</v>
+      </c>
+      <c r="W40">
+        <v>165.291718</v>
+      </c>
+      <c r="X40">
+        <v>168.077484</v>
+      </c>
+      <c r="Y40">
+        <v>170.81916799999999</v>
+      </c>
+      <c r="Z40">
+        <v>173.538025</v>
+      </c>
+      <c r="AA40">
+        <v>176.25592</v>
+      </c>
+      <c r="AB40">
+        <v>178.97232099999999</v>
+      </c>
+      <c r="AC40">
+        <v>181.686172</v>
+      </c>
+      <c r="AD40">
+        <v>184.39811700000001</v>
+      </c>
+      <c r="AE40">
+        <v>187.11021400000001</v>
+      </c>
+      <c r="AF40">
+        <v>189.81712300000001</v>
+      </c>
+      <c r="AG40" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" t="s">
+        <v>551</v>
+      </c>
+      <c r="C42" t="s">
+        <v>550</v>
+      </c>
+      <c r="D42" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42">
+        <v>185.51213100000001</v>
+      </c>
+      <c r="G42">
+        <v>187.57015999999999</v>
+      </c>
+      <c r="H42">
+        <v>189.72297699999999</v>
+      </c>
+      <c r="I42">
+        <v>191.892639</v>
+      </c>
+      <c r="J42">
+        <v>194.05687</v>
+      </c>
+      <c r="K42">
+        <v>196.26173399999999</v>
+      </c>
+      <c r="L42">
+        <v>198.461578</v>
+      </c>
+      <c r="M42">
+        <v>200.66261299999999</v>
+      </c>
+      <c r="N42">
+        <v>202.84565699999999</v>
+      </c>
+      <c r="O42">
+        <v>204.960297</v>
+      </c>
+      <c r="P42">
+        <v>206.98817399999999</v>
+      </c>
+      <c r="Q42">
+        <v>208.988495</v>
+      </c>
+      <c r="R42">
+        <v>210.94859299999999</v>
+      </c>
+      <c r="S42">
+        <v>212.83372499999999</v>
+      </c>
+      <c r="T42">
+        <v>214.64849899999999</v>
+      </c>
+      <c r="U42">
+        <v>216.38301100000001</v>
+      </c>
+      <c r="V42">
+        <v>218.05542</v>
+      </c>
+      <c r="W42">
+        <v>219.65475499999999</v>
+      </c>
+      <c r="X42">
+        <v>221.20091199999999</v>
+      </c>
+      <c r="Y42">
+        <v>222.68464700000001</v>
+      </c>
+      <c r="Z42">
+        <v>224.13630699999999</v>
+      </c>
+      <c r="AA42">
+        <v>225.58776900000001</v>
+      </c>
+      <c r="AB42">
+        <v>227.03428600000001</v>
+      </c>
+      <c r="AC42">
+        <v>228.47901899999999</v>
+      </c>
+      <c r="AD42">
+        <v>229.92160000000001</v>
+      </c>
+      <c r="AE42">
+        <v>231.36346399999999</v>
+      </c>
+      <c r="AF42">
+        <v>232.79994199999999</v>
+      </c>
+      <c r="AG42" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>549</v>
+      </c>
+      <c r="C43" t="s">
+        <v>548</v>
+      </c>
+      <c r="D43" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43">
+        <v>48.421523999999998</v>
+      </c>
+      <c r="G43">
+        <v>48.897556000000002</v>
+      </c>
+      <c r="H43">
+        <v>49.389957000000003</v>
+      </c>
+      <c r="I43">
+        <v>49.883246999999997</v>
+      </c>
+      <c r="J43">
+        <v>50.367457999999999</v>
+      </c>
+      <c r="K43">
+        <v>50.854793999999998</v>
+      </c>
+      <c r="L43">
+        <v>51.338000999999998</v>
+      </c>
+      <c r="M43">
+        <v>51.821067999999997</v>
+      </c>
+      <c r="N43">
+        <v>52.302494000000003</v>
+      </c>
+      <c r="O43">
+        <v>52.772449000000002</v>
+      </c>
+      <c r="P43">
+        <v>53.225802999999999</v>
+      </c>
+      <c r="Q43">
+        <v>53.674511000000003</v>
+      </c>
+      <c r="R43">
+        <v>54.115622999999999</v>
+      </c>
+      <c r="S43">
+        <v>54.542957000000001</v>
+      </c>
+      <c r="T43">
+        <v>54.956287000000003</v>
+      </c>
+      <c r="U43">
+        <v>55.352367000000001</v>
+      </c>
+      <c r="V43">
+        <v>55.735515999999997</v>
+      </c>
+      <c r="W43">
+        <v>56.103614999999998</v>
+      </c>
+      <c r="X43">
+        <v>56.460856999999997</v>
+      </c>
+      <c r="Y43">
+        <v>56.802979000000001</v>
+      </c>
+      <c r="Z43">
+        <v>57.136333</v>
+      </c>
+      <c r="AA43">
+        <v>57.469645999999997</v>
+      </c>
+      <c r="AB43">
+        <v>57.801506000000003</v>
+      </c>
+      <c r="AC43">
+        <v>58.133105999999998</v>
+      </c>
+      <c r="AD43">
+        <v>58.464126999999998</v>
+      </c>
+      <c r="AE43">
+        <v>58.794894999999997</v>
+      </c>
+      <c r="AF43">
+        <v>59.124156999999997</v>
+      </c>
+      <c r="AG43" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" t="s">
+        <v>547</v>
+      </c>
+      <c r="C46" t="s">
+        <v>546</v>
+      </c>
+      <c r="D46" t="s">
+        <v>63</v>
+      </c>
+      <c r="F46">
+        <v>8.3015749999999997</v>
+      </c>
+      <c r="G46">
+        <v>8.4117829999999998</v>
+      </c>
+      <c r="H46">
+        <v>8.5242609999999992</v>
+      </c>
+      <c r="I46">
+        <v>8.6396730000000002</v>
+      </c>
+      <c r="J46">
+        <v>8.7591149999999995</v>
+      </c>
+      <c r="K46">
+        <v>8.8707279999999997</v>
+      </c>
+      <c r="L46">
+        <v>8.974126</v>
+      </c>
+      <c r="M46">
+        <v>9.0690150000000003</v>
+      </c>
+      <c r="N46">
+        <v>9.1557250000000003</v>
+      </c>
+      <c r="O46">
+        <v>9.2265060000000005</v>
+      </c>
+      <c r="P46">
+        <v>9.2895909999999997</v>
+      </c>
+      <c r="Q46">
+        <v>9.3448089999999997</v>
+      </c>
+      <c r="R46">
+        <v>9.3924570000000003</v>
+      </c>
+      <c r="S46">
+        <v>9.4328009999999995</v>
+      </c>
+      <c r="T46">
+        <v>9.4657739999999997</v>
+      </c>
+      <c r="U46">
+        <v>9.4915289999999999</v>
+      </c>
+      <c r="V46">
+        <v>9.5116619999999994</v>
+      </c>
+      <c r="W46">
+        <v>9.5233550000000005</v>
+      </c>
+      <c r="X46">
+        <v>9.5257579999999997</v>
+      </c>
+      <c r="Y46">
+        <v>9.5284410000000008</v>
+      </c>
+      <c r="Z46">
+        <v>9.5312710000000003</v>
+      </c>
+      <c r="AA46">
+        <v>9.5340980000000002</v>
+      </c>
+      <c r="AB46">
+        <v>9.5369150000000005</v>
+      </c>
+      <c r="AC46">
+        <v>9.5396990000000006</v>
+      </c>
+      <c r="AD46">
+        <v>9.5424229999999994</v>
+      </c>
+      <c r="AE46">
+        <v>9.5450660000000003</v>
+      </c>
+      <c r="AF46">
+        <v>9.5476329999999994</v>
+      </c>
+      <c r="AG46" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" t="s">
+        <v>545</v>
+      </c>
+      <c r="C47" t="s">
+        <v>544</v>
+      </c>
+      <c r="D47" t="s">
+        <v>65</v>
+      </c>
+      <c r="F47">
+        <v>1.3</v>
+      </c>
+      <c r="G47">
+        <v>1.3</v>
+      </c>
+      <c r="H47">
+        <v>1.3</v>
+      </c>
+      <c r="I47">
+        <v>1.3</v>
+      </c>
+      <c r="J47">
+        <v>1.3</v>
+      </c>
+      <c r="K47">
+        <v>1.3</v>
+      </c>
+      <c r="L47">
+        <v>1.3</v>
+      </c>
+      <c r="M47">
+        <v>1.3</v>
+      </c>
+      <c r="N47">
+        <v>1.3</v>
+      </c>
+      <c r="O47">
+        <v>1.3</v>
+      </c>
+      <c r="P47">
+        <v>1.3</v>
+      </c>
+      <c r="Q47">
+        <v>1.3</v>
+      </c>
+      <c r="R47">
+        <v>1.3</v>
+      </c>
+      <c r="S47">
+        <v>1.3</v>
+      </c>
+      <c r="T47">
+        <v>1.3</v>
+      </c>
+      <c r="U47">
+        <v>1.3</v>
+      </c>
+      <c r="V47">
+        <v>1.3</v>
+      </c>
+      <c r="W47">
+        <v>1.3</v>
+      </c>
+      <c r="X47">
+        <v>1.3</v>
+      </c>
+      <c r="Y47">
+        <v>1.3</v>
+      </c>
+      <c r="Z47">
+        <v>1.3</v>
+      </c>
+      <c r="AA47">
+        <v>1.3</v>
+      </c>
+      <c r="AB47">
+        <v>1.3</v>
+      </c>
+      <c r="AC47">
+        <v>1.3</v>
+      </c>
+      <c r="AD47">
+        <v>1.3</v>
+      </c>
+      <c r="AE47">
+        <v>1.3</v>
+      </c>
+      <c r="AF47">
+        <v>1.3</v>
+      </c>
+      <c r="AG47" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" t="s">
+        <v>543</v>
+      </c>
+      <c r="C48" t="s">
+        <v>542</v>
+      </c>
+      <c r="D48" t="s">
+        <v>67</v>
+      </c>
+      <c r="F48">
+        <v>3.1980179999999998</v>
+      </c>
+      <c r="G48">
+        <v>3.2298360000000002</v>
+      </c>
+      <c r="H48">
+        <v>3.2606570000000001</v>
+      </c>
+      <c r="I48">
+        <v>3.2903829999999998</v>
+      </c>
+      <c r="J48">
+        <v>3.3189289999999998</v>
+      </c>
+      <c r="K48">
+        <v>3.3464049999999999</v>
+      </c>
+      <c r="L48">
+        <v>3.3728039999999999</v>
+      </c>
+      <c r="M48">
+        <v>3.3982709999999998</v>
+      </c>
+      <c r="N48">
+        <v>3.4217919999999999</v>
+      </c>
+      <c r="O48">
+        <v>3.4418000000000002</v>
+      </c>
+      <c r="P48">
+        <v>3.4592320000000001</v>
+      </c>
+      <c r="Q48">
+        <v>3.469077</v>
+      </c>
+      <c r="R48">
+        <v>3.477528</v>
+      </c>
+      <c r="S48">
+        <v>3.485055</v>
+      </c>
+      <c r="T48">
+        <v>3.4917150000000001</v>
+      </c>
+      <c r="U48">
+        <v>3.4976020000000001</v>
+      </c>
+      <c r="V48">
+        <v>3.5028269999999999</v>
+      </c>
+      <c r="W48">
+        <v>3.5072960000000002</v>
+      </c>
+      <c r="X48">
+        <v>3.5110809999999999</v>
+      </c>
+      <c r="Y48">
+        <v>3.5141840000000002</v>
+      </c>
+      <c r="Z48">
+        <v>3.5166650000000002</v>
+      </c>
+      <c r="AA48">
+        <v>3.5184199999999999</v>
+      </c>
+      <c r="AB48">
+        <v>3.5196239999999999</v>
+      </c>
+      <c r="AC48">
+        <v>3.5202610000000001</v>
+      </c>
+      <c r="AD48">
+        <v>3.5203120000000001</v>
+      </c>
+      <c r="AE48">
+        <v>3.5199310000000001</v>
+      </c>
+      <c r="AF48">
+        <v>3.519072</v>
+      </c>
+      <c r="AG48" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B49" t="s">
+        <v>541</v>
+      </c>
+      <c r="C49" t="s">
+        <v>540</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49">
+        <v>0.81869000000000003</v>
+      </c>
+      <c r="G49">
+        <v>0.82376499999999997</v>
+      </c>
+      <c r="H49">
+        <v>0.82883799999999996</v>
+      </c>
+      <c r="I49">
+        <v>0.83387900000000004</v>
+      </c>
+      <c r="J49">
+        <v>0.83890600000000004</v>
+      </c>
+      <c r="K49">
+        <v>0.84789700000000001</v>
+      </c>
+      <c r="L49">
+        <v>0.85755800000000004</v>
+      </c>
+      <c r="M49">
+        <v>0.86722600000000005</v>
+      </c>
+      <c r="N49">
+        <v>0.87631700000000001</v>
+      </c>
+      <c r="O49">
+        <v>0.88464299999999996</v>
+      </c>
+      <c r="P49">
+        <v>0.89239999999999997</v>
+      </c>
+      <c r="Q49">
+        <v>0.89957799999999999</v>
+      </c>
+      <c r="R49">
+        <v>0.90626099999999998</v>
+      </c>
+      <c r="S49">
+        <v>0.91242199999999996</v>
+      </c>
+      <c r="T49">
+        <v>0.91810099999999994</v>
+      </c>
+      <c r="U49">
+        <v>0.92328900000000003</v>
+      </c>
+      <c r="V49">
+        <v>0.92801299999999998</v>
+      </c>
+      <c r="W49">
+        <v>0.93226600000000004</v>
+      </c>
+      <c r="X49">
+        <v>0.93608599999999997</v>
+      </c>
+      <c r="Y49">
+        <v>0.939438</v>
+      </c>
+      <c r="Z49">
+        <v>0.94230899999999995</v>
+      </c>
+      <c r="AA49">
+        <v>0.944658</v>
+      </c>
+      <c r="AB49">
+        <v>0.94646699999999995</v>
+      </c>
+      <c r="AC49">
+        <v>0.948268</v>
+      </c>
+      <c r="AD49">
+        <v>0.95002399999999998</v>
+      </c>
+      <c r="AE49">
+        <v>0.95170399999999999</v>
+      </c>
+      <c r="AF49">
+        <v>0.95327700000000004</v>
+      </c>
+      <c r="AG49" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" t="s">
+        <v>539</v>
+      </c>
+      <c r="C50" t="s">
+        <v>538</v>
+      </c>
+      <c r="D50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50">
+        <v>0.83582100000000004</v>
+      </c>
+      <c r="G50">
+        <v>0.83736999999999995</v>
+      </c>
+      <c r="H50">
+        <v>0.83893399999999996</v>
+      </c>
+      <c r="I50">
+        <v>0.84047899999999998</v>
+      </c>
+      <c r="J50">
+        <v>0.84198799999999996</v>
+      </c>
+      <c r="K50">
+        <v>0.84346500000000002</v>
+      </c>
+      <c r="L50">
+        <v>0.84493399999999996</v>
+      </c>
+      <c r="M50">
+        <v>0.84641200000000005</v>
+      </c>
+      <c r="N50">
+        <v>0.84782100000000005</v>
+      </c>
+      <c r="O50">
+        <v>0.84907299999999997</v>
+      </c>
+      <c r="P50">
+        <v>0.85023499999999996</v>
+      </c>
+      <c r="Q50">
+        <v>0.85128599999999999</v>
+      </c>
+      <c r="R50">
+        <v>0.85225200000000001</v>
+      </c>
+      <c r="S50">
+        <v>0.85311000000000003</v>
+      </c>
+      <c r="T50">
+        <v>0.85387800000000003</v>
+      </c>
+      <c r="U50">
+        <v>0.85455499999999995</v>
+      </c>
+      <c r="V50">
+        <v>0.85513799999999995</v>
+      </c>
+      <c r="W50">
+        <v>0.85562499999999997</v>
+      </c>
+      <c r="X50">
+        <v>0.85601799999999995</v>
+      </c>
+      <c r="Y50">
+        <v>0.85631400000000002</v>
+      </c>
+      <c r="Z50">
+        <v>0.85650599999999999</v>
+      </c>
+      <c r="AA50">
+        <v>0.85658599999999996</v>
+      </c>
+      <c r="AB50">
+        <v>0.856572</v>
+      </c>
+      <c r="AC50">
+        <v>0.85655800000000004</v>
+      </c>
+      <c r="AD50">
+        <v>0.856545</v>
+      </c>
+      <c r="AE50">
+        <v>0.85653199999999996</v>
+      </c>
+      <c r="AF50">
+        <v>0.85651900000000003</v>
+      </c>
+      <c r="AG50" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" t="s">
+        <v>537</v>
+      </c>
+      <c r="C52" t="s">
+        <v>536</v>
+      </c>
+      <c r="D52" t="s">
+        <v>73</v>
+      </c>
+      <c r="F52">
+        <v>13.990335</v>
+      </c>
+      <c r="G52">
+        <v>14.225822000000001</v>
+      </c>
+      <c r="H52">
+        <v>14.465521000000001</v>
+      </c>
+      <c r="I52">
+        <v>14.710986</v>
+      </c>
+      <c r="J52">
+        <v>14.964726000000001</v>
+      </c>
+      <c r="K52">
+        <v>15.201395</v>
+      </c>
+      <c r="L52">
+        <v>15.42023</v>
+      </c>
+      <c r="M52">
+        <v>15.620710000000001</v>
+      </c>
+      <c r="N52">
+        <v>15.803606</v>
+      </c>
+      <c r="O52">
+        <v>15.951933</v>
+      </c>
+      <c r="P52">
+        <v>16.083611999999999</v>
+      </c>
+      <c r="Q52">
+        <v>16.198575999999999</v>
+      </c>
+      <c r="R52">
+        <v>16.297474000000001</v>
+      </c>
+      <c r="S52">
+        <v>16.380913</v>
+      </c>
+      <c r="T52">
+        <v>16.448741999999999</v>
+      </c>
+      <c r="U52">
+        <v>16.501339000000002</v>
+      </c>
+      <c r="V52">
+        <v>16.546972</v>
+      </c>
+      <c r="W52">
+        <v>16.574265</v>
+      </c>
+      <c r="X52">
+        <v>16.581530000000001</v>
+      </c>
+      <c r="Y52">
+        <v>16.589703</v>
+      </c>
+      <c r="Z52">
+        <v>16.598382999999998</v>
+      </c>
+      <c r="AA52">
+        <v>16.607206000000001</v>
+      </c>
+      <c r="AB52">
+        <v>16.616085000000002</v>
+      </c>
+      <c r="AC52">
+        <v>16.624941</v>
+      </c>
+      <c r="AD52">
+        <v>16.633641999999998</v>
+      </c>
+      <c r="AE52">
+        <v>16.642115</v>
+      </c>
+      <c r="AF52">
+        <v>16.650321999999999</v>
+      </c>
+      <c r="AG52" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" t="s">
+        <v>535</v>
+      </c>
+      <c r="C53" t="s">
+        <v>534</v>
+      </c>
+      <c r="D53" t="s">
+        <v>65</v>
+      </c>
+      <c r="F53">
+        <v>0.62333899999999998</v>
+      </c>
+      <c r="G53">
+        <v>0.62898399999999999</v>
+      </c>
+      <c r="H53">
+        <v>0.63492199999999999</v>
+      </c>
+      <c r="I53">
+        <v>0.64126799999999995</v>
+      </c>
+      <c r="J53">
+        <v>0.64812000000000003</v>
+      </c>
+      <c r="K53">
+        <v>0.65468099999999996</v>
+      </c>
+      <c r="L53">
+        <v>0.66091200000000005</v>
+      </c>
+      <c r="M53">
+        <v>0.66676400000000002</v>
+      </c>
+      <c r="N53">
+        <v>0.672238</v>
+      </c>
+      <c r="O53">
+        <v>0.677284</v>
+      </c>
+      <c r="P53">
+        <v>0.68191199999999996</v>
+      </c>
+      <c r="Q53">
+        <v>0.68607399999999996</v>
+      </c>
+      <c r="R53">
+        <v>0.68975900000000001</v>
+      </c>
+      <c r="S53">
+        <v>0.69294900000000004</v>
+      </c>
+      <c r="T53">
+        <v>0.695604</v>
+      </c>
+      <c r="U53">
+        <v>0.69770399999999999</v>
+      </c>
+      <c r="V53">
+        <v>0.69920199999999999</v>
+      </c>
+      <c r="W53">
+        <v>0.7</v>
+      </c>
+      <c r="X53">
+        <v>0.7</v>
+      </c>
+      <c r="Y53">
+        <v>0.7</v>
+      </c>
+      <c r="Z53">
+        <v>0.7</v>
+      </c>
+      <c r="AA53">
+        <v>0.7</v>
+      </c>
+      <c r="AB53">
+        <v>0.7</v>
+      </c>
+      <c r="AC53">
+        <v>0.7</v>
+      </c>
+      <c r="AD53">
+        <v>0.7</v>
+      </c>
+      <c r="AE53">
+        <v>0.7</v>
+      </c>
+      <c r="AF53">
+        <v>0.7</v>
+      </c>
+      <c r="AG53" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" t="s">
+        <v>533</v>
+      </c>
+      <c r="C54" t="s">
+        <v>532</v>
+      </c>
+      <c r="D54" t="s">
+        <v>75</v>
+      </c>
+      <c r="F54">
+        <v>13.993668</v>
+      </c>
+      <c r="G54">
+        <v>14.221729</v>
+      </c>
+      <c r="H54">
+        <v>14.442513999999999</v>
+      </c>
+      <c r="I54">
+        <v>14.655156</v>
+      </c>
+      <c r="J54">
+        <v>14.858943</v>
+      </c>
+      <c r="K54">
+        <v>15.054792000000001</v>
+      </c>
+      <c r="L54">
+        <v>15.242620000000001</v>
+      </c>
+      <c r="M54">
+        <v>15.423491</v>
+      </c>
+      <c r="N54">
+        <v>15.590322</v>
+      </c>
+      <c r="O54">
+        <v>15.732929</v>
+      </c>
+      <c r="P54">
+        <v>15.857524</v>
+      </c>
+      <c r="Q54">
+        <v>15.92991</v>
+      </c>
+      <c r="R54">
+        <v>15.991645999999999</v>
+      </c>
+      <c r="S54">
+        <v>16.046742999999999</v>
+      </c>
+      <c r="T54">
+        <v>16.095617000000001</v>
+      </c>
+      <c r="U54">
+        <v>16.138884999999998</v>
+      </c>
+      <c r="V54">
+        <v>16.177298</v>
+      </c>
+      <c r="W54">
+        <v>16.210196</v>
+      </c>
+      <c r="X54">
+        <v>16.238112999999998</v>
+      </c>
+      <c r="Y54">
+        <v>16.261043999999998</v>
+      </c>
+      <c r="Z54">
+        <v>16.279423000000001</v>
+      </c>
+      <c r="AA54">
+        <v>16.292555</v>
+      </c>
+      <c r="AB54">
+        <v>16.301682</v>
+      </c>
+      <c r="AC54">
+        <v>16.306694</v>
+      </c>
+      <c r="AD54">
+        <v>16.307490999999999</v>
+      </c>
+      <c r="AE54">
+        <v>16.305126000000001</v>
+      </c>
+      <c r="AF54">
+        <v>16.299299000000001</v>
+      </c>
+      <c r="AG54" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" t="s">
+        <v>531</v>
+      </c>
+      <c r="C55" t="s">
+        <v>530</v>
+      </c>
+      <c r="D55" t="s">
+        <v>73</v>
+      </c>
+      <c r="F55">
+        <v>13.469367999999999</v>
+      </c>
+      <c r="G55">
+        <v>13.760479999999999</v>
+      </c>
+      <c r="H55">
+        <v>14.051945</v>
+      </c>
+      <c r="I55">
+        <v>14.34586</v>
+      </c>
+      <c r="J55">
+        <v>14.645688</v>
+      </c>
+      <c r="K55">
+        <v>14.925357</v>
+      </c>
+      <c r="L55">
+        <v>15.18473</v>
+      </c>
+      <c r="M55">
+        <v>15.422160999999999</v>
+      </c>
+      <c r="N55">
+        <v>15.637525</v>
+      </c>
+      <c r="O55">
+        <v>15.709616</v>
+      </c>
+      <c r="P55">
+        <v>15.752591000000001</v>
+      </c>
+      <c r="Q55">
+        <v>15.78285</v>
+      </c>
+      <c r="R55">
+        <v>15.799917000000001</v>
+      </c>
+      <c r="S55">
+        <v>15.80462</v>
+      </c>
+      <c r="T55">
+        <v>15.79846</v>
+      </c>
+      <c r="U55">
+        <v>15.781046</v>
+      </c>
+      <c r="V55">
+        <v>15.753360000000001</v>
+      </c>
+      <c r="W55">
+        <v>15.715132000000001</v>
+      </c>
+      <c r="X55">
+        <v>15.665411000000001</v>
+      </c>
+      <c r="Y55">
+        <v>15.616528000000001</v>
+      </c>
+      <c r="Z55">
+        <v>15.568357000000001</v>
+      </c>
+      <c r="AA55">
+        <v>15.521165999999999</v>
+      </c>
+      <c r="AB55">
+        <v>15.475282</v>
+      </c>
+      <c r="AC55">
+        <v>15.430944999999999</v>
+      </c>
+      <c r="AD55">
+        <v>15.388375999999999</v>
+      </c>
+      <c r="AE55">
+        <v>15.347758000000001</v>
+      </c>
+      <c r="AF55">
+        <v>15.309222</v>
+      </c>
+      <c r="AG55" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" t="s">
+        <v>529</v>
+      </c>
+      <c r="C56" t="s">
+        <v>528</v>
+      </c>
+      <c r="D56" t="s">
+        <v>75</v>
+      </c>
+      <c r="F56">
+        <v>11.448732</v>
+      </c>
+      <c r="G56">
+        <v>11.644736999999999</v>
+      </c>
+      <c r="H56">
+        <v>11.847325</v>
+      </c>
+      <c r="I56">
+        <v>12.298437</v>
+      </c>
+      <c r="J56">
+        <v>12.757018</v>
+      </c>
+      <c r="K56">
+        <v>13.272966</v>
+      </c>
+      <c r="L56">
+        <v>13.771557</v>
+      </c>
+      <c r="M56">
+        <v>14.233993999999999</v>
+      </c>
+      <c r="N56">
+        <v>14.651569</v>
+      </c>
+      <c r="O56">
+        <v>15.024331999999999</v>
+      </c>
+      <c r="P56">
+        <v>15.341799</v>
+      </c>
+      <c r="Q56">
+        <v>15.580716000000001</v>
+      </c>
+      <c r="R56">
+        <v>15.738295000000001</v>
+      </c>
+      <c r="S56">
+        <v>15.813057000000001</v>
+      </c>
+      <c r="T56">
+        <v>15.872056000000001</v>
+      </c>
+      <c r="U56">
+        <v>15.916221999999999</v>
+      </c>
+      <c r="V56">
+        <v>15.947607</v>
+      </c>
+      <c r="W56">
+        <v>15.968753</v>
+      </c>
+      <c r="X56">
+        <v>15.982252000000001</v>
+      </c>
+      <c r="Y56">
+        <v>15.990417000000001</v>
+      </c>
+      <c r="Z56">
+        <v>15.995094999999999</v>
+      </c>
+      <c r="AA56">
+        <v>15.997622</v>
+      </c>
+      <c r="AB56">
+        <v>15.998911</v>
+      </c>
+      <c r="AC56">
+        <v>15.999532</v>
+      </c>
+      <c r="AD56">
+        <v>15.999801</v>
+      </c>
+      <c r="AE56">
+        <v>15.999924</v>
+      </c>
+      <c r="AF56">
+        <v>15.999976</v>
+      </c>
+      <c r="AG56" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58" t="s">
+        <v>527</v>
+      </c>
+      <c r="C58" t="s">
+        <v>526</v>
+      </c>
+      <c r="D58" t="s">
+        <v>80</v>
+      </c>
+      <c r="F58">
+        <v>1.089594</v>
+      </c>
+      <c r="G58">
+        <v>1.1425160000000001</v>
+      </c>
+      <c r="H58">
+        <v>1.194647</v>
+      </c>
+      <c r="I58">
+        <v>1.2457849999999999</v>
+      </c>
+      <c r="J58">
+        <v>1.296718</v>
+      </c>
+      <c r="K58">
+        <v>1.427567</v>
+      </c>
+      <c r="L58">
+        <v>1.530845</v>
+      </c>
+      <c r="M58">
+        <v>1.6406940000000001</v>
+      </c>
+      <c r="N58">
+        <v>1.7447140000000001</v>
+      </c>
+      <c r="O58">
+        <v>1.833205</v>
+      </c>
+      <c r="P58">
+        <v>1.91778</v>
+      </c>
+      <c r="Q58">
+        <v>1.995061</v>
+      </c>
+      <c r="R58">
+        <v>2.064635</v>
+      </c>
+      <c r="S58">
+        <v>2.1261709999999998</v>
+      </c>
+      <c r="T58">
+        <v>2.179694</v>
+      </c>
+      <c r="U58">
+        <v>2.225028</v>
+      </c>
+      <c r="V58">
+        <v>2.2624460000000002</v>
+      </c>
+      <c r="W58">
+        <v>2.291731</v>
+      </c>
+      <c r="X58">
+        <v>2.3127049999999998</v>
+      </c>
+      <c r="Y58">
+        <v>2.3256410000000001</v>
+      </c>
+      <c r="Z58">
+        <v>2.3376600000000001</v>
+      </c>
+      <c r="AA58">
+        <v>2.3487290000000001</v>
+      </c>
+      <c r="AB58">
+        <v>2.3588469999999999</v>
+      </c>
+      <c r="AC58">
+        <v>2.3680279999999998</v>
+      </c>
+      <c r="AD58">
+        <v>2.3763190000000001</v>
+      </c>
+      <c r="AE58">
+        <v>2.3837579999999998</v>
+      </c>
+      <c r="AF58">
+        <v>2.3903810000000001</v>
+      </c>
+      <c r="AG58" s="9">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>81</v>
+      </c>
+      <c r="B59" t="s">
+        <v>525</v>
+      </c>
+      <c r="C59" t="s">
+        <v>524</v>
+      </c>
+      <c r="D59" t="s">
+        <v>80</v>
+      </c>
+      <c r="F59">
+        <v>0.60598600000000002</v>
+      </c>
+      <c r="G59">
+        <v>0.61377400000000004</v>
+      </c>
+      <c r="H59">
+        <v>0.62073199999999995</v>
+      </c>
+      <c r="I59">
+        <v>0.62687899999999996</v>
+      </c>
+      <c r="J59">
+        <v>0.63224800000000003</v>
+      </c>
+      <c r="K59">
+        <v>0.64028099999999999</v>
+      </c>
+      <c r="L59">
+        <v>0.64717400000000003</v>
+      </c>
+      <c r="M59">
+        <v>0.653142</v>
+      </c>
+      <c r="N59">
+        <v>0.65814099999999998</v>
+      </c>
+      <c r="O59">
+        <v>0.66080300000000003</v>
+      </c>
+      <c r="P59">
+        <v>0.66259400000000002</v>
+      </c>
+      <c r="Q59">
+        <v>0.66352299999999997</v>
+      </c>
+      <c r="R59">
+        <v>0.66439199999999998</v>
+      </c>
+      <c r="S59">
+        <v>0.66519700000000004</v>
+      </c>
+      <c r="T59">
+        <v>0.66593599999999997</v>
+      </c>
+      <c r="U59">
+        <v>0.66660900000000001</v>
+      </c>
+      <c r="V59">
+        <v>0.66721600000000003</v>
+      </c>
+      <c r="W59">
+        <v>0.66775799999999996</v>
+      </c>
+      <c r="X59">
+        <v>0.668238</v>
+      </c>
+      <c r="Y59">
+        <v>0.66866000000000003</v>
+      </c>
+      <c r="Z59">
+        <v>0.66902799999999996</v>
+      </c>
+      <c r="AA59">
+        <v>0.669346</v>
+      </c>
+      <c r="AB59">
+        <v>0.66961800000000005</v>
+      </c>
+      <c r="AC59">
+        <v>0.66984900000000003</v>
+      </c>
+      <c r="AD59">
+        <v>0.67004300000000006</v>
+      </c>
+      <c r="AE59">
+        <v>0.67020400000000002</v>
+      </c>
+      <c r="AF59">
+        <v>0.67033699999999996</v>
+      </c>
+      <c r="AG59" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" t="s">
+        <v>523</v>
+      </c>
+      <c r="C60" t="s">
+        <v>522</v>
+      </c>
+      <c r="D60" t="s">
+        <v>80</v>
+      </c>
+      <c r="F60">
+        <v>0.54769800000000002</v>
+      </c>
+      <c r="G60">
+        <v>0.55999399999999999</v>
+      </c>
+      <c r="H60">
+        <v>0.57217899999999999</v>
+      </c>
+      <c r="I60">
+        <v>0.58399400000000001</v>
+      </c>
+      <c r="J60">
+        <v>0.59521000000000002</v>
+      </c>
+      <c r="K60">
+        <v>0.60663999999999996</v>
+      </c>
+      <c r="L60">
+        <v>0.61675899999999995</v>
+      </c>
+      <c r="M60">
+        <v>0.625502</v>
+      </c>
+      <c r="N60">
+        <v>0.63254699999999997</v>
+      </c>
+      <c r="O60">
+        <v>0.63764500000000002</v>
+      </c>
+      <c r="P60">
+        <v>0.640544</v>
+      </c>
+      <c r="Q60">
+        <v>0.64108200000000004</v>
+      </c>
+      <c r="R60">
+        <v>0.64163400000000004</v>
+      </c>
+      <c r="S60">
+        <v>0.64219300000000001</v>
+      </c>
+      <c r="T60">
+        <v>0.64275400000000005</v>
+      </c>
+      <c r="U60">
+        <v>0.64331199999999999</v>
+      </c>
+      <c r="V60">
+        <v>0.64386200000000005</v>
+      </c>
+      <c r="W60">
+        <v>0.644401</v>
+      </c>
+      <c r="X60">
+        <v>0.64492499999999997</v>
+      </c>
+      <c r="Y60">
+        <v>0.64542999999999995</v>
+      </c>
+      <c r="Z60">
+        <v>0.64591299999999996</v>
+      </c>
+      <c r="AA60">
+        <v>0.646374</v>
+      </c>
+      <c r="AB60">
+        <v>0.64680899999999997</v>
+      </c>
+      <c r="AC60">
+        <v>0.64721899999999999</v>
+      </c>
+      <c r="AD60">
+        <v>0.64760200000000001</v>
+      </c>
+      <c r="AE60">
+        <v>0.64795700000000001</v>
+      </c>
+      <c r="AF60">
+        <v>0.648285</v>
+      </c>
+      <c r="AG60" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>83</v>
+      </c>
+      <c r="B61" t="s">
+        <v>521</v>
+      </c>
+      <c r="C61" t="s">
+        <v>520</v>
+      </c>
+      <c r="D61" t="s">
+        <v>80</v>
+      </c>
+      <c r="F61">
+        <v>0.60939900000000002</v>
+      </c>
+      <c r="G61">
+        <v>0.61870400000000003</v>
+      </c>
+      <c r="H61">
+        <v>0.627502</v>
+      </c>
+      <c r="I61">
+        <v>0.635687</v>
+      </c>
+      <c r="J61">
+        <v>0.64312899999999995</v>
+      </c>
+      <c r="K61">
+        <v>0.650474</v>
+      </c>
+      <c r="L61">
+        <v>0.65689600000000004</v>
+      </c>
+      <c r="M61">
+        <v>0.662416</v>
+      </c>
+      <c r="N61">
+        <v>0.66691800000000001</v>
+      </c>
+      <c r="O61">
+        <v>0.66920900000000005</v>
+      </c>
+      <c r="P61">
+        <v>0.67036200000000001</v>
+      </c>
+      <c r="Q61">
+        <v>0.67031200000000002</v>
+      </c>
+      <c r="R61">
+        <v>0.67021699999999995</v>
+      </c>
+      <c r="S61">
+        <v>0.67008400000000001</v>
+      </c>
+      <c r="T61">
+        <v>0.66991699999999998</v>
+      </c>
+      <c r="U61">
+        <v>0.66972299999999996</v>
+      </c>
+      <c r="V61">
+        <v>0.66950500000000002</v>
+      </c>
+      <c r="W61">
+        <v>0.66927000000000003</v>
+      </c>
+      <c r="X61">
+        <v>0.66902200000000001</v>
+      </c>
+      <c r="Y61">
+        <v>0.66876599999999997</v>
+      </c>
+      <c r="Z61">
+        <v>0.66850799999999999</v>
+      </c>
+      <c r="AA61">
+        <v>0.66824899999999998</v>
+      </c>
+      <c r="AB61">
+        <v>0.66799500000000001</v>
+      </c>
+      <c r="AC61">
+        <v>0.66774800000000001</v>
+      </c>
+      <c r="AD61">
+        <v>0.66751099999999997</v>
+      </c>
+      <c r="AE61">
+        <v>0.66728600000000005</v>
+      </c>
+      <c r="AF61">
+        <v>0.66707499999999997</v>
+      </c>
+      <c r="AG61" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" t="s">
+        <v>519</v>
+      </c>
+      <c r="C63" t="s">
+        <v>518</v>
+      </c>
+      <c r="D63" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63">
+        <v>605.32141100000001</v>
+      </c>
+      <c r="G63">
+        <v>596.56372099999999</v>
+      </c>
+      <c r="H63">
+        <v>587.74408000000005</v>
+      </c>
+      <c r="I63">
+        <v>578.85461399999997</v>
+      </c>
+      <c r="J63">
+        <v>569.90594499999997</v>
+      </c>
+      <c r="K63">
+        <v>561.43499799999995</v>
+      </c>
+      <c r="L63">
+        <v>548.93573000000004</v>
+      </c>
+      <c r="M63">
+        <v>536.88128700000004</v>
+      </c>
+      <c r="N63">
+        <v>525.27539100000001</v>
+      </c>
+      <c r="O63">
+        <v>514.09533699999997</v>
+      </c>
+      <c r="P63">
+        <v>503.33850100000001</v>
+      </c>
+      <c r="Q63">
+        <v>493.03497299999998</v>
+      </c>
+      <c r="R63">
+        <v>483.48178100000001</v>
+      </c>
+      <c r="S63">
+        <v>474.760132</v>
+      </c>
+      <c r="T63">
+        <v>466.87344400000001</v>
+      </c>
+      <c r="U63">
+        <v>459.84948700000001</v>
+      </c>
+      <c r="V63">
+        <v>453.64550800000001</v>
+      </c>
+      <c r="W63">
+        <v>448.24676499999998</v>
+      </c>
+      <c r="X63">
+        <v>443.60870399999999</v>
+      </c>
+      <c r="Y63">
+        <v>439.75659200000001</v>
+      </c>
+      <c r="Z63">
+        <v>436.64328</v>
+      </c>
+      <c r="AA63">
+        <v>434.29330399999998</v>
+      </c>
+      <c r="AB63">
+        <v>432.73150600000002</v>
+      </c>
+      <c r="AC63">
+        <v>431.93127399999997</v>
+      </c>
+      <c r="AD63">
+        <v>431.20816000000002</v>
+      </c>
+      <c r="AE63">
+        <v>430.55432100000002</v>
+      </c>
+      <c r="AF63">
+        <v>429.95950299999998</v>
+      </c>
+      <c r="AG63" s="9">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" t="s">
+        <v>517</v>
+      </c>
+      <c r="C64" t="s">
+        <v>516</v>
+      </c>
+      <c r="D64" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64">
+        <v>463.55093399999998</v>
+      </c>
+      <c r="G64">
+        <v>458.890198</v>
+      </c>
+      <c r="H64">
+        <v>454.28131100000002</v>
+      </c>
+      <c r="I64">
+        <v>449.72030599999999</v>
+      </c>
+      <c r="J64">
+        <v>445.12622099999999</v>
+      </c>
+      <c r="K64">
+        <v>440.455017</v>
+      </c>
+      <c r="L64">
+        <v>433.68933099999998</v>
+      </c>
+      <c r="M64">
+        <v>426.78295900000001</v>
+      </c>
+      <c r="N64">
+        <v>419.79501299999998</v>
+      </c>
+      <c r="O64">
+        <v>413.10067700000002</v>
+      </c>
+      <c r="P64">
+        <v>406.70031699999998</v>
+      </c>
+      <c r="Q64">
+        <v>400.597534</v>
+      </c>
+      <c r="R64">
+        <v>394.77926600000001</v>
+      </c>
+      <c r="S64">
+        <v>389.23379499999999</v>
+      </c>
+      <c r="T64">
+        <v>383.98913599999997</v>
+      </c>
+      <c r="U64">
+        <v>379.06469700000002</v>
+      </c>
+      <c r="V64">
+        <v>374.43823200000003</v>
+      </c>
+      <c r="W64">
+        <v>370.161316</v>
+      </c>
+      <c r="X64">
+        <v>366.20214800000002</v>
+      </c>
+      <c r="Y64">
+        <v>362.57891799999999</v>
+      </c>
+      <c r="Z64">
+        <v>359.27200299999998</v>
+      </c>
+      <c r="AA64">
+        <v>356.26269500000001</v>
+      </c>
+      <c r="AB64">
+        <v>353.61422700000003</v>
+      </c>
+      <c r="AC64">
+        <v>351.29882800000001</v>
+      </c>
+      <c r="AD64">
+        <v>349.36639400000001</v>
+      </c>
+      <c r="AE64">
+        <v>347.84356700000001</v>
+      </c>
+      <c r="AF64">
+        <v>346.73440599999998</v>
+      </c>
+      <c r="AG64" s="9">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>509</v>
+      </c>
+      <c r="B67" t="s">
+        <v>515</v>
+      </c>
+      <c r="C67" t="s">
+        <v>514</v>
+      </c>
+      <c r="D67" t="s">
+        <v>89</v>
+      </c>
+      <c r="F67">
+        <v>0.96249899999999999</v>
+      </c>
+      <c r="G67">
+        <v>0.95829299999999995</v>
+      </c>
+      <c r="H67">
+        <v>0.95386099999999996</v>
+      </c>
+      <c r="I67">
+        <v>0.94897600000000004</v>
+      </c>
+      <c r="J67">
+        <v>0.94338</v>
+      </c>
+      <c r="K67">
+        <v>0.93713900000000006</v>
+      </c>
+      <c r="L67">
+        <v>0.93051399999999995</v>
+      </c>
+      <c r="M67">
+        <v>0.92341399999999996</v>
+      </c>
+      <c r="N67">
+        <v>0.91581699999999999</v>
+      </c>
+      <c r="O67">
+        <v>0.90795400000000004</v>
+      </c>
+      <c r="P67">
+        <v>0.90028900000000001</v>
+      </c>
+      <c r="Q67">
+        <v>0.89305000000000001</v>
+      </c>
+      <c r="R67">
+        <v>0.88626899999999997</v>
+      </c>
+      <c r="S67">
+        <v>0.87971500000000002</v>
+      </c>
+      <c r="T67">
+        <v>0.87315799999999999</v>
+      </c>
+      <c r="U67">
+        <v>0.86665999999999999</v>
+      </c>
+      <c r="V67">
+        <v>0.860093</v>
+      </c>
+      <c r="W67">
+        <v>0.85333700000000001</v>
+      </c>
+      <c r="X67">
+        <v>0.84650400000000003</v>
+      </c>
+      <c r="Y67">
+        <v>0.83967000000000003</v>
+      </c>
+      <c r="Z67">
+        <v>0.83284999999999998</v>
+      </c>
+      <c r="AA67">
+        <v>0.82602600000000004</v>
+      </c>
+      <c r="AB67">
+        <v>0.81914399999999998</v>
+      </c>
+      <c r="AC67">
+        <v>0.81228999999999996</v>
+      </c>
+      <c r="AD67">
+        <v>0.80550299999999997</v>
+      </c>
+      <c r="AE67">
+        <v>0.79870200000000002</v>
+      </c>
+      <c r="AF67">
+        <v>0.791856</v>
+      </c>
+      <c r="AG67" s="9">
+        <v>-7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68" t="s">
+        <v>513</v>
+      </c>
+      <c r="C68" t="s">
+        <v>512</v>
+      </c>
+      <c r="D68" t="s">
+        <v>89</v>
+      </c>
+      <c r="F68">
+        <v>0.77779500000000001</v>
+      </c>
+      <c r="G68">
+        <v>0.77780400000000005</v>
+      </c>
+      <c r="H68">
+        <v>0.78845600000000005</v>
+      </c>
+      <c r="I68">
+        <v>0.79193599999999997</v>
+      </c>
+      <c r="J68">
+        <v>0.79717300000000002</v>
+      </c>
+      <c r="K68">
+        <v>0.79640299999999997</v>
+      </c>
+      <c r="L68">
+        <v>0.79713100000000003</v>
+      </c>
+      <c r="M68">
+        <v>0.79560699999999995</v>
+      </c>
+      <c r="N68">
+        <v>0.79143799999999997</v>
+      </c>
+      <c r="O68">
+        <v>0.90783000000000003</v>
+      </c>
+      <c r="P68">
+        <v>0.90350900000000001</v>
+      </c>
+      <c r="Q68">
+        <v>0.90333200000000002</v>
+      </c>
+      <c r="R68">
+        <v>0.90135600000000005</v>
+      </c>
+      <c r="S68">
+        <v>0.89688199999999996</v>
+      </c>
+      <c r="T68">
+        <v>0.89327900000000005</v>
+      </c>
+      <c r="U68">
+        <v>0.89083299999999999</v>
+      </c>
+      <c r="V68">
+        <v>0.88829000000000002</v>
+      </c>
+      <c r="W68">
+        <v>0.88452799999999998</v>
+      </c>
+      <c r="X68">
+        <v>0.88126199999999999</v>
+      </c>
+      <c r="Y68">
+        <v>0.88093200000000005</v>
+      </c>
+      <c r="Z68">
+        <v>0.88181200000000004</v>
+      </c>
+      <c r="AA68">
+        <v>0.88065700000000002</v>
+      </c>
+      <c r="AB68">
+        <v>0.87968900000000005</v>
+      </c>
+      <c r="AC68">
+        <v>0.87822</v>
+      </c>
+      <c r="AD68">
+        <v>0.87721899999999997</v>
+      </c>
+      <c r="AE68">
+        <v>0.87615900000000002</v>
+      </c>
+      <c r="AF68">
+        <v>0.87512100000000004</v>
+      </c>
+      <c r="AG68" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>91</v>
+      </c>
+      <c r="B69" t="s">
+        <v>511</v>
+      </c>
+      <c r="C69" t="s">
+        <v>510</v>
+      </c>
+      <c r="D69" t="s">
+        <v>89</v>
+      </c>
+      <c r="F69">
+        <v>0.95514299999999996</v>
+      </c>
+      <c r="G69">
+        <v>0.94909500000000002</v>
+      </c>
+      <c r="H69">
+        <v>0.94300399999999995</v>
+      </c>
+      <c r="I69">
+        <v>0.93666700000000003</v>
+      </c>
+      <c r="J69">
+        <v>0.92990099999999998</v>
+      </c>
+      <c r="K69">
+        <v>0.922678</v>
+      </c>
+      <c r="L69">
+        <v>0.9153</v>
+      </c>
+      <c r="M69">
+        <v>0.907667</v>
+      </c>
+      <c r="N69">
+        <v>0.89975099999999997</v>
+      </c>
+      <c r="O69">
+        <v>0.89316200000000001</v>
+      </c>
+      <c r="P69">
+        <v>0.88683000000000001</v>
+      </c>
+      <c r="Q69">
+        <v>0.88098299999999996</v>
+      </c>
+      <c r="R69">
+        <v>0.87561</v>
+      </c>
+      <c r="S69">
+        <v>0.870475</v>
+      </c>
+      <c r="T69">
+        <v>0.86539299999999997</v>
+      </c>
+      <c r="U69">
+        <v>0.86041800000000002</v>
+      </c>
+      <c r="V69">
+        <v>0.85544500000000001</v>
+      </c>
+      <c r="W69">
+        <v>0.85036100000000003</v>
+      </c>
+      <c r="X69">
+        <v>0.84526299999999999</v>
+      </c>
+      <c r="Y69">
+        <v>0.840229</v>
+      </c>
+      <c r="Z69">
+        <v>0.83528000000000002</v>
+      </c>
+      <c r="AA69">
+        <v>0.83039099999999999</v>
+      </c>
+      <c r="AB69">
+        <v>0.82552000000000003</v>
+      </c>
+      <c r="AC69">
+        <v>0.82072599999999996</v>
+      </c>
+      <c r="AD69">
+        <v>0.81604299999999996</v>
+      </c>
+      <c r="AE69">
+        <v>0.81140699999999999</v>
+      </c>
+      <c r="AF69">
+        <v>0.80679100000000004</v>
+      </c>
+      <c r="AG69" s="9">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>509</v>
+      </c>
+      <c r="B71" t="s">
+        <v>508</v>
+      </c>
+      <c r="C71" t="s">
+        <v>507</v>
+      </c>
+      <c r="D71" t="s">
+        <v>89</v>
+      </c>
+      <c r="F71">
+        <v>0.98706400000000005</v>
+      </c>
+      <c r="G71">
+        <v>0.98577199999999998</v>
+      </c>
+      <c r="H71">
+        <v>0.98426999999999998</v>
+      </c>
+      <c r="I71">
+        <v>0.98250800000000005</v>
+      </c>
+      <c r="J71">
+        <v>0.98045800000000005</v>
+      </c>
+      <c r="K71">
+        <v>0.97818700000000003</v>
+      </c>
+      <c r="L71">
+        <v>0.97578299999999996</v>
+      </c>
+      <c r="M71">
+        <v>0.97324600000000006</v>
+      </c>
+      <c r="N71">
+        <v>0.97056500000000001</v>
+      </c>
+      <c r="O71">
+        <v>0.96779499999999996</v>
+      </c>
+      <c r="P71">
+        <v>0.96509599999999995</v>
+      </c>
+      <c r="Q71">
+        <v>0.96253900000000003</v>
+      </c>
+      <c r="R71">
+        <v>0.96013199999999999</v>
+      </c>
+      <c r="S71">
+        <v>0.95780299999999996</v>
+      </c>
+      <c r="T71">
+        <v>0.95547099999999996</v>
+      </c>
+      <c r="U71">
+        <v>0.95317200000000002</v>
+      </c>
+      <c r="V71">
+        <v>0.95085500000000001</v>
+      </c>
+      <c r="W71">
+        <v>0.94845699999999999</v>
+      </c>
+      <c r="X71">
+        <v>0.94602200000000003</v>
+      </c>
+      <c r="Y71">
+        <v>0.94357500000000005</v>
+      </c>
+      <c r="Z71">
+        <v>0.94112799999999996</v>
+      </c>
+      <c r="AA71">
+        <v>0.93869599999999997</v>
+      </c>
+      <c r="AB71">
+        <v>0.93624700000000005</v>
+      </c>
+      <c r="AC71">
+        <v>0.933813</v>
+      </c>
+      <c r="AD71">
+        <v>0.931396</v>
+      </c>
+      <c r="AE71">
+        <v>0.92897200000000002</v>
+      </c>
+      <c r="AF71">
+        <v>0.92652999999999996</v>
+      </c>
+      <c r="AG71" s="9">
+        <v>-2E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>90</v>
+      </c>
+      <c r="B72" t="s">
+        <v>506</v>
+      </c>
+      <c r="C72" t="s">
+        <v>505</v>
+      </c>
+      <c r="D72" t="s">
+        <v>89</v>
+      </c>
+      <c r="F72">
+        <v>0.96223800000000004</v>
+      </c>
+      <c r="G72">
+        <v>0.96373500000000001</v>
+      </c>
+      <c r="H72">
+        <v>0.97250599999999998</v>
+      </c>
+      <c r="I72">
+        <v>0.97536900000000004</v>
+      </c>
+      <c r="J72">
+        <v>0.97906000000000004</v>
+      </c>
+      <c r="K72">
+        <v>0.98203700000000005</v>
+      </c>
+      <c r="L72">
+        <v>0.98287800000000003</v>
+      </c>
+      <c r="M72">
+        <v>0.982742</v>
+      </c>
+      <c r="N72">
+        <v>0.98086799999999996</v>
+      </c>
+      <c r="O72">
+        <v>1.0203709999999999</v>
+      </c>
+      <c r="P72">
+        <v>1.0181690000000001</v>
+      </c>
+      <c r="Q72">
+        <v>1.0179069999999999</v>
+      </c>
+      <c r="R72">
+        <v>1.016993</v>
+      </c>
+      <c r="S72">
+        <v>1.014689</v>
+      </c>
+      <c r="T72">
+        <v>1.0129760000000001</v>
+      </c>
+      <c r="U72">
+        <v>1.0120750000000001</v>
+      </c>
+      <c r="V72">
+        <v>1.0114399999999999</v>
+      </c>
+      <c r="W72">
+        <v>1.010168</v>
+      </c>
+      <c r="X72">
+        <v>1.0089360000000001</v>
+      </c>
+      <c r="Y72">
+        <v>1.0096099999999999</v>
+      </c>
+      <c r="Z72">
+        <v>1.0109030000000001</v>
+      </c>
+      <c r="AA72">
+        <v>1.0107729999999999</v>
+      </c>
+      <c r="AB72">
+        <v>1.010664</v>
+      </c>
+      <c r="AC72">
+        <v>1.0103740000000001</v>
+      </c>
+      <c r="AD72">
+        <v>1.010311</v>
+      </c>
+      <c r="AE72">
+        <v>1.0102930000000001</v>
+      </c>
+      <c r="AF72">
+        <v>1.0102</v>
+      </c>
+      <c r="AG72" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" t="s">
+        <v>504</v>
+      </c>
+      <c r="C73" t="s">
+        <v>503</v>
+      </c>
+      <c r="D73" t="s">
+        <v>89</v>
+      </c>
+      <c r="F73">
+        <v>0.98711800000000005</v>
+      </c>
+      <c r="G73">
+        <v>0.98565800000000003</v>
+      </c>
+      <c r="H73">
+        <v>0.98411000000000004</v>
+      </c>
+      <c r="I73">
+        <v>0.98237699999999994</v>
+      </c>
+      <c r="J73">
+        <v>0.98045300000000002</v>
+      </c>
+      <c r="K73">
+        <v>0.97839399999999999</v>
+      </c>
+      <c r="L73">
+        <v>0.97626400000000002</v>
+      </c>
+      <c r="M73">
+        <v>0.974055</v>
+      </c>
+      <c r="N73">
+        <v>0.97173900000000002</v>
+      </c>
+      <c r="O73">
+        <v>0.96975900000000004</v>
+      </c>
+      <c r="P73">
+        <v>0.96782999999999997</v>
+      </c>
+      <c r="Q73">
+        <v>0.96604500000000004</v>
+      </c>
+      <c r="R73">
+        <v>0.96439600000000003</v>
+      </c>
+      <c r="S73">
+        <v>0.96279999999999999</v>
+      </c>
+      <c r="T73">
+        <v>0.96119299999999996</v>
+      </c>
+      <c r="U73">
+        <v>0.95961099999999999</v>
+      </c>
+      <c r="V73">
+        <v>0.95801400000000003</v>
+      </c>
+      <c r="W73">
+        <v>0.95634399999999997</v>
+      </c>
+      <c r="X73">
+        <v>0.95464099999999996</v>
+      </c>
+      <c r="Y73">
+        <v>0.95293700000000003</v>
+      </c>
+      <c r="Z73">
+        <v>0.95125099999999996</v>
+      </c>
+      <c r="AA73">
+        <v>0.94959099999999996</v>
+      </c>
+      <c r="AB73">
+        <v>0.94793099999999997</v>
+      </c>
+      <c r="AC73">
+        <v>0.946295</v>
+      </c>
+      <c r="AD73">
+        <v>0.94468700000000005</v>
+      </c>
+      <c r="AE73">
+        <v>0.94308499999999995</v>
+      </c>
+      <c r="AF73">
+        <v>0.94148100000000001</v>
+      </c>
+      <c r="AG73" s="9">
+        <v>-2E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" t="s">
+        <v>502</v>
+      </c>
+      <c r="C77" t="s">
+        <v>501</v>
+      </c>
+      <c r="D77" t="s">
+        <v>95</v>
+      </c>
+      <c r="F77">
+        <v>1.725E-3</v>
+      </c>
+      <c r="G77">
+        <v>3.088E-3</v>
+      </c>
+      <c r="H77">
+        <v>3.101E-3</v>
+      </c>
+      <c r="I77">
+        <v>3.114E-3</v>
+      </c>
+      <c r="J77">
+        <v>3.127E-3</v>
+      </c>
+      <c r="K77">
+        <v>3.14E-3</v>
+      </c>
+      <c r="L77">
+        <v>3.153E-3</v>
+      </c>
+      <c r="M77">
+        <v>3.166E-3</v>
+      </c>
+      <c r="N77">
+        <v>3.179E-3</v>
+      </c>
+      <c r="O77">
+        <v>3.192E-3</v>
+      </c>
+      <c r="P77">
+        <v>3.2049999999999999E-3</v>
+      </c>
+      <c r="Q77">
+        <v>3.2179999999999999E-3</v>
+      </c>
+      <c r="R77">
+        <v>3.2309999999999999E-3</v>
+      </c>
+      <c r="S77">
+        <v>3.2439999999999999E-3</v>
+      </c>
+      <c r="T77">
+        <v>3.2569999999999999E-3</v>
+      </c>
+      <c r="U77">
+        <v>3.2699999999999999E-3</v>
+      </c>
+      <c r="V77">
+        <v>3.2850000000000002E-3</v>
+      </c>
+      <c r="W77">
+        <v>3.3010000000000001E-3</v>
+      </c>
+      <c r="X77">
+        <v>3.3219999999999999E-3</v>
+      </c>
+      <c r="Y77">
+        <v>3.3519999999999999E-3</v>
+      </c>
+      <c r="Z77">
+        <v>3.3990000000000001E-3</v>
+      </c>
+      <c r="AA77">
+        <v>3.4780000000000002E-3</v>
+      </c>
+      <c r="AB77">
+        <v>3.6180000000000001E-3</v>
+      </c>
+      <c r="AC77">
+        <v>3.7590000000000002E-3</v>
+      </c>
+      <c r="AD77">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="AE77">
+        <v>4.0419999999999996E-3</v>
+      </c>
+      <c r="AF77">
+        <v>4.1850000000000004E-3</v>
+      </c>
+      <c r="AG77" s="9">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F78" s="14">
+        <v>41.307827000000003</v>
+      </c>
+      <c r="G78" s="14">
+        <v>47.377986999999997</v>
+      </c>
+      <c r="H78" s="14">
+        <v>53.527718</v>
+      </c>
+      <c r="I78" s="14">
+        <v>59.344631</v>
+      </c>
+      <c r="J78" s="14">
+        <v>65.296081999999998</v>
+      </c>
+      <c r="K78" s="14">
+        <v>71.340698000000003</v>
+      </c>
+      <c r="L78" s="14">
+        <v>77.804955000000007</v>
+      </c>
+      <c r="M78" s="14">
+        <v>84.770461999999995</v>
+      </c>
+      <c r="N78" s="14">
+        <v>91.686965999999998</v>
+      </c>
+      <c r="O78" s="14">
+        <v>98.871689000000003</v>
+      </c>
+      <c r="P78" s="14">
+        <v>105.994034</v>
+      </c>
+      <c r="Q78" s="14">
+        <v>111.568611</v>
+      </c>
+      <c r="R78" s="14">
+        <v>117.32034299999999</v>
+      </c>
+      <c r="S78" s="14">
+        <v>123.133934</v>
+      </c>
+      <c r="T78" s="14">
+        <v>129.23361199999999</v>
+      </c>
+      <c r="U78" s="14">
+        <v>135.37600699999999</v>
+      </c>
+      <c r="V78" s="14">
+        <v>141.64863600000001</v>
+      </c>
+      <c r="W78" s="14">
+        <v>147.97232099999999</v>
+      </c>
+      <c r="X78" s="14">
+        <v>154.48625200000001</v>
+      </c>
+      <c r="Y78" s="14">
+        <v>161.08810399999999</v>
+      </c>
+      <c r="Z78" s="14">
+        <v>167.799713</v>
+      </c>
+      <c r="AA78" s="14">
+        <v>174.750168</v>
+      </c>
+      <c r="AB78" s="14">
+        <v>181.85144</v>
+      </c>
+      <c r="AC78" s="14">
+        <v>189.17082199999999</v>
+      </c>
+      <c r="AD78" s="14">
+        <v>196.66996800000001</v>
+      </c>
+      <c r="AE78" s="14">
+        <v>204.34806800000001</v>
+      </c>
+      <c r="AF78" s="14">
+        <v>212.126541</v>
+      </c>
+      <c r="AG78" s="15">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>97</v>
+      </c>
+      <c r="B79" t="s">
+        <v>498</v>
+      </c>
+      <c r="C79" t="s">
+        <v>497</v>
+      </c>
+      <c r="D79" t="s">
+        <v>95</v>
+      </c>
+      <c r="F79">
+        <v>0.30817899999999998</v>
+      </c>
+      <c r="G79">
+        <v>0.560921</v>
+      </c>
+      <c r="H79">
+        <v>0.80604399999999998</v>
+      </c>
+      <c r="I79">
+        <v>0.90843200000000002</v>
+      </c>
+      <c r="J79">
+        <v>1.022869</v>
+      </c>
+      <c r="K79">
+        <v>1.146172</v>
+      </c>
+      <c r="L79">
+        <v>1.390895</v>
+      </c>
+      <c r="M79">
+        <v>1.6908190000000001</v>
+      </c>
+      <c r="N79">
+        <v>1.994769</v>
+      </c>
+      <c r="O79">
+        <v>2.108177</v>
+      </c>
+      <c r="P79">
+        <v>2.1611229999999999</v>
+      </c>
+      <c r="Q79">
+        <v>2.1623380000000001</v>
+      </c>
+      <c r="R79">
+        <v>2.1638169999999999</v>
+      </c>
+      <c r="S79">
+        <v>2.1655449999999998</v>
+      </c>
+      <c r="T79">
+        <v>2.1675360000000001</v>
+      </c>
+      <c r="U79">
+        <v>2.1697259999999998</v>
+      </c>
+      <c r="V79">
+        <v>2.172139</v>
+      </c>
+      <c r="W79">
+        <v>2.1747999999999998</v>
+      </c>
+      <c r="X79">
+        <v>2.1776339999999998</v>
+      </c>
+      <c r="Y79">
+        <v>2.18058</v>
+      </c>
+      <c r="Z79">
+        <v>2.1836340000000001</v>
+      </c>
+      <c r="AA79">
+        <v>2.1868249999999998</v>
+      </c>
+      <c r="AB79">
+        <v>2.190188</v>
+      </c>
+      <c r="AC79">
+        <v>2.193648</v>
+      </c>
+      <c r="AD79">
+        <v>2.1972459999999998</v>
+      </c>
+      <c r="AE79">
+        <v>2.2009859999999999</v>
+      </c>
+      <c r="AF79">
+        <v>2.2048700000000001</v>
+      </c>
+      <c r="AG79" s="9">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>49</v>
+      </c>
+      <c r="B80" t="s">
+        <v>496</v>
+      </c>
+      <c r="C80" t="s">
+        <v>495</v>
+      </c>
+      <c r="D80" t="s">
+        <v>95</v>
+      </c>
+      <c r="F80">
+        <v>41.617728999999997</v>
+      </c>
+      <c r="G80">
+        <v>47.941997999999998</v>
+      </c>
+      <c r="H80">
+        <v>54.336863999999998</v>
+      </c>
+      <c r="I80">
+        <v>60.256176000000004</v>
+      </c>
+      <c r="J80">
+        <v>66.322074999999998</v>
+      </c>
+      <c r="K80">
+        <v>72.490013000000005</v>
+      </c>
+      <c r="L80">
+        <v>79.198997000000006</v>
+      </c>
+      <c r="M80">
+        <v>86.464447000000007</v>
+      </c>
+      <c r="N80">
+        <v>93.684914000000006</v>
+      </c>
+      <c r="O80">
+        <v>100.98305499999999</v>
+      </c>
+      <c r="P80">
+        <v>108.15836299999999</v>
+      </c>
+      <c r="Q80">
+        <v>113.73416899999999</v>
+      </c>
+      <c r="R80">
+        <v>119.487396</v>
+      </c>
+      <c r="S80">
+        <v>125.302719</v>
+      </c>
+      <c r="T80">
+        <v>131.404404</v>
+      </c>
+      <c r="U80">
+        <v>137.54899599999999</v>
+      </c>
+      <c r="V80">
+        <v>143.824051</v>
+      </c>
+      <c r="W80">
+        <v>150.15042099999999</v>
+      </c>
+      <c r="X80">
+        <v>156.66720599999999</v>
+      </c>
+      <c r="Y80">
+        <v>163.27203399999999</v>
+      </c>
+      <c r="Z80">
+        <v>169.98675499999999</v>
+      </c>
+      <c r="AA80">
+        <v>176.94047499999999</v>
+      </c>
+      <c r="AB80">
+        <v>184.045242</v>
+      </c>
+      <c r="AC80">
+        <v>191.368225</v>
+      </c>
+      <c r="AD80">
+        <v>198.87112400000001</v>
+      </c>
+      <c r="AE80">
+        <v>206.553101</v>
+      </c>
+      <c r="AF80">
+        <v>214.335587</v>
+      </c>
+      <c r="AG80" s="9">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" t="s">
+        <v>494</v>
+      </c>
+      <c r="C82" t="s">
+        <v>493</v>
+      </c>
+      <c r="D82" t="s">
+        <v>98</v>
+      </c>
+      <c r="F82">
+        <v>6.8329999999999997E-3</v>
+      </c>
+      <c r="G82">
+        <v>1.223E-2</v>
+      </c>
+      <c r="H82">
+        <v>1.2281E-2</v>
+      </c>
+      <c r="I82">
+        <v>1.2333E-2</v>
+      </c>
+      <c r="J82">
+        <v>1.2383999999999999E-2</v>
+      </c>
+      <c r="K82">
+        <v>1.2435999999999999E-2</v>
+      </c>
+      <c r="L82">
+        <v>1.2487E-2</v>
+      </c>
+      <c r="M82">
+        <v>1.2539E-2</v>
+      </c>
+      <c r="N82">
+        <v>1.259E-2</v>
+      </c>
+      <c r="O82">
+        <v>1.2642E-2</v>
+      </c>
+      <c r="P82">
+        <v>1.2692999999999999E-2</v>
+      </c>
+      <c r="Q82">
+        <v>1.2744E-2</v>
+      </c>
+      <c r="R82">
+        <v>1.2796E-2</v>
+      </c>
+      <c r="S82">
+        <v>1.2847000000000001E-2</v>
+      </c>
+      <c r="T82">
+        <v>1.2899000000000001E-2</v>
+      </c>
+      <c r="U82">
+        <v>1.2951000000000001E-2</v>
+      </c>
+      <c r="V82">
+        <v>1.3006999999999999E-2</v>
+      </c>
+      <c r="W82">
+        <v>1.3070999999999999E-2</v>
+      </c>
+      <c r="X82">
+        <v>1.3154000000000001E-2</v>
+      </c>
+      <c r="Y82">
+        <v>1.3272000000000001E-2</v>
+      </c>
+      <c r="Z82">
+        <v>1.3459E-2</v>
+      </c>
+      <c r="AA82">
+        <v>1.3774E-2</v>
+      </c>
+      <c r="AB82">
+        <v>1.4328E-2</v>
+      </c>
+      <c r="AC82">
+        <v>1.4885000000000001E-2</v>
+      </c>
+      <c r="AD82">
+        <v>1.5443999999999999E-2</v>
+      </c>
+      <c r="AE82">
+        <v>1.6007E-2</v>
+      </c>
+      <c r="AF82">
+        <v>1.6572E-2</v>
+      </c>
+      <c r="AG82" s="9">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>96</v>
+      </c>
+      <c r="B83" t="s">
+        <v>492</v>
+      </c>
+      <c r="C83" t="s">
+        <v>491</v>
+      </c>
+      <c r="D83" t="s">
+        <v>98</v>
+      </c>
+      <c r="F83">
+        <v>62.697704000000002</v>
+      </c>
+      <c r="G83">
+        <v>71.294235</v>
+      </c>
+      <c r="H83">
+        <v>79.992973000000006</v>
+      </c>
+      <c r="I83">
+        <v>88.178039999999996</v>
+      </c>
+      <c r="J83">
+        <v>96.523482999999999</v>
+      </c>
+      <c r="K83">
+        <v>104.968887</v>
+      </c>
+      <c r="L83">
+        <v>113.990364</v>
+      </c>
+      <c r="M83">
+        <v>123.68132</v>
+      </c>
+      <c r="N83">
+        <v>133.259018</v>
+      </c>
+      <c r="O83">
+        <v>143.18649300000001</v>
+      </c>
+      <c r="P83">
+        <v>153.01391599999999</v>
+      </c>
+      <c r="Q83">
+        <v>160.67247</v>
+      </c>
+      <c r="R83">
+        <v>168.56346099999999</v>
+      </c>
+      <c r="S83">
+        <v>176.51448099999999</v>
+      </c>
+      <c r="T83">
+        <v>184.853317</v>
+      </c>
+      <c r="U83">
+        <v>193.228027</v>
+      </c>
+      <c r="V83">
+        <v>201.758499</v>
+      </c>
+      <c r="W83">
+        <v>210.33152799999999</v>
+      </c>
+      <c r="X83">
+        <v>219.14546200000001</v>
+      </c>
+      <c r="Y83">
+        <v>228.058289</v>
+      </c>
+      <c r="Z83">
+        <v>237.096405</v>
+      </c>
+      <c r="AA83">
+        <v>246.43699599999999</v>
+      </c>
+      <c r="AB83">
+        <v>255.963303</v>
+      </c>
+      <c r="AC83">
+        <v>265.76538099999999</v>
+      </c>
+      <c r="AD83">
+        <v>275.789062</v>
+      </c>
+      <c r="AE83">
+        <v>286.03298999999998</v>
+      </c>
+      <c r="AF83">
+        <v>296.38397200000003</v>
+      </c>
+      <c r="AG83" s="9">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>97</v>
+      </c>
+      <c r="B84" t="s">
+        <v>490</v>
+      </c>
+      <c r="C84" t="s">
+        <v>489</v>
+      </c>
+      <c r="D84" t="s">
+        <v>98</v>
+      </c>
+      <c r="F84">
+        <v>0.36942000000000003</v>
+      </c>
+      <c r="G84">
+        <v>0.62720100000000001</v>
+      </c>
+      <c r="H84">
+        <v>0.87962300000000004</v>
+      </c>
+      <c r="I84">
+        <v>0.99686600000000003</v>
+      </c>
+      <c r="J84">
+        <v>1.1279790000000001</v>
+      </c>
+      <c r="K84">
+        <v>1.269903</v>
+      </c>
+      <c r="L84">
+        <v>1.541979</v>
+      </c>
+      <c r="M84">
+        <v>1.9001189999999999</v>
+      </c>
+      <c r="N84">
+        <v>2.2639939999999998</v>
+      </c>
+      <c r="O84">
+        <v>2.3875139999999999</v>
+      </c>
+      <c r="P84">
+        <v>2.4449730000000001</v>
+      </c>
+      <c r="Q84">
+        <v>2.4463569999999999</v>
+      </c>
+      <c r="R84">
+        <v>2.448035</v>
+      </c>
+      <c r="S84">
+        <v>2.4499900000000001</v>
+      </c>
+      <c r="T84">
+        <v>2.4522360000000001</v>
+      </c>
+      <c r="U84">
+        <v>2.4546999999999999</v>
+      </c>
+      <c r="V84">
+        <v>2.4574090000000002</v>
+      </c>
+      <c r="W84">
+        <v>2.4603890000000002</v>
+      </c>
+      <c r="X84">
+        <v>2.4635590000000001</v>
+      </c>
+      <c r="Y84">
+        <v>2.4668480000000002</v>
+      </c>
+      <c r="Z84">
+        <v>2.4702540000000002</v>
+      </c>
+      <c r="AA84">
+        <v>2.4738060000000002</v>
+      </c>
+      <c r="AB84">
+        <v>2.4775369999999999</v>
+      </c>
+      <c r="AC84">
+        <v>2.4813749999999999</v>
+      </c>
+      <c r="AD84">
+        <v>2.4853670000000001</v>
+      </c>
+      <c r="AE84">
+        <v>2.4895170000000002</v>
+      </c>
+      <c r="AF84">
+        <v>2.493827</v>
+      </c>
+      <c r="AG84" s="9">
+        <v>7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>49</v>
+      </c>
+      <c r="B85" t="s">
+        <v>488</v>
+      </c>
+      <c r="C85" t="s">
+        <v>487</v>
+      </c>
+      <c r="D85" t="s">
+        <v>98</v>
+      </c>
+      <c r="F85">
+        <v>63.073956000000003</v>
+      </c>
+      <c r="G85">
+        <v>71.933661999999998</v>
+      </c>
+      <c r="H85">
+        <v>80.884879999999995</v>
+      </c>
+      <c r="I85">
+        <v>89.187233000000006</v>
+      </c>
+      <c r="J85">
+        <v>97.663848999999999</v>
+      </c>
+      <c r="K85">
+        <v>106.251228</v>
+      </c>
+      <c r="L85">
+        <v>115.54483</v>
+      </c>
+      <c r="M85">
+        <v>125.593971</v>
+      </c>
+      <c r="N85">
+        <v>135.53559899999999</v>
+      </c>
+      <c r="O85">
+        <v>145.58663899999999</v>
+      </c>
+      <c r="P85">
+        <v>155.471588</v>
+      </c>
+      <c r="Q85">
+        <v>163.131561</v>
+      </c>
+      <c r="R85">
+        <v>171.024292</v>
+      </c>
+      <c r="S85">
+        <v>178.97732500000001</v>
+      </c>
+      <c r="T85">
+        <v>187.31845100000001</v>
+      </c>
+      <c r="U85">
+        <v>195.69567900000001</v>
+      </c>
+      <c r="V85">
+        <v>204.22891200000001</v>
+      </c>
+      <c r="W85">
+        <v>212.804993</v>
+      </c>
+      <c r="X85">
+        <v>221.62217699999999</v>
+      </c>
+      <c r="Y85">
+        <v>230.53840600000001</v>
+      </c>
+      <c r="Z85">
+        <v>239.58012400000001</v>
+      </c>
+      <c r="AA85">
+        <v>248.924576</v>
+      </c>
+      <c r="AB85">
+        <v>258.45517000000001</v>
+      </c>
+      <c r="AC85">
+        <v>268.26165800000001</v>
+      </c>
+      <c r="AD85">
+        <v>278.28988600000002</v>
+      </c>
+      <c r="AE85">
+        <v>288.53851300000002</v>
+      </c>
+      <c r="AF85">
+        <v>298.89437900000001</v>
+      </c>
+      <c r="AG85" s="9">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" t="s">
+        <v>486</v>
+      </c>
+      <c r="C87" t="s">
+        <v>485</v>
+      </c>
+      <c r="D87" t="s">
+        <v>98</v>
+      </c>
+      <c r="F87">
+        <v>11.527926000000001</v>
+      </c>
+      <c r="G87">
+        <v>13.327674999999999</v>
+      </c>
+      <c r="H87">
+        <v>15.115705</v>
+      </c>
+      <c r="I87">
+        <v>16.711511999999999</v>
+      </c>
+      <c r="J87">
+        <v>18.336743999999999</v>
+      </c>
+      <c r="K87">
+        <v>19.964907</v>
+      </c>
+      <c r="L87">
+        <v>21.847279</v>
+      </c>
+      <c r="M87">
+        <v>23.999292000000001</v>
+      </c>
+      <c r="N87">
+        <v>26.075050000000001</v>
+      </c>
+      <c r="O87">
+        <v>28.288122000000001</v>
+      </c>
+      <c r="P87">
+        <v>30.488133999999999</v>
+      </c>
+      <c r="Q87">
+        <v>32.147984000000001</v>
+      </c>
+      <c r="R87">
+        <v>33.877605000000003</v>
+      </c>
+      <c r="S87">
+        <v>35.583419999999997</v>
+      </c>
+      <c r="T87">
+        <v>37.429049999999997</v>
+      </c>
+      <c r="U87">
+        <v>39.226177</v>
+      </c>
+      <c r="V87">
+        <v>41.045380000000002</v>
+      </c>
+      <c r="W87">
+        <v>42.813847000000003</v>
+      </c>
+      <c r="X87">
+        <v>44.644409000000003</v>
+      </c>
+      <c r="Y87">
+        <v>46.466735999999997</v>
+      </c>
+      <c r="Z87">
+        <v>48.275852</v>
+      </c>
+      <c r="AA87">
+        <v>50.168255000000002</v>
+      </c>
+      <c r="AB87">
+        <v>52.062747999999999</v>
+      </c>
+      <c r="AC87">
+        <v>54.058846000000003</v>
+      </c>
+      <c r="AD87">
+        <v>56.059513000000003</v>
+      </c>
+      <c r="AE87">
+        <v>58.126334999999997</v>
+      </c>
+      <c r="AF87">
+        <v>60.175502999999999</v>
+      </c>
+      <c r="AG87" s="9">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" t="s">
+        <v>484</v>
+      </c>
+      <c r="C88" t="s">
+        <v>483</v>
+      </c>
+      <c r="D88" t="s">
+        <v>98</v>
+      </c>
+      <c r="F88">
+        <v>51.546031999999997</v>
+      </c>
+      <c r="G88">
+        <v>58.605991000000003</v>
+      </c>
+      <c r="H88">
+        <v>65.769172999999995</v>
+      </c>
+      <c r="I88">
+        <v>72.475723000000002</v>
+      </c>
+      <c r="J88">
+        <v>79.327110000000005</v>
+      </c>
+      <c r="K88">
+        <v>86.286323999999993</v>
+      </c>
+      <c r="L88">
+        <v>93.697556000000006</v>
+      </c>
+      <c r="M88">
+        <v>101.594688</v>
+      </c>
+      <c r="N88">
+        <v>109.460548</v>
+      </c>
+      <c r="O88">
+        <v>117.298531</v>
+      </c>
+      <c r="P88">
+        <v>124.983452</v>
+      </c>
+      <c r="Q88">
+        <v>130.98358200000001</v>
+      </c>
+      <c r="R88">
+        <v>137.146683</v>
+      </c>
+      <c r="S88">
+        <v>143.39390599999999</v>
+      </c>
+      <c r="T88">
+        <v>149.88938899999999</v>
+      </c>
+      <c r="U88">
+        <v>156.46949799999999</v>
+      </c>
+      <c r="V88">
+        <v>163.18351699999999</v>
+      </c>
+      <c r="W88">
+        <v>169.99115</v>
+      </c>
+      <c r="X88">
+        <v>176.977768</v>
+      </c>
+      <c r="Y88">
+        <v>184.07167100000001</v>
+      </c>
+      <c r="Z88">
+        <v>191.30427599999999</v>
+      </c>
+      <c r="AA88">
+        <v>198.75633199999999</v>
+      </c>
+      <c r="AB88">
+        <v>206.39241000000001</v>
+      </c>
+      <c r="AC88">
+        <v>214.20282</v>
+      </c>
+      <c r="AD88">
+        <v>222.230377</v>
+      </c>
+      <c r="AE88">
+        <v>230.41217</v>
+      </c>
+      <c r="AF88">
+        <v>238.718842</v>
+      </c>
+      <c r="AG88" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" t="s">
+        <v>482</v>
+      </c>
+      <c r="C90" t="s">
+        <v>481</v>
+      </c>
+      <c r="D90" t="s">
+        <v>103</v>
+      </c>
+      <c r="F90">
+        <v>5.2158999999999997E-2</v>
+      </c>
+      <c r="G90">
+        <v>9.3352000000000004E-2</v>
+      </c>
+      <c r="H90">
+        <v>9.3744999999999995E-2</v>
+      </c>
+      <c r="I90">
+        <v>9.4137999999999999E-2</v>
+      </c>
+      <c r="J90">
+        <v>9.4531000000000004E-2</v>
+      </c>
+      <c r="K90">
+        <v>9.4923999999999994E-2</v>
+      </c>
+      <c r="L90">
+        <v>9.5316999999999999E-2</v>
+      </c>
+      <c r="M90">
+        <v>9.5710000000000003E-2</v>
+      </c>
+      <c r="N90">
+        <v>9.6102999999999994E-2</v>
+      </c>
+      <c r="O90">
+        <v>9.6495999999999998E-2</v>
+      </c>
+      <c r="P90">
+        <v>9.6889000000000003E-2</v>
+      </c>
+      <c r="Q90">
+        <v>9.7281999999999993E-2</v>
+      </c>
+      <c r="R90">
+        <v>9.7674999999999998E-2</v>
+      </c>
+      <c r="S90">
+        <v>9.8068000000000002E-2</v>
+      </c>
+      <c r="T90">
+        <v>9.8461000000000007E-2</v>
+      </c>
+      <c r="U90">
+        <v>9.8860000000000003E-2</v>
+      </c>
+      <c r="V90">
+        <v>9.9283999999999997E-2</v>
+      </c>
+      <c r="W90">
+        <v>9.9774000000000002E-2</v>
+      </c>
+      <c r="X90">
+        <v>0.100407</v>
+      </c>
+      <c r="Y90">
+        <v>0.101309</v>
+      </c>
+      <c r="Z90">
+        <v>0.10273500000000001</v>
+      </c>
+      <c r="AA90">
+        <v>0.105142</v>
+      </c>
+      <c r="AB90">
+        <v>0.109371</v>
+      </c>
+      <c r="AC90">
+        <v>0.113619</v>
+      </c>
+      <c r="AD90">
+        <v>0.117891</v>
+      </c>
+      <c r="AE90">
+        <v>0.122184</v>
+      </c>
+      <c r="AF90">
+        <v>0.126495</v>
+      </c>
+      <c r="AG90" s="9">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" t="s">
+        <v>480</v>
+      </c>
+      <c r="C91" t="s">
+        <v>479</v>
+      </c>
+      <c r="D91" t="s">
+        <v>103</v>
+      </c>
+      <c r="F91">
+        <v>213.92456100000001</v>
+      </c>
+      <c r="G91">
+        <v>243.25592</v>
+      </c>
+      <c r="H91">
+        <v>272.93600500000002</v>
+      </c>
+      <c r="I91">
+        <v>300.86346400000002</v>
+      </c>
+      <c r="J91">
+        <v>329.33810399999999</v>
+      </c>
+      <c r="K91">
+        <v>358.15386999999998</v>
+      </c>
+      <c r="L91">
+        <v>388.93511999999998</v>
+      </c>
+      <c r="M91">
+        <v>422.00060999999999</v>
+      </c>
+      <c r="N91">
+        <v>454.67974900000002</v>
+      </c>
+      <c r="O91">
+        <v>488.55230699999998</v>
+      </c>
+      <c r="P91">
+        <v>522.08343500000001</v>
+      </c>
+      <c r="Q91">
+        <v>548.21447799999999</v>
+      </c>
+      <c r="R91">
+        <v>575.13855000000001</v>
+      </c>
+      <c r="S91">
+        <v>602.26739499999996</v>
+      </c>
+      <c r="T91">
+        <v>630.71948199999997</v>
+      </c>
+      <c r="U91">
+        <v>659.29394500000001</v>
+      </c>
+      <c r="V91">
+        <v>688.399902</v>
+      </c>
+      <c r="W91">
+        <v>717.65118399999994</v>
+      </c>
+      <c r="X91">
+        <v>747.72436500000003</v>
+      </c>
+      <c r="Y91">
+        <v>778.13476600000001</v>
+      </c>
+      <c r="Z91">
+        <v>808.97296100000005</v>
+      </c>
+      <c r="AA91">
+        <v>840.84301800000003</v>
+      </c>
+      <c r="AB91">
+        <v>873.34674099999995</v>
+      </c>
+      <c r="AC91">
+        <v>906.79150400000003</v>
+      </c>
+      <c r="AD91">
+        <v>940.99224900000002</v>
+      </c>
+      <c r="AE91">
+        <v>975.94445800000005</v>
+      </c>
+      <c r="AF91">
+        <v>1011.261963</v>
+      </c>
+      <c r="AG91" s="9">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" t="s">
+        <v>478</v>
+      </c>
+      <c r="C92" t="s">
+        <v>477</v>
+      </c>
+      <c r="D92" t="s">
+        <v>103</v>
+      </c>
+      <c r="F92">
+        <v>1.2604599999999999</v>
+      </c>
+      <c r="G92">
+        <v>2.1400079999999999</v>
+      </c>
+      <c r="H92">
+        <v>3.0012729999999999</v>
+      </c>
+      <c r="I92">
+        <v>3.4013070000000001</v>
+      </c>
+      <c r="J92">
+        <v>3.848665</v>
+      </c>
+      <c r="K92">
+        <v>4.3329079999999998</v>
+      </c>
+      <c r="L92">
+        <v>5.2612310000000004</v>
+      </c>
+      <c r="M92">
+        <v>6.483206</v>
+      </c>
+      <c r="N92">
+        <v>7.7247459999999997</v>
+      </c>
+      <c r="O92">
+        <v>8.1461970000000008</v>
+      </c>
+      <c r="P92">
+        <v>8.3422479999999997</v>
+      </c>
+      <c r="Q92">
+        <v>8.3469700000000007</v>
+      </c>
+      <c r="R92">
+        <v>8.3526950000000006</v>
+      </c>
+      <c r="S92">
+        <v>8.3593650000000004</v>
+      </c>
+      <c r="T92">
+        <v>8.3670290000000005</v>
+      </c>
+      <c r="U92">
+        <v>8.3754380000000008</v>
+      </c>
+      <c r="V92">
+        <v>8.3846799999999995</v>
+      </c>
+      <c r="W92">
+        <v>8.3948470000000004</v>
+      </c>
+      <c r="X92">
+        <v>8.4056619999999995</v>
+      </c>
+      <c r="Y92">
+        <v>8.4168839999999996</v>
+      </c>
+      <c r="Z92">
+        <v>8.4285049999999995</v>
+      </c>
+      <c r="AA92">
+        <v>8.4406239999999997</v>
+      </c>
+      <c r="AB92">
+        <v>8.4533539999999991</v>
+      </c>
+      <c r="AC92">
+        <v>8.46645</v>
+      </c>
+      <c r="AD92">
+        <v>8.4800719999999998</v>
+      </c>
+      <c r="AE92">
+        <v>8.4942320000000002</v>
+      </c>
+      <c r="AF92">
+        <v>8.5089380000000006</v>
+      </c>
+      <c r="AG92" s="9">
+        <v>7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>49</v>
+      </c>
+      <c r="B93" t="s">
+        <v>476</v>
+      </c>
+      <c r="C93" t="s">
+        <v>475</v>
+      </c>
+      <c r="D93" t="s">
+        <v>103</v>
+      </c>
+      <c r="F93">
+        <v>215.237167</v>
+      </c>
+      <c r="G93">
+        <v>245.48928799999999</v>
+      </c>
+      <c r="H93">
+        <v>276.03103599999997</v>
+      </c>
+      <c r="I93">
+        <v>304.35891700000002</v>
+      </c>
+      <c r="J93">
+        <v>333.28131100000002</v>
+      </c>
+      <c r="K93">
+        <v>362.58169600000002</v>
+      </c>
+      <c r="L93">
+        <v>394.29165599999999</v>
+      </c>
+      <c r="M93">
+        <v>428.57952899999998</v>
+      </c>
+      <c r="N93">
+        <v>462.50058000000001</v>
+      </c>
+      <c r="O93">
+        <v>496.79501299999998</v>
+      </c>
+      <c r="P93">
+        <v>530.52252199999998</v>
+      </c>
+      <c r="Q93">
+        <v>556.65875200000005</v>
+      </c>
+      <c r="R93">
+        <v>583.58892800000001</v>
+      </c>
+      <c r="S93">
+        <v>610.72485400000005</v>
+      </c>
+      <c r="T93">
+        <v>639.18493699999999</v>
+      </c>
+      <c r="U93">
+        <v>667.76824999999997</v>
+      </c>
+      <c r="V93">
+        <v>696.88391100000001</v>
+      </c>
+      <c r="W93">
+        <v>726.14581299999998</v>
+      </c>
+      <c r="X93">
+        <v>756.23040800000001</v>
+      </c>
+      <c r="Y93">
+        <v>786.65295400000002</v>
+      </c>
+      <c r="Z93">
+        <v>817.50421100000005</v>
+      </c>
+      <c r="AA93">
+        <v>849.38879399999996</v>
+      </c>
+      <c r="AB93">
+        <v>881.90948500000002</v>
+      </c>
+      <c r="AC93">
+        <v>915.37158199999999</v>
+      </c>
+      <c r="AD93">
+        <v>949.59020999999996</v>
+      </c>
+      <c r="AE93">
+        <v>984.56091300000003</v>
+      </c>
+      <c r="AF93">
+        <v>1019.897339</v>
+      </c>
+      <c r="AG93" s="9">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D70599EA-D981-4346-8208-F8655DA9ABC5}">
   <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17631,49 +24866,49 @@
       <c r="A2" t="s">
         <v>466</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="16">
         <f>'Table 21'!F187</f>
         <v>25.940821</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="16">
         <f>'Table 21'!G187</f>
         <v>28.426915999999999</v>
       </c>
       <c r="E2">
-        <f>'Table 21'!H187</f>
-        <v>31.317519999999998</v>
+        <f>Table_21._Residential_Sector_Eq!F78</f>
+        <v>41.307827000000003</v>
       </c>
       <c r="F2">
-        <f>'Table 21'!I187</f>
-        <v>34.213085</v>
+        <f>Table_21._Residential_Sector_Eq!G78</f>
+        <v>47.377986999999997</v>
       </c>
       <c r="G2">
-        <f>'Table 21'!J187</f>
-        <v>37.102398000000001</v>
+        <f>Table_21._Residential_Sector_Eq!H78</f>
+        <v>53.527718</v>
       </c>
       <c r="H2">
-        <f>'Table 21'!K187</f>
-        <v>40.088000999999998</v>
+        <f>Table_21._Residential_Sector_Eq!I78</f>
+        <v>59.344631</v>
       </c>
       <c r="I2">
-        <f>'Table 21'!L187</f>
-        <v>43.162284999999997</v>
+        <f>Table_21._Residential_Sector_Eq!J78</f>
+        <v>65.296081999999998</v>
       </c>
       <c r="J2">
-        <f>'Table 21'!M187</f>
-        <v>46.379024999999999</v>
+        <f>Table_21._Residential_Sector_Eq!K78</f>
+        <v>71.340698000000003</v>
       </c>
       <c r="K2">
-        <f>'Table 21'!N187</f>
-        <v>49.715114999999997</v>
+        <f>Table_21._Residential_Sector_Eq!L78</f>
+        <v>77.804955000000007</v>
       </c>
       <c r="L2">
-        <f>'Table 21'!O187</f>
-        <v>53.221054000000002</v>
+        <f>Table_21._Residential_Sector_Eq!M78</f>
+        <v>84.770461999999995</v>
       </c>
       <c r="M2">
-        <f>'Table 21'!P187</f>
-        <v>56.974155000000003</v>
+        <f>Table_21._Residential_Sector_Eq!N78</f>
+        <v>91.686965999999998</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -17738,39 +24973,39 @@
       </c>
       <c r="E5">
         <f t="shared" ref="E5:M5" si="0">E2-D2</f>
-        <v>2.8906039999999997</v>
+        <v>12.880911000000005</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>2.8955650000000013</v>
+        <v>6.0701599999999942</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>2.8893130000000014</v>
+        <v>6.1497310000000027</v>
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>2.9856029999999976</v>
+        <v>5.8169129999999996</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>3.0742839999999987</v>
+        <v>5.9514509999999987</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>3.2167400000000015</v>
+        <v>6.0446160000000049</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>3.3360899999999987</v>
+        <v>6.4642570000000035</v>
       </c>
       <c r="L5">
         <f t="shared" si="0"/>
-        <v>3.505939000000005</v>
+        <v>6.9655069999999881</v>
       </c>
       <c r="M5">
         <f t="shared" si="0"/>
-        <v>3.7531010000000009</v>
+        <v>6.9165040000000033</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -17838,39 +25073,39 @@
       </c>
       <c r="E8">
         <f t="shared" si="2"/>
-        <v>661.21197668582363</v>
+        <v>8784.1491990609593</v>
       </c>
       <c r="F8">
         <f t="shared" si="2"/>
-        <v>619.0699447907383</v>
+        <v>3200.2754964785818</v>
       </c>
       <c r="G8">
         <f t="shared" si="2"/>
-        <v>582.27799141909122</v>
+        <v>3233.2646660730225</v>
       </c>
       <c r="H8">
         <f t="shared" si="2"/>
-        <v>587.38577155347048</v>
+        <v>2889.4725229498936</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>550.85563053508963</v>
+        <v>2890.2278759815399</v>
       </c>
       <c r="J8">
         <f t="shared" si="2"/>
-        <v>560.02963296365431</v>
+        <v>2859.3242613130456</v>
       </c>
       <c r="K8">
         <f t="shared" si="2"/>
-        <v>573.55931482230824</v>
+        <v>3117.015102728084</v>
       </c>
       <c r="L8">
         <f t="shared" si="2"/>
-        <v>591.4243490650066</v>
+        <v>3404.3362726463092</v>
       </c>
       <c r="M8">
         <f t="shared" si="2"/>
-        <v>666.12461717801534</v>
+        <v>3238.2301568849707</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -17890,39 +25125,39 @@
       </c>
       <c r="E9">
         <f t="shared" si="3"/>
-        <v>152.00502331417434</v>
+        <v>2019.3748009390438</v>
       </c>
       <c r="F9">
         <f t="shared" si="3"/>
-        <v>142.31705520926076</v>
+        <v>735.70650352141035</v>
       </c>
       <c r="G9">
         <f t="shared" si="3"/>
-        <v>133.85900858091213</v>
+        <v>743.29033392698216</v>
       </c>
       <c r="H9">
         <f t="shared" si="3"/>
-        <v>135.03322844653161</v>
+        <v>664.25647705010999</v>
       </c>
       <c r="I9">
         <f t="shared" si="3"/>
-        <v>126.63536946490662</v>
+        <v>664.43012401845635</v>
       </c>
       <c r="J9">
         <f t="shared" si="3"/>
-        <v>128.74436703634785</v>
+        <v>657.32573868695965</v>
       </c>
       <c r="K9">
         <f t="shared" si="3"/>
-        <v>131.85468517768916</v>
+        <v>716.56589727191817</v>
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
-        <v>135.96165093499604</v>
+        <v>782.61772735367663</v>
       </c>
       <c r="M9">
         <f t="shared" si="3"/>
-        <v>153.134382821987</v>
+        <v>744.43184311503364</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -17933,7 +25168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -18629,11 +25864,11 @@
       </c>
       <c r="E8">
         <f>-Calculations!E8</f>
-        <v>-661.21197668582363</v>
+        <v>-8784.1491990609593</v>
       </c>
       <c r="F8">
         <f>-Calculations!F8</f>
-        <v>-619.0699447907383</v>
+        <v>-3200.2754964785818</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -20331,7 +27566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -21028,11 +28263,11 @@
       </c>
       <c r="E8">
         <f>-Calculations!E9</f>
-        <v>-152.00502331417434</v>
+        <v>-2019.3748009390438</v>
       </c>
       <c r="F8">
         <f>-Calculations!F9</f>
-        <v>-142.31705520926076</v>
+        <v>-735.70650352141035</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -22730,7 +29965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>

--- a/InputData/bldgs/CiDESCTY/Change in Distribued Electricity Source Capacities This Year.xlsx
+++ b/InputData/bldgs/CiDESCTY/Change in Distribued Electricity Source Capacities This Year.xlsx
@@ -1,28 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\bldgs\CiDESCTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BAE7ED-9CDA-48AB-83E7-111DCB24A6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1F5186-8B76-440D-AA12-E7A5709BB92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="905" xr2:uid="{EAFC2935-000E-413A-B5D2-814429F7674A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="CiDESCTY-urban-residential" sheetId="6" r:id="rId2"/>
-    <sheet name="CiDESCTY-rural-residential" sheetId="10" r:id="rId3"/>
-    <sheet name="CiDESCTY-commercial" sheetId="7" r:id="rId4"/>
+    <sheet name="REPEAT dist solar data" sheetId="11" r:id="rId2"/>
+    <sheet name="CiDESCTY-urban-residential" sheetId="6" r:id="rId3"/>
+    <sheet name="CiDESCTY-rural-residential" sheetId="10" r:id="rId4"/>
+    <sheet name="CiDESCTY-commercial" sheetId="7" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="billion_kw_to_MW">About!$B$13</definedName>
-    <definedName name="gigwatt_to_megawatt">About!$B$14</definedName>
-    <definedName name="Percent_rural">About!$A$11</definedName>
-    <definedName name="Percent_Urban">About!$A$10</definedName>
+    <definedName name="billion_kw_to_MW" localSheetId="1">#REF!</definedName>
+    <definedName name="billion_kw_to_MW">About!$B$22</definedName>
+    <definedName name="CH4_to_CO2e">'[2]Cross-Page Data'!$C$12</definedName>
+    <definedName name="cpi_2010to2012">#REF!</definedName>
+    <definedName name="cpi_2013to2012">#REF!</definedName>
+    <definedName name="cpi_2014to2012">#REF!</definedName>
+    <definedName name="cpi_2016to2012">#REF!</definedName>
+    <definedName name="dollars_2020_2012">[4]About!$A$113</definedName>
+    <definedName name="dollars_2022_2012">[4]About!$A$111</definedName>
+    <definedName name="gigwatt_to_megawatt" localSheetId="1">#REF!</definedName>
+    <definedName name="gigwatt_to_megawatt">About!$B$23</definedName>
+    <definedName name="gigwatts_to_megawatts">[5]About!$A$31</definedName>
+    <definedName name="Google_Sheet_Link_1041556874" localSheetId="1" hidden="1">'REPEAT dist solar data'!gigwatt_to_megawatt</definedName>
+    <definedName name="Google_Sheet_Link_1041556874" hidden="1">gigwatt_to_megawatt</definedName>
+    <definedName name="Google_Sheet_Link_1113742247" localSheetId="1" hidden="1">'REPEAT dist solar data'!Percent_rural</definedName>
+    <definedName name="Google_Sheet_Link_1113742247" hidden="1">Percent_rural</definedName>
+    <definedName name="Google_Sheet_Link_27960059" localSheetId="1" hidden="1">'REPEAT dist solar data'!Percent_Urban</definedName>
+    <definedName name="Google_Sheet_Link_27960059" hidden="1">Percent_Urban</definedName>
+    <definedName name="Google_Sheet_Link_678979968" localSheetId="1" hidden="1">'REPEAT dist solar data'!billion_kw_to_MW</definedName>
+    <definedName name="Google_Sheet_Link_678979968" hidden="1">billion_kw_to_MW</definedName>
+    <definedName name="N2O_to_CO2e">'[2]Cross-Page Data'!$C$13</definedName>
+    <definedName name="Percent_rural" localSheetId="1">#REF!</definedName>
+    <definedName name="Percent_rural">About!$A$20</definedName>
+    <definedName name="Percent_Urban" localSheetId="1">#REF!</definedName>
+    <definedName name="Percent_Urban">About!$A$19</definedName>
+    <definedName name="unit_conv">[6]About!$A$123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="131">
   <si>
     <t>nuclear</t>
   </si>
@@ -128,10 +159,310 @@
     <t>This file can be used to test an alternate distributed solar additions schedule.</t>
   </si>
   <si>
-    <t>By default, we do not use this in the U.S. model.</t>
-  </si>
-  <si>
-    <t>None</t>
+    <t>res v commercial breakdown</t>
+  </si>
+  <si>
+    <t>Energy Information Administration</t>
+  </si>
+  <si>
+    <t>Annual Electric Power Industry Report, Form EIA-861 detailed data files</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/electricity/data/eia861/</t>
+  </si>
+  <si>
+    <t>Net_metering_2022</t>
+  </si>
+  <si>
+    <t>Urban vs. Rural Residential Households</t>
+  </si>
+  <si>
+    <t>Residential Energy Consumption Survey (RECS)</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/consumption/residential/data/2015/hc/hc2.1.xlsx</t>
+  </si>
+  <si>
+    <t>Table HC2.1</t>
+  </si>
+  <si>
+    <t>states</t>
+  </si>
+  <si>
+    <t>REPEAT Model</t>
+  </si>
+  <si>
+    <t>Princeton University</t>
+  </si>
+  <si>
+    <t>IRA mid and Frozen Scenarios</t>
+  </si>
+  <si>
+    <t>https://repeatproject.org/results?comparison=benchmark&amp;state=national&amp;page=1&amp;limit=25</t>
+  </si>
+  <si>
+    <t>By default, this is configured to add distributed solar in the NDC scenario,</t>
+  </si>
+  <si>
+    <t>which applies the same rate of distributed solar adoption expected from IRA</t>
+  </si>
+  <si>
+    <t>tax credits (starting in 2030 and running through 2050).</t>
+  </si>
+  <si>
+    <t>REPEAT Data</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t>subcategories</t>
+  </si>
+  <si>
+    <t>variables</t>
+  </si>
+  <si>
+    <t>units</t>
+  </si>
+  <si>
+    <t>frozen_pol_2024</t>
+  </si>
+  <si>
+    <t>frozen_pol_2026</t>
+  </si>
+  <si>
+    <t>frozen_pol_2028</t>
+  </si>
+  <si>
+    <t>frozen_pol_2030</t>
+  </si>
+  <si>
+    <t>frozen_pol_2032</t>
+  </si>
+  <si>
+    <t>frozen_pol_2035</t>
+  </si>
+  <si>
+    <t>frozen_pol_2040</t>
+  </si>
+  <si>
+    <t>frozen_pol_2050</t>
+  </si>
+  <si>
+    <t>ira-mid_pol_2024</t>
+  </si>
+  <si>
+    <t>ira-mid_pol_2026</t>
+  </si>
+  <si>
+    <t>ira-mid_pol_2028</t>
+  </si>
+  <si>
+    <t>ira-mid_pol_2030</t>
+  </si>
+  <si>
+    <t>ira-mid_pol_2032</t>
+  </si>
+  <si>
+    <t>ira-mid_pol_2035</t>
+  </si>
+  <si>
+    <t>ira-mid_pol_2040</t>
+  </si>
+  <si>
+    <t>ira-mid_pol_2050</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Capacity by type</t>
+  </si>
+  <si>
+    <t>Capacity - Rooftop Solar</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
+    <t>US Total</t>
+  </si>
+  <si>
+    <t>No Policy</t>
+  </si>
+  <si>
+    <t>IRA Mid</t>
+  </si>
+  <si>
+    <t>No Policy Growth</t>
+  </si>
+  <si>
+    <t>IRA Mid Growth</t>
+  </si>
+  <si>
+    <t>Policy Induced Growth</t>
+  </si>
+  <si>
+    <t>Urban Rural Split</t>
+  </si>
+  <si>
+    <t>Urban</t>
+  </si>
+  <si>
+    <t>Rural</t>
+  </si>
+  <si>
+    <t>Conversion from billion kilowatthours to megawatthours</t>
+  </si>
+  <si>
+    <t>Conversion from gigawatts to megawatts</t>
   </si>
 </sst>
 </file>
@@ -143,7 +474,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,19 +658,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -514,6 +878,36 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7B7B7"/>
+        <bgColor rgb="FFB7B7B7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -680,7 +1074,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
@@ -709,48 +1103,50 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -762,8 +1158,39 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" xfId="53" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="53" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="53" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="53"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="54" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="53" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" xfId="53" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="55" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="56">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="31" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="34" builtinId="38" customBuiltin="1"/>
@@ -809,10 +1236,13 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal 3" xfId="52" xr:uid="{6D5BFB4D-1C20-4C02-A8DF-639CF758385B}"/>
+    <cellStyle name="Normal 3 2" xfId="53" xr:uid="{4C1E9A2B-E5B0-4261-83E8-F390C3F3DF18}"/>
     <cellStyle name="Note" xfId="24" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="19" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Parent row" xfId="4" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Percent" xfId="8" builtinId="5"/>
+    <cellStyle name="Percent 2" xfId="54" xr:uid="{E7E9704A-4386-42B8-A0D5-7EF3A707C8A4}"/>
+    <cellStyle name="Percent 2 2" xfId="55" xr:uid="{E5E866C2-4D2D-4616-ADBB-140C7BB153D0}"/>
     <cellStyle name="Table title" xfId="3" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Title" xfId="11" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="26" builtinId="25" customBuiltin="1"/>
@@ -829,6 +1259,462 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="REPEAT DATA"/>
+      <sheetName val="States"/>
+      <sheetName val="res v com"/>
+      <sheetName val="calcs"/>
+      <sheetName val="CiDESCTY-urban-residential"/>
+      <sheetName val="CiDESCTY-rural-residential"/>
+      <sheetName val="CiDESCTY-commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Cross-Page Data"/>
+      <sheetName val="Non-Energy FF CO2 Emissions"/>
+      <sheetName val="Cement CO2 Emissions"/>
+      <sheetName val="Iron and Steel"/>
+      <sheetName val="Coal Mining"/>
+      <sheetName val="Natural Gas Systems"/>
+      <sheetName val="Petroleum Systems"/>
+      <sheetName val="Chem - HCFC 22 Production"/>
+      <sheetName val="Chem - ODS"/>
+      <sheetName val="Other - Aluminum"/>
+      <sheetName val="Other - Magnesium"/>
+      <sheetName val="Other - Semiconductor Mfg"/>
+      <sheetName val="Other - Elec Trans and Dist"/>
+      <sheetName val="Agriculture - EF &amp; Manure Mgmt"/>
+      <sheetName val="Agriculture - Rice Cultivation"/>
+      <sheetName val="Agriculture - Soil Mgmt"/>
+      <sheetName val="Waste - Landfills"/>
+      <sheetName val="Waste - Water Treatment"/>
+      <sheetName val="Other Industrial Processes"/>
+      <sheetName val="Combined Data"/>
+      <sheetName val="BPEiC-CO2"/>
+      <sheetName val="BPEiC-CH4"/>
+      <sheetName val="BPEiC-N2O"/>
+      <sheetName val="BPEiC-F-gases"/>
+      <sheetName val="EPA (2017) Table A3.6-1"/>
+      <sheetName val="EPA (2017) Table A3.6-7"/>
+      <sheetName val="EPA (2017) Table A3.6-10"/>
+      <sheetName val="AEO 2017_Table 6"/>
+      <sheetName val="AEO 2017_Table 11"/>
+      <sheetName val="AEO 2017_Table 13"/>
+      <sheetName val="AEO 2017_Table 15"/>
+      <sheetName val="AEO 2017_Table 19"/>
+      <sheetName val="AEO 2017_Table 20"/>
+      <sheetName val="AEO 2017_Table 24"/>
+      <sheetName val="AEO 2017_Table 62"/>
+      <sheetName val="AEO 2016_Table 6"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="12">
+          <cell r="C12">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>265</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Transport Refrigeration</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NDC-orig"/>
+      <sheetName val="guidance"/>
+      <sheetName val="ndc new"/>
+      <sheetName val="fopity"/>
+      <sheetName val="calcs&gt;"/>
+      <sheetName val="REPEAT dist solar data"/>
+      <sheetName val="coal retire"/>
+      <sheetName val="ces"/>
+      <sheetName val="elec tax credits"/>
+      <sheetName val="vehicle tax credits"/>
+      <sheetName val="building retrofit"/>
+      <sheetName val="ZEV std"/>
+      <sheetName val="Indst Fuel Switching"/>
+      <sheetName val="BAU Data"/>
+      <sheetName val="Boilers"/>
+      <sheetName val="Nonboiler Low Temp"/>
+      <sheetName val="Nonboiler Med Temp"/>
+      <sheetName val="Nonboiler High Temp"/>
+      <sheetName val="Cooling"/>
+      <sheetName val="Machine Drive"/>
+      <sheetName val="Other Processes"/>
+      <sheetName val="4.1-indst-IESD"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="AEO 2023 Table 2"/>
+      <sheetName val="AEO 2022 Table 2"/>
+      <sheetName val="Gas Futures"/>
+      <sheetName val="Henry Hub Historicals"/>
+      <sheetName val="NG Sector Price Historicals"/>
+      <sheetName val="Historical Monthly Gas Cons"/>
+      <sheetName val="NG Calcs"/>
+      <sheetName val="AEO 2023 Table 3"/>
+      <sheetName val="AEO 2022 Table 3"/>
+      <sheetName val="AEO 2023 Table 12"/>
+      <sheetName val="AEO 2022 Table 12"/>
+      <sheetName val="AEO 2023 Table 57"/>
+      <sheetName val="AEO 2022 Table 57"/>
+      <sheetName val="AEO Table 57"/>
+      <sheetName val="STEO"/>
+      <sheetName val="Hard Coal and Lig Multipliers"/>
+      <sheetName val="Hydrogen"/>
+      <sheetName val="Transp Charging"/>
+      <sheetName val="Other Fuels"/>
+      <sheetName val="Inflation Reduction Act"/>
+      <sheetName val="Tax Percentages"/>
+      <sheetName val="Pretax &gt;"/>
+      <sheetName val="BFPaT-pretax-electricity"/>
+      <sheetName val="BFPaT-pretax-coal"/>
+      <sheetName val="BFPaT-pretax-natgas"/>
+      <sheetName val="BFPaT-pretax-nuclear"/>
+      <sheetName val="BFPaT-pretax-hydro"/>
+      <sheetName val="BFPaT-pretax-wind"/>
+      <sheetName val="BFPaT-pretax-solar"/>
+      <sheetName val="BFPaT-pretax-biomass"/>
+      <sheetName val="BFPaT-pretax-petgas"/>
+      <sheetName val="BFPaT-pretax-petdies"/>
+      <sheetName val="BFPaT-pretax-biogas"/>
+      <sheetName val="BFPaT-pretax-biodies"/>
+      <sheetName val="BFPaT-pretax-jetkerosene"/>
+      <sheetName val="BFPaT-pretax-heat"/>
+      <sheetName val="BFPaT-pretax-geothermal"/>
+      <sheetName val="BFPaT-pretax-lignite"/>
+      <sheetName val="BFPaT-pretax-crude"/>
+      <sheetName val="BFPaT-pretax-heavyfueloil"/>
+      <sheetName val="BFPaT-pretax-lpgpropbut"/>
+      <sheetName val="BFPaT-pretax-msw"/>
+      <sheetName val="BFPaT-pretax-hydrogen"/>
+      <sheetName val="Summary_pretax"/>
+      <sheetName val="Fuel Tax &gt;"/>
+      <sheetName val="BFPaT-fueltax-electricity"/>
+      <sheetName val="BFPaT-fueltax-coal"/>
+      <sheetName val="BFPaT-fueltax-natgas"/>
+      <sheetName val="BFPaT-fueltax-nuclear"/>
+      <sheetName val="BFPaT-fueltax-hydro"/>
+      <sheetName val="BFPaT-fueltax-wind"/>
+      <sheetName val="BFPaT-fueltax-solar"/>
+      <sheetName val="BFPaT-fueltax-biomass"/>
+      <sheetName val="BFPaT-fueltax-petgas"/>
+      <sheetName val="BFPaT-fueltax-petdies"/>
+      <sheetName val="BFPaT-fueltax-biogas"/>
+      <sheetName val="BFPaT-fueltax-biodies"/>
+      <sheetName val="BFPaT-fueltax-jetkerosene"/>
+      <sheetName val="BFPaT-fueltax-heat"/>
+      <sheetName val="BFPaT-fueltax-geothermal"/>
+      <sheetName val="BFPaT-fueltax-lignite"/>
+      <sheetName val="BFPaT-fueltax-crude"/>
+      <sheetName val="BFPaT-fueltax-heavyfueloil"/>
+      <sheetName val="BFPaT-fueltax-lpgpropbut"/>
+      <sheetName val="BFPaT-fueltax-msw"/>
+      <sheetName val="BFPaT-fueltax-hydrogen"/>
+      <sheetName val="Summary_tax"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="113">
+          <cell r="A113" t="str">
+            <v>The EIA SEDS document reports dollars that are not adjusted for inflation (according to associated technical notes document).  We</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16">
+        <row r="15">
+          <cell r="N15">
+            <v>0.92062879123815489</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18">
+        <row r="1">
+          <cell r="D1" t="str">
+            <v>Hydrogen ($/kg)</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+      <sheetData sheetId="48"/>
+      <sheetData sheetId="49"/>
+      <sheetData sheetId="50"/>
+      <sheetData sheetId="51"/>
+      <sheetData sheetId="52"/>
+      <sheetData sheetId="53"/>
+      <sheetData sheetId="54"/>
+      <sheetData sheetId="55"/>
+      <sheetData sheetId="56"/>
+      <sheetData sheetId="57"/>
+      <sheetData sheetId="58"/>
+      <sheetData sheetId="59"/>
+      <sheetData sheetId="60"/>
+      <sheetData sheetId="61"/>
+      <sheetData sheetId="62"/>
+      <sheetData sheetId="63"/>
+      <sheetData sheetId="64"/>
+      <sheetData sheetId="65"/>
+      <sheetData sheetId="66"/>
+      <sheetData sheetId="67"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="2035 Report Deployment"/>
+      <sheetName val="2035 Report Data"/>
+      <sheetName val="EPS Output"/>
+      <sheetName val="AEO Table 9"/>
+      <sheetName val="AEO Table 9 (2019)"/>
+      <sheetName val="AEO Table 16"/>
+      <sheetName val="BGBSC"/>
+      <sheetName val="PAGBSC"/>
+      <sheetName val="SYGBSC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="31">
+          <cell r="A31">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Country Selector"/>
+      <sheetName val="Multipliers and Adjustments"/>
+      <sheetName val="EPA Data"/>
+      <sheetName val="Tech to Policy Mapping"/>
+      <sheetName val="SNAP Adjustment"/>
+      <sheetName val="Cement Data"/>
+      <sheetName val="Data Check"/>
+      <sheetName val="PERAC-cement"/>
+      <sheetName val="PERAC-ngps-mthncptr"/>
+      <sheetName val="PERAC-ngps-mthndstr"/>
+      <sheetName val="PERAC-fgassubstitution"/>
+      <sheetName val="PERAC-fgasdestruction"/>
+      <sheetName val="PERAC-fgasrecovery"/>
+      <sheetName val="PERAC-inspctmaintretrofit"/>
+      <sheetName val="PERAC-coalmining-mthncptr"/>
+      <sheetName val="PERAC-coalmining-mthndstr"/>
+      <sheetName val="PERAC-waste-mthncptr"/>
+      <sheetName val="PERAC-waste-mthndstr"/>
+      <sheetName val="PERAC-cropsrice"/>
+      <sheetName val="PERAC-livestock"/>
+      <sheetName val="PERAC-MCD"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="123">
+          <cell r="A123">
+            <v>1000000000000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1118,7 +2004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.1796875" customWidth="1"/>
@@ -1127,51 +2013,181 @@
     <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="11">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="11">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B17" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F14" s="7"/>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="27"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="28">
+        <v>0.80118443316412857</v>
+      </c>
+      <c r="B30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="28">
+        <v>0.1988155668358714</v>
+      </c>
+      <c r="B31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="27"/>
+      <c r="B32" s="27"/>
+    </row>
+    <row r="33" spans="1:2" ht="56.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34">
+        <v>1000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1180,6 +2196,3905 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE4F9B22-CE90-4FE0-93FE-AB7B4D55A19F}">
+  <dimension ref="A1:AH60"/>
+  <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="9.81640625" style="19"/>
+    <col min="4" max="4" width="14.453125" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.36328125" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.81640625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" s="17" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="D2" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="V2" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="W2" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y2" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D3" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J3" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K3" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L3" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M3" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N3" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="O3" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="P3" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="S3" s="19">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="T3" s="19">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="U3" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="V3" s="19">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="W3" s="19">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="X3" s="19">
+        <v>0.108</v>
+      </c>
+      <c r="Y3" s="19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D4" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="J4" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="K4" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="L4" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="M4" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="N4" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="O4" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="P4" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="19">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="S4" s="19">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="T4" s="19">
+        <v>5.36</v>
+      </c>
+      <c r="U4" s="19">
+        <v>5.88</v>
+      </c>
+      <c r="V4" s="19">
+        <v>6.37</v>
+      </c>
+      <c r="W4" s="19">
+        <v>6.57</v>
+      </c>
+      <c r="X4" s="19">
+        <v>6.83</v>
+      </c>
+      <c r="Y4" s="19">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" s="19">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J5" s="19">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K5" s="19">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L5" s="19">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M5" s="19">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="N5" s="19">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="O5" s="19">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="P5" s="19">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="S5" s="19">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="T5" s="19">
+        <v>0.113</v>
+      </c>
+      <c r="U5" s="19">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="V5" s="19">
+        <v>0.214</v>
+      </c>
+      <c r="W5" s="19">
+        <v>0.254</v>
+      </c>
+      <c r="X5" s="19">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="Y5" s="19">
+        <v>0.373</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D6" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="J6" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="K6" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="L6" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="M6" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="N6" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="O6" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="P6" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="19">
+        <v>28.4</v>
+      </c>
+      <c r="S6" s="19">
+        <v>31.4</v>
+      </c>
+      <c r="T6" s="19">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="U6" s="19">
+        <v>35.1</v>
+      </c>
+      <c r="V6" s="19">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="W6" s="19">
+        <v>37.9</v>
+      </c>
+      <c r="X6" s="19">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="Y6" s="19">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D7" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="J7" s="19">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="K7" s="19">
+        <v>0.72</v>
+      </c>
+      <c r="L7" s="19">
+        <v>0.72</v>
+      </c>
+      <c r="M7" s="19">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="N7" s="19">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="O7" s="19">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="P7" s="19">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="19">
+        <v>1.64</v>
+      </c>
+      <c r="S7" s="19">
+        <v>1.93</v>
+      </c>
+      <c r="T7" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="U7" s="19">
+        <v>2.54</v>
+      </c>
+      <c r="V7" s="19">
+        <v>2.88</v>
+      </c>
+      <c r="W7" s="19">
+        <v>3.3</v>
+      </c>
+      <c r="X7" s="19">
+        <v>3.86</v>
+      </c>
+      <c r="Y7" s="19">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D8" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="J8" s="19">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="K8" s="19">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="L8" s="19">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="M8" s="19">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="N8" s="19">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="O8" s="19">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="P8" s="19">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="19">
+        <v>1.38</v>
+      </c>
+      <c r="S8" s="19">
+        <v>1.51</v>
+      </c>
+      <c r="T8" s="19">
+        <v>1.58</v>
+      </c>
+      <c r="U8" s="19">
+        <v>1.64</v>
+      </c>
+      <c r="V8" s="19">
+        <v>1.7</v>
+      </c>
+      <c r="W8" s="19">
+        <v>1.75</v>
+      </c>
+      <c r="X8" s="19">
+        <v>1.8</v>
+      </c>
+      <c r="Y8" s="19">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D9" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="J9" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="K9" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="L9" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="M9" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="N9" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="O9" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="P9" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="19">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="S9" s="19">
+        <v>0.39</v>
+      </c>
+      <c r="T9" s="19">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="U9" s="19">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="V9" s="19">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="W9" s="19">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="X9" s="19">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="Y9" s="19">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D10" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="19">
+        <v>1.08</v>
+      </c>
+      <c r="J10" s="19">
+        <v>1.08</v>
+      </c>
+      <c r="K10" s="19">
+        <v>1.08</v>
+      </c>
+      <c r="L10" s="19">
+        <v>1.08</v>
+      </c>
+      <c r="M10" s="19">
+        <v>1.08</v>
+      </c>
+      <c r="N10" s="19">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="O10" s="19">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="P10" s="19">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="19">
+        <v>3.22</v>
+      </c>
+      <c r="S10" s="19">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="T10" s="19">
+        <v>7.13</v>
+      </c>
+      <c r="U10" s="19">
+        <v>10.1</v>
+      </c>
+      <c r="V10" s="19">
+        <v>12.8</v>
+      </c>
+      <c r="W10" s="19">
+        <v>13.2</v>
+      </c>
+      <c r="X10" s="19">
+        <v>13.7</v>
+      </c>
+      <c r="Y10" s="19">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D11" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="19">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="J11" s="19">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="K11" s="19">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="L11" s="19">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="M11" s="19">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="N11" s="19">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="O11" s="19">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="P11" s="19">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="19">
+        <v>0.318</v>
+      </c>
+      <c r="S11" s="19">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="T11" s="19">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="U11" s="19">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="V11" s="19">
+        <v>1.56</v>
+      </c>
+      <c r="W11" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="X11" s="19">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Y11" s="19">
+        <v>4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D12" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="19">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="J12" s="19">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="K12" s="19">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="L12" s="19">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="M12" s="19">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="N12" s="19">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="O12" s="19">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="P12" s="19">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="19">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="S12" s="19">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="T12" s="19">
+        <v>0.104</v>
+      </c>
+      <c r="U12" s="19">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="V12" s="19">
+        <v>0.13</v>
+      </c>
+      <c r="W12" s="19">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="X12" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="Y12" s="19">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D13" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="19">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="J13" s="19">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="K13" s="19">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="L13" s="19">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="M13" s="19">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="N13" s="19">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="O13" s="19">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="P13" s="19">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="19">
+        <v>0.98699999999999999</v>
+      </c>
+      <c r="S13" s="19">
+        <v>1.26</v>
+      </c>
+      <c r="T13" s="19">
+        <v>1.66</v>
+      </c>
+      <c r="U13" s="19">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="V13" s="19">
+        <v>2.77</v>
+      </c>
+      <c r="W13" s="19">
+        <v>3.64</v>
+      </c>
+      <c r="X13" s="19">
+        <v>5.16</v>
+      </c>
+      <c r="Y13" s="19">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D14" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="J14" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="K14" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="L14" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="M14" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="N14" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="O14" s="19">
+        <v>0.151</v>
+      </c>
+      <c r="P14" s="19">
+        <v>0.152</v>
+      </c>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="19">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="S14" s="19">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="T14" s="19">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="U14" s="19">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="V14" s="19">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="W14" s="19">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="X14" s="19">
+        <v>1.63</v>
+      </c>
+      <c r="Y14" s="19">
+        <v>2.3199999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D15" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="19">
+        <v>0.186</v>
+      </c>
+      <c r="J15" s="19">
+        <v>0.186</v>
+      </c>
+      <c r="K15" s="19">
+        <v>0.186</v>
+      </c>
+      <c r="L15" s="19">
+        <v>0.187</v>
+      </c>
+      <c r="M15" s="19">
+        <v>0.187</v>
+      </c>
+      <c r="N15" s="19">
+        <v>0.188</v>
+      </c>
+      <c r="O15" s="19">
+        <v>0.189</v>
+      </c>
+      <c r="P15" s="19">
+        <v>0.19</v>
+      </c>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="19">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="S15" s="19">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="T15" s="19">
+        <v>1.19</v>
+      </c>
+      <c r="U15" s="19">
+        <v>1.51</v>
+      </c>
+      <c r="V15" s="19">
+        <v>1.88</v>
+      </c>
+      <c r="W15" s="19">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="X15" s="19">
+        <v>2.74</v>
+      </c>
+      <c r="Y15" s="19">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D16" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="19">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="J16" s="19">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="K16" s="19">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="L16" s="19">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M16" s="19">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="N16" s="19">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="O16" s="19">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="P16" s="19">
+        <v>3.9E-2</v>
+      </c>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="19">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="S16" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="T16" s="19">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="U16" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="V16" s="19">
+        <v>0.187</v>
+      </c>
+      <c r="W16" s="19">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="X16" s="19">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="Y16" s="19">
+        <v>0.59099999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D17" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="19">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J17" s="19">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K17" s="19">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="L17" s="19">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="M17" s="19">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="N17" s="19">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="O17" s="19">
+        <v>2.7E-2</v>
+      </c>
+      <c r="P17" s="19">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="19">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="S17" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="T17" s="19">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="U17" s="19">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="V17" s="19">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="W17" s="19">
+        <v>0.375</v>
+      </c>
+      <c r="X17" s="19">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="Y17" s="19">
+        <v>0.94099999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D18" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="19">
+        <v>0.253</v>
+      </c>
+      <c r="J18" s="19">
+        <v>0.253</v>
+      </c>
+      <c r="K18" s="19">
+        <v>0.253</v>
+      </c>
+      <c r="L18" s="19">
+        <v>0.255</v>
+      </c>
+      <c r="M18" s="19">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="N18" s="19">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="O18" s="19">
+        <v>0.26</v>
+      </c>
+      <c r="P18" s="19">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="19">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="S18" s="19">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="T18" s="19">
+        <v>1.18</v>
+      </c>
+      <c r="U18" s="19">
+        <v>1.77</v>
+      </c>
+      <c r="V18" s="19">
+        <v>2.23</v>
+      </c>
+      <c r="W18" s="19">
+        <v>2.66</v>
+      </c>
+      <c r="X18" s="19">
+        <v>3.1</v>
+      </c>
+      <c r="Y18" s="19">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D19" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J19" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K19" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="L19" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="M19" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="N19" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="O19" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P19" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="S19" s="19">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="T19" s="19">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="U19" s="19">
+        <v>0.184</v>
+      </c>
+      <c r="V19" s="19">
+        <v>0.19</v>
+      </c>
+      <c r="W19" s="19">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="X19" s="19">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="Y19" s="19">
+        <v>0.20799999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D20" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="19">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="J20" s="19">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="K20" s="19">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="L20" s="19">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="M20" s="19">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="N20" s="19">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="O20" s="19">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="P20" s="19">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="19">
+        <v>2.74</v>
+      </c>
+      <c r="S20" s="19">
+        <v>3.43</v>
+      </c>
+      <c r="T20" s="19">
+        <v>4.21</v>
+      </c>
+      <c r="U20" s="19">
+        <v>5.23</v>
+      </c>
+      <c r="V20" s="19">
+        <v>6.26</v>
+      </c>
+      <c r="W20" s="19">
+        <v>7.07</v>
+      </c>
+      <c r="X20" s="19">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="Y20" s="19">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D21" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="J21" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="K21" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="L21" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="M21" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="N21" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="O21" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="P21" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="19">
+        <v>5.32</v>
+      </c>
+      <c r="S21" s="19">
+        <v>5.84</v>
+      </c>
+      <c r="T21" s="19">
+        <v>6.11</v>
+      </c>
+      <c r="U21" s="19">
+        <v>6.35</v>
+      </c>
+      <c r="V21" s="19">
+        <v>6.58</v>
+      </c>
+      <c r="W21" s="19">
+        <v>6.76</v>
+      </c>
+      <c r="X21" s="19">
+        <v>6.94</v>
+      </c>
+      <c r="Y21" s="19">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D22" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" s="19">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="J22" s="19">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="K22" s="19">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="L22" s="19">
+        <v>0.182</v>
+      </c>
+      <c r="M22" s="19">
+        <v>0.182</v>
+      </c>
+      <c r="N22" s="19">
+        <v>0.183</v>
+      </c>
+      <c r="O22" s="19">
+        <v>0.183</v>
+      </c>
+      <c r="P22" s="19">
+        <v>0.186</v>
+      </c>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="19">
+        <v>0.437</v>
+      </c>
+      <c r="S22" s="19">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="T22" s="19">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="U22" s="19">
+        <v>1.48</v>
+      </c>
+      <c r="V22" s="19">
+        <v>2.15</v>
+      </c>
+      <c r="W22" s="19">
+        <v>3.03</v>
+      </c>
+      <c r="X22" s="19">
+        <v>4.04</v>
+      </c>
+      <c r="Y22" s="19">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D23" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="J23" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="K23" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="L23" s="19">
+        <v>0.129</v>
+      </c>
+      <c r="M23" s="19">
+        <v>0.129</v>
+      </c>
+      <c r="N23" s="19">
+        <v>0.129</v>
+      </c>
+      <c r="O23" s="19">
+        <v>0.13</v>
+      </c>
+      <c r="P23" s="19">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="19">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="S23" s="19">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="T23" s="19">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="U23" s="19">
+        <v>1.01</v>
+      </c>
+      <c r="V23" s="19">
+        <v>1.27</v>
+      </c>
+      <c r="W23" s="19">
+        <v>1.57</v>
+      </c>
+      <c r="X23" s="19">
+        <v>1.84</v>
+      </c>
+      <c r="Y23" s="19">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D24" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I24" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J24" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="K24" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="L24" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="M24" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="N24" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="O24" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="P24" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="19">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="S24" s="19">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="T24" s="19">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="U24" s="19">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="V24" s="19">
+        <v>0.09</v>
+      </c>
+      <c r="W24" s="19">
+        <v>0.113</v>
+      </c>
+      <c r="X24" s="19">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="Y24" s="19">
+        <v>0.247</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D25" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" s="19">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="J25" s="19">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="K25" s="19">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="L25" s="19">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="M25" s="19">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="N25" s="19">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="O25" s="19">
+        <v>0.37</v>
+      </c>
+      <c r="P25" s="19">
+        <v>0.374</v>
+      </c>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="19">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="S25" s="19">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="T25" s="19">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="U25" s="19">
+        <v>1.47</v>
+      </c>
+      <c r="V25" s="19">
+        <v>1.85</v>
+      </c>
+      <c r="W25" s="19">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="X25" s="19">
+        <v>3.46</v>
+      </c>
+      <c r="Y25" s="19">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D26" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="J26" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="K26" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="L26" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="M26" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="N26" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="O26" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="P26" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="19">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="S26" s="19">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="T26" s="19">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="U26" s="19">
+        <v>0.08</v>
+      </c>
+      <c r="V26" s="19">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="W26" s="19">
+        <v>0.111</v>
+      </c>
+      <c r="X26" s="19">
+        <v>0.13</v>
+      </c>
+      <c r="Y26" s="19">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D27" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I27" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="J27" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="K27" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="L27" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="M27" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="N27" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="O27" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="P27" s="19">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="19">
+        <v>5.5E-2</v>
+      </c>
+      <c r="S27" s="19">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="T27" s="19">
+        <v>7.8E-2</v>
+      </c>
+      <c r="U27" s="19">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="V27" s="19">
+        <v>0.112</v>
+      </c>
+      <c r="W27" s="19">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="X27" s="19">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="Y27" s="19">
+        <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D28" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" s="19">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="L28" s="19">
+        <v>0.59</v>
+      </c>
+      <c r="M28" s="19">
+        <v>0.59</v>
+      </c>
+      <c r="N28" s="19">
+        <v>0.59</v>
+      </c>
+      <c r="O28" s="19">
+        <v>0.59</v>
+      </c>
+      <c r="P28" s="19">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="19">
+        <v>1.3</v>
+      </c>
+      <c r="S28" s="19">
+        <v>1.48</v>
+      </c>
+      <c r="T28" s="19">
+        <v>1.64</v>
+      </c>
+      <c r="U28" s="19">
+        <v>1.84</v>
+      </c>
+      <c r="V28" s="19">
+        <v>1.99</v>
+      </c>
+      <c r="W28" s="19">
+        <v>2.11</v>
+      </c>
+      <c r="X28" s="19">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="Y28" s="19">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D29" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="J29" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="K29" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="L29" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="M29" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="N29" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="O29" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="P29" s="19">
+        <v>0.128</v>
+      </c>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="19">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="S29" s="19">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="T29" s="19">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="U29" s="19">
+        <v>0.36</v>
+      </c>
+      <c r="V29" s="19">
+        <v>0.374</v>
+      </c>
+      <c r="W29" s="19">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="X29" s="19">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="Y29" s="19">
+        <v>0.40899999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D30" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I30" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="J30" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="K30" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="L30" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="M30" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="N30" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="O30" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="P30" s="19">
+        <v>1.92</v>
+      </c>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="19">
+        <v>5.66</v>
+      </c>
+      <c r="S30" s="19">
+        <v>6.83</v>
+      </c>
+      <c r="T30" s="19">
+        <v>7.94</v>
+      </c>
+      <c r="U30" s="19">
+        <v>9.17</v>
+      </c>
+      <c r="V30" s="19">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="W30" s="19">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X30" s="19">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="Y30" s="19">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D31" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I31" s="19">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="J31" s="19">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="K31" s="19">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="L31" s="19">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="M31" s="19">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="N31" s="19">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="O31" s="19">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="P31" s="19">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="19">
+        <v>0.498</v>
+      </c>
+      <c r="S31" s="19">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="T31" s="19">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="U31" s="19">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="V31" s="19">
+        <v>1.03</v>
+      </c>
+      <c r="W31" s="19">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="X31" s="19">
+        <v>1.27</v>
+      </c>
+      <c r="Y31" s="19">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D32" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I32" s="19">
+        <v>2.19</v>
+      </c>
+      <c r="J32" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K32" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L32" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M32" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N32" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O32" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P32" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="19">
+        <v>4.7</v>
+      </c>
+      <c r="S32" s="19">
+        <v>5.48</v>
+      </c>
+      <c r="T32" s="19">
+        <v>6.23</v>
+      </c>
+      <c r="U32" s="19">
+        <v>7.1</v>
+      </c>
+      <c r="V32" s="19">
+        <v>7.89</v>
+      </c>
+      <c r="W32" s="19">
+        <v>8.73</v>
+      </c>
+      <c r="X32" s="19">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Y32" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D33" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33" s="19">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="J33" s="19">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="K33" s="19">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="L33" s="19">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="M33" s="19">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N33" s="19">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O33" s="19">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="P33" s="19">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="19">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="S33" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="T33" s="19">
+        <v>1.95</v>
+      </c>
+      <c r="U33" s="19">
+        <v>2.62</v>
+      </c>
+      <c r="V33" s="19">
+        <v>3.31</v>
+      </c>
+      <c r="W33" s="19">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="X33" s="19">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="Y33" s="19">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D34" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="19">
+        <v>0</v>
+      </c>
+      <c r="J34" s="19">
+        <v>0</v>
+      </c>
+      <c r="K34" s="19">
+        <v>0</v>
+      </c>
+      <c r="L34" s="19">
+        <v>0</v>
+      </c>
+      <c r="M34" s="19">
+        <v>0</v>
+      </c>
+      <c r="N34" s="19">
+        <v>0</v>
+      </c>
+      <c r="O34" s="19">
+        <v>0</v>
+      </c>
+      <c r="P34" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="19">
+        <v>2E-3</v>
+      </c>
+      <c r="S34" s="19">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="T34" s="19">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="U34" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="V34" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W34" s="19">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X34" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y34" s="19">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D35" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I35" s="19">
+        <v>0.114</v>
+      </c>
+      <c r="J35" s="19">
+        <v>0.114</v>
+      </c>
+      <c r="K35" s="19">
+        <v>0.114</v>
+      </c>
+      <c r="L35" s="19">
+        <v>0.114</v>
+      </c>
+      <c r="M35" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="N35" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="O35" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="P35" s="19">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="19">
+        <v>0.443</v>
+      </c>
+      <c r="S35" s="19">
+        <v>0.626</v>
+      </c>
+      <c r="T35" s="19">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="U35" s="19">
+        <v>1.18</v>
+      </c>
+      <c r="V35" s="19">
+        <v>1.56</v>
+      </c>
+      <c r="W35" s="19">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="X35" s="19">
+        <v>2.86</v>
+      </c>
+      <c r="Y35" s="19">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D36" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I36" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="J36" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="K36" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="L36" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="M36" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="N36" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="O36" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="P36" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="19">
+        <v>2.7E-2</v>
+      </c>
+      <c r="S36" s="19">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="T36" s="19">
+        <v>6.2E-2</v>
+      </c>
+      <c r="U36" s="19">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="V36" s="19">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="W36" s="19">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="X36" s="19">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="Y36" s="19">
+        <v>0.24199999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D37" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I37" s="19">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J37" s="19">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="K37" s="19">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="L37" s="19">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="M37" s="19">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="N37" s="19">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="O37" s="19">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="P37" s="19">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="19">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="S37" s="19">
+        <v>0.36</v>
+      </c>
+      <c r="T37" s="19">
+        <v>0.441</v>
+      </c>
+      <c r="U37" s="19">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="V37" s="19">
+        <v>0.67600000000000005</v>
+      </c>
+      <c r="W37" s="19">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="X37" s="19">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="Y37" s="19">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D38" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I38" s="19">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="J38" s="19">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="K38" s="19">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="L38" s="19">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="M38" s="19">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="N38" s="19">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="O38" s="19">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="P38" s="19">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="19">
+        <v>1.22</v>
+      </c>
+      <c r="S38" s="19">
+        <v>1.54</v>
+      </c>
+      <c r="T38" s="19">
+        <v>1.9</v>
+      </c>
+      <c r="U38" s="19">
+        <v>2.35</v>
+      </c>
+      <c r="V38" s="19">
+        <v>2.82</v>
+      </c>
+      <c r="W38" s="19">
+        <v>3.19</v>
+      </c>
+      <c r="X38" s="19">
+        <v>3.89</v>
+      </c>
+      <c r="Y38" s="19">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D39" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I39" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="J39" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="K39" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="L39" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="M39" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="N39" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="O39" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="P39" s="19">
+        <v>0.115</v>
+      </c>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="19">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="S39" s="19">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="T39" s="19">
+        <v>0.311</v>
+      </c>
+      <c r="U39" s="19">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="V39" s="19">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="W39" s="19">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="X39" s="19">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="Y39" s="19">
+        <v>0.36699999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D40" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I40" s="19">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="J40" s="19">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="K40" s="19">
+        <v>0.35</v>
+      </c>
+      <c r="L40" s="19">
+        <v>0.35</v>
+      </c>
+      <c r="M40" s="19">
+        <v>0.35</v>
+      </c>
+      <c r="N40" s="19">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="O40" s="19">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="P40" s="19">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="19">
+        <v>1.39</v>
+      </c>
+      <c r="S40" s="19">
+        <v>1.87</v>
+      </c>
+      <c r="T40" s="19">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="U40" s="19">
+        <v>3.25</v>
+      </c>
+      <c r="V40" s="19">
+        <v>4.08</v>
+      </c>
+      <c r="W40" s="19">
+        <v>5.16</v>
+      </c>
+      <c r="X40" s="19">
+        <v>5.96</v>
+      </c>
+      <c r="Y40" s="19">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D41" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I41" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="J41" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="K41" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="L41" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="M41" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="N41" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="O41" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="P41" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="19">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="S41" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="T41" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="U41" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="V41" s="19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="W41" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="X41" s="19">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="Y41" s="19">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D42" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I42" s="19">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="J42" s="19">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="K42" s="19">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="L42" s="19">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="M42" s="19">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="N42" s="19">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O42" s="19">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="P42" s="19">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="19">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="S42" s="19">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="T42" s="19">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="U42" s="19">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="V42" s="19">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="W42" s="19">
+        <v>1.05</v>
+      </c>
+      <c r="X42" s="19">
+        <v>1.43</v>
+      </c>
+      <c r="Y42" s="19">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D43" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I43" s="19">
+        <v>1.56</v>
+      </c>
+      <c r="J43" s="19">
+        <v>1.56</v>
+      </c>
+      <c r="K43" s="19">
+        <v>1.56</v>
+      </c>
+      <c r="L43" s="19">
+        <v>1.56</v>
+      </c>
+      <c r="M43" s="19">
+        <v>1.57</v>
+      </c>
+      <c r="N43" s="19">
+        <v>1.57</v>
+      </c>
+      <c r="O43" s="19">
+        <v>1.57</v>
+      </c>
+      <c r="P43" s="19">
+        <v>1.58</v>
+      </c>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="19">
+        <v>4.25</v>
+      </c>
+      <c r="S43" s="19">
+        <v>6.21</v>
+      </c>
+      <c r="T43" s="19">
+        <v>8.66</v>
+      </c>
+      <c r="U43" s="19">
+        <v>12.1</v>
+      </c>
+      <c r="V43" s="19">
+        <v>15.7</v>
+      </c>
+      <c r="W43" s="19">
+        <v>17.3</v>
+      </c>
+      <c r="X43" s="19">
+        <v>19.3</v>
+      </c>
+      <c r="Y43" s="19">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D44" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I44" s="19">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="J44" s="19">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="K44" s="19">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="L44" s="19">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="M44" s="19">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="N44" s="19">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="O44" s="19">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="P44" s="19">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="19">
+        <v>1.04</v>
+      </c>
+      <c r="S44" s="19">
+        <v>1.19</v>
+      </c>
+      <c r="T44" s="19">
+        <v>1.32</v>
+      </c>
+      <c r="U44" s="19">
+        <v>1.48</v>
+      </c>
+      <c r="V44" s="19">
+        <v>1.59</v>
+      </c>
+      <c r="W44" s="19">
+        <v>1.69</v>
+      </c>
+      <c r="X44" s="19">
+        <v>1.82</v>
+      </c>
+      <c r="Y44" s="19">
+        <v>2.0699999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D45" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I45" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="J45" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="K45" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="L45" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="M45" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="N45" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="O45" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="P45" s="19">
+        <v>0.154</v>
+      </c>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="19">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="S45" s="19">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="T45" s="19">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="U45" s="19">
+        <v>0.434</v>
+      </c>
+      <c r="V45" s="19">
+        <v>0.45</v>
+      </c>
+      <c r="W45" s="19">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="X45" s="19">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="Y45" s="19">
+        <v>0.49199999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D46" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I46" s="19">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="J46" s="19">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="K46" s="19">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="L46" s="19">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="M46" s="19">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="N46" s="19">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="O46" s="19">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="P46" s="19">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="19">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="S46" s="19">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="T46" s="19">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="U46" s="19">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="V46" s="19">
+        <v>1.26</v>
+      </c>
+      <c r="W46" s="19">
+        <v>1.58</v>
+      </c>
+      <c r="X46" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="Y46" s="19">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D47" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G47" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I47" s="19">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="J47" s="19">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="K47" s="19">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="L47" s="19">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="M47" s="19">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="N47" s="19">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="O47" s="19">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="P47" s="19">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="19">
+        <v>0.215</v>
+      </c>
+      <c r="S47" s="19">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="T47" s="19">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="U47" s="19">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="V47" s="19">
+        <v>0.495</v>
+      </c>
+      <c r="W47" s="19">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="X47" s="19">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="Y47" s="19">
+        <v>0.74399999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D48" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G48" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H48" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I48" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J48" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="K48" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="L48" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="M48" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="N48" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="O48" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="P48" s="19">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="19">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S48" s="19">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="T48" s="19">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="U48" s="19">
+        <v>7.8E-2</v>
+      </c>
+      <c r="V48" s="19">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="W48" s="19">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="X48" s="19">
+        <v>0.188</v>
+      </c>
+      <c r="Y48" s="19">
+        <v>0.23300000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="D49" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I49" s="19">
+        <v>0.124</v>
+      </c>
+      <c r="J49" s="19">
+        <v>0.124</v>
+      </c>
+      <c r="K49" s="19">
+        <v>0.124</v>
+      </c>
+      <c r="L49" s="19">
+        <v>0.125</v>
+      </c>
+      <c r="M49" s="19">
+        <v>0.125</v>
+      </c>
+      <c r="N49" s="19">
+        <v>0.125</v>
+      </c>
+      <c r="O49" s="19">
+        <v>0.125</v>
+      </c>
+      <c r="P49" s="19">
+        <v>0.126</v>
+      </c>
+      <c r="Q49" s="20"/>
+      <c r="R49" s="19">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="S49" s="19">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="T49" s="19">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="U49" s="19">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="V49" s="19">
+        <v>1.19</v>
+      </c>
+      <c r="W49" s="19">
+        <v>1.47</v>
+      </c>
+      <c r="X49" s="19">
+        <v>1.72</v>
+      </c>
+      <c r="Y49" s="19">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="50" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="D50" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I50" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="J50" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="K50" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="L50" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="M50" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="N50" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="O50" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="P50" s="19">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="19">
+        <v>1.6E-2</v>
+      </c>
+      <c r="S50" s="19">
+        <v>1.9E-2</v>
+      </c>
+      <c r="T50" s="19">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="U50" s="19">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="V50" s="19">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W50" s="19">
+        <v>3.1E-2</v>
+      </c>
+      <c r="X50" s="19">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="Y50" s="19">
+        <v>4.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="G53" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="H54" s="19">
+        <v>2024</v>
+      </c>
+      <c r="I54" s="19">
+        <v>2025</v>
+      </c>
+      <c r="J54" s="19">
+        <v>2026</v>
+      </c>
+      <c r="K54" s="19">
+        <v>2027</v>
+      </c>
+      <c r="L54" s="19">
+        <v>2028</v>
+      </c>
+      <c r="M54" s="19">
+        <v>2029</v>
+      </c>
+      <c r="N54" s="19">
+        <v>2030</v>
+      </c>
+      <c r="O54" s="19">
+        <v>2031</v>
+      </c>
+      <c r="P54" s="19">
+        <v>2032</v>
+      </c>
+      <c r="Q54" s="19">
+        <v>2033</v>
+      </c>
+      <c r="R54" s="19">
+        <v>2034</v>
+      </c>
+      <c r="S54" s="19">
+        <v>2035</v>
+      </c>
+      <c r="T54" s="19">
+        <v>2036</v>
+      </c>
+      <c r="U54" s="19">
+        <v>2037</v>
+      </c>
+      <c r="V54" s="19">
+        <v>2038</v>
+      </c>
+      <c r="W54" s="19">
+        <v>2039</v>
+      </c>
+      <c r="X54" s="19">
+        <v>2040</v>
+      </c>
+      <c r="Y54" s="19">
+        <v>2041</v>
+      </c>
+      <c r="Z54" s="19">
+        <v>2042</v>
+      </c>
+      <c r="AA54" s="19">
+        <v>2043</v>
+      </c>
+      <c r="AB54" s="19">
+        <v>2044</v>
+      </c>
+      <c r="AC54" s="19">
+        <v>2045</v>
+      </c>
+      <c r="AD54" s="19">
+        <v>2046</v>
+      </c>
+      <c r="AE54" s="19">
+        <v>2047</v>
+      </c>
+      <c r="AF54" s="19">
+        <v>2048</v>
+      </c>
+      <c r="AG54" s="19">
+        <v>2049</v>
+      </c>
+      <c r="AH54" s="19">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="55" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="G55" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="H55" s="19">
+        <f>SUM(I$3:I$50)</f>
+        <v>31.450000000000003</v>
+      </c>
+      <c r="I55" s="23">
+        <f>AVERAGE(H55,J55)</f>
+        <v>31.456500000000005</v>
+      </c>
+      <c r="J55" s="19">
+        <f>SUM(J$3:J$50)</f>
+        <v>31.463000000000005</v>
+      </c>
+      <c r="K55" s="23">
+        <f>AVERAGE(J55,L55)</f>
+        <v>31.465000000000003</v>
+      </c>
+      <c r="L55" s="19">
+        <f>SUM(K$3:K$50)</f>
+        <v>31.467000000000006</v>
+      </c>
+      <c r="M55" s="23">
+        <f>AVERAGE(L55,N55)</f>
+        <v>31.473500000000001</v>
+      </c>
+      <c r="N55" s="19">
+        <f>SUM(L$3:L$50)</f>
+        <v>31.48</v>
+      </c>
+      <c r="O55" s="23">
+        <f>AVERAGE(N55,P55)</f>
+        <v>31.491</v>
+      </c>
+      <c r="P55" s="19">
+        <f>SUM(M$3:M$50)</f>
+        <v>31.501999999999999</v>
+      </c>
+      <c r="Q55" s="23">
+        <f>(S55-P55)/2+P55</f>
+        <v>31.510999999999996</v>
+      </c>
+      <c r="R55" s="23">
+        <f>(S55-P55)/2+Q55</f>
+        <v>31.519999999999992</v>
+      </c>
+      <c r="S55" s="19">
+        <f>SUM(N$3:N$50)</f>
+        <v>31.519999999999992</v>
+      </c>
+      <c r="T55" s="23">
+        <f>($X55-$S55)/4+S55</f>
+        <v>31.523749999999996</v>
+      </c>
+      <c r="U55" s="23">
+        <f t="shared" ref="U55:W55" si="0">($X55-$S55)/4+T55</f>
+        <v>31.5275</v>
+      </c>
+      <c r="V55" s="23">
+        <f t="shared" si="0"/>
+        <v>31.531250000000004</v>
+      </c>
+      <c r="W55" s="23">
+        <f t="shared" si="0"/>
+        <v>31.535000000000007</v>
+      </c>
+      <c r="X55" s="19">
+        <f>SUM(O$3:O$50)</f>
+        <v>31.535000000000004</v>
+      </c>
+      <c r="Y55" s="23">
+        <f>($AH55-$X55)/9+X55</f>
+        <v>31.542111111111115</v>
+      </c>
+      <c r="Z55" s="23">
+        <f t="shared" ref="Z55:AG55" si="1">($AH55-$X55)/9+Y55</f>
+        <v>31.549222222222227</v>
+      </c>
+      <c r="AA55" s="23">
+        <f t="shared" si="1"/>
+        <v>31.556333333333338</v>
+      </c>
+      <c r="AB55" s="23">
+        <f t="shared" si="1"/>
+        <v>31.56344444444445</v>
+      </c>
+      <c r="AC55" s="23">
+        <f t="shared" si="1"/>
+        <v>31.570555555555561</v>
+      </c>
+      <c r="AD55" s="23">
+        <f t="shared" si="1"/>
+        <v>31.577666666666673</v>
+      </c>
+      <c r="AE55" s="23">
+        <f t="shared" si="1"/>
+        <v>31.584777777777784</v>
+      </c>
+      <c r="AF55" s="23">
+        <f t="shared" si="1"/>
+        <v>31.591888888888896</v>
+      </c>
+      <c r="AG55" s="23">
+        <f t="shared" si="1"/>
+        <v>31.599000000000007</v>
+      </c>
+      <c r="AH55" s="19">
+        <f>SUM(P$3:P$50)</f>
+        <v>31.599</v>
+      </c>
+    </row>
+    <row r="56" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="G56" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="H56" s="19">
+        <f>SUM(R$3:R$50)</f>
+        <v>76.67</v>
+      </c>
+      <c r="I56" s="23">
+        <f>AVERAGE(H56,J56)</f>
+        <v>84.141500000000008</v>
+      </c>
+      <c r="J56" s="19">
+        <f>SUM(S$3:S$50)</f>
+        <v>91.613</v>
+      </c>
+      <c r="K56" s="23">
+        <f>AVERAGE(J56,L56)</f>
+        <v>99.218000000000004</v>
+      </c>
+      <c r="L56" s="19">
+        <f>SUM(T$3:T$50)</f>
+        <v>106.82300000000001</v>
+      </c>
+      <c r="M56" s="23">
+        <f>AVERAGE(L56,N56)</f>
+        <v>116.72550000000001</v>
+      </c>
+      <c r="N56" s="19">
+        <f>SUM(U$3:U$50)</f>
+        <v>126.62800000000003</v>
+      </c>
+      <c r="O56" s="23">
+        <f>AVERAGE(N56,P56)</f>
+        <v>136.27100000000002</v>
+      </c>
+      <c r="P56" s="19">
+        <f>SUM(V$3:V$50)</f>
+        <v>145.91399999999999</v>
+      </c>
+      <c r="Q56" s="23">
+        <f>(S56-P56)/3+P56</f>
+        <v>150.65266666666668</v>
+      </c>
+      <c r="R56" s="23">
+        <f>(S56-P56)/3+Q56</f>
+        <v>155.39133333333336</v>
+      </c>
+      <c r="S56" s="19">
+        <f>SUM(W$3:W$50)</f>
+        <v>160.13000000000002</v>
+      </c>
+      <c r="T56" s="23">
+        <f>($X56-$S56)/5+S56</f>
+        <v>163.78880000000001</v>
+      </c>
+      <c r="U56" s="23">
+        <f t="shared" ref="U56:V56" si="2">($X56-$S56)/5+T56</f>
+        <v>167.44759999999999</v>
+      </c>
+      <c r="V56" s="23">
+        <f t="shared" si="2"/>
+        <v>171.10639999999998</v>
+      </c>
+      <c r="W56" s="23">
+        <f>($X56-$S56)/5+V56</f>
+        <v>174.76519999999996</v>
+      </c>
+      <c r="X56" s="19">
+        <f>SUM(X$3:X$50)</f>
+        <v>178.42399999999995</v>
+      </c>
+      <c r="Y56" s="23">
+        <f>($AH56-$X56)/10+X56</f>
+        <v>181.37509999999995</v>
+      </c>
+      <c r="Z56" s="23">
+        <f t="shared" ref="Z56:AG56" si="3">($AH56-$X56)/10+Y56</f>
+        <v>184.32619999999994</v>
+      </c>
+      <c r="AA56" s="23">
+        <f t="shared" si="3"/>
+        <v>187.27729999999994</v>
+      </c>
+      <c r="AB56" s="23">
+        <f t="shared" si="3"/>
+        <v>190.22839999999994</v>
+      </c>
+      <c r="AC56" s="23">
+        <f t="shared" si="3"/>
+        <v>193.17949999999993</v>
+      </c>
+      <c r="AD56" s="23">
+        <f t="shared" si="3"/>
+        <v>196.13059999999993</v>
+      </c>
+      <c r="AE56" s="23">
+        <f t="shared" si="3"/>
+        <v>199.08169999999993</v>
+      </c>
+      <c r="AF56" s="23">
+        <f t="shared" si="3"/>
+        <v>202.03279999999992</v>
+      </c>
+      <c r="AG56" s="23">
+        <f t="shared" si="3"/>
+        <v>204.98389999999992</v>
+      </c>
+      <c r="AH56" s="19">
+        <f>SUM(Y$3:Y$50)</f>
+        <v>207.93499999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="G58" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H58" s="24"/>
+      <c r="I58" s="25">
+        <f>I55-H55</f>
+        <v>6.5000000000026148E-3</v>
+      </c>
+      <c r="J58" s="25">
+        <f t="shared" ref="J58:AH59" si="4">J55-I55</f>
+        <v>6.4999999999990621E-3</v>
+      </c>
+      <c r="K58" s="25">
+        <f t="shared" si="4"/>
+        <v>1.9999999999988916E-3</v>
+      </c>
+      <c r="L58" s="25">
+        <f t="shared" si="4"/>
+        <v>2.0000000000024443E-3</v>
+      </c>
+      <c r="M58" s="25">
+        <f t="shared" si="4"/>
+        <v>6.4999999999955094E-3</v>
+      </c>
+      <c r="N58" s="25">
+        <f t="shared" si="4"/>
+        <v>6.4999999999990621E-3</v>
+      </c>
+      <c r="O58" s="25">
+        <f t="shared" si="4"/>
+        <v>1.0999999999999233E-2</v>
+      </c>
+      <c r="P58" s="25">
+        <f t="shared" si="4"/>
+        <v>1.0999999999999233E-2</v>
+      </c>
+      <c r="Q58" s="25">
+        <f t="shared" si="4"/>
+        <v>8.9999999999967883E-3</v>
+      </c>
+      <c r="R58" s="25">
+        <f t="shared" si="4"/>
+        <v>8.9999999999967883E-3</v>
+      </c>
+      <c r="S58" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="25">
+        <f t="shared" si="4"/>
+        <v>3.7500000000036948E-3</v>
+      </c>
+      <c r="U58" s="25">
+        <f t="shared" si="4"/>
+        <v>3.7500000000036948E-3</v>
+      </c>
+      <c r="V58" s="25">
+        <f t="shared" si="4"/>
+        <v>3.7500000000036948E-3</v>
+      </c>
+      <c r="W58" s="25">
+        <f t="shared" si="4"/>
+        <v>3.7500000000036948E-3</v>
+      </c>
+      <c r="X58" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="Z58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="AA58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="AB58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="AC58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="AD58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="AE58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="AF58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="AG58" s="25">
+        <f t="shared" si="4"/>
+        <v>7.1111111111115122E-3</v>
+      </c>
+      <c r="AH58" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="G59" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I59" s="19">
+        <f>I56-H56</f>
+        <v>7.471500000000006</v>
+      </c>
+      <c r="J59" s="19">
+        <f t="shared" si="4"/>
+        <v>7.4714999999999918</v>
+      </c>
+      <c r="K59" s="19">
+        <f t="shared" si="4"/>
+        <v>7.605000000000004</v>
+      </c>
+      <c r="L59" s="19">
+        <f t="shared" si="4"/>
+        <v>7.605000000000004</v>
+      </c>
+      <c r="M59" s="19">
+        <f t="shared" si="4"/>
+        <v>9.9025000000000034</v>
+      </c>
+      <c r="N59" s="19">
+        <f t="shared" si="4"/>
+        <v>9.9025000000000176</v>
+      </c>
+      <c r="O59" s="19">
+        <f t="shared" si="4"/>
+        <v>9.6429999999999865</v>
+      </c>
+      <c r="P59" s="19">
+        <f t="shared" si="4"/>
+        <v>9.6429999999999723</v>
+      </c>
+      <c r="Q59" s="19">
+        <f t="shared" si="4"/>
+        <v>4.7386666666666883</v>
+      </c>
+      <c r="R59" s="19">
+        <f t="shared" si="4"/>
+        <v>4.7386666666666883</v>
+      </c>
+      <c r="S59" s="19">
+        <f t="shared" si="4"/>
+        <v>4.7386666666666599</v>
+      </c>
+      <c r="T59" s="19">
+        <f t="shared" si="4"/>
+        <v>3.6587999999999852</v>
+      </c>
+      <c r="U59" s="19">
+        <f t="shared" si="4"/>
+        <v>3.6587999999999852</v>
+      </c>
+      <c r="V59" s="19">
+        <f t="shared" si="4"/>
+        <v>3.6587999999999852</v>
+      </c>
+      <c r="W59" s="19">
+        <f t="shared" si="4"/>
+        <v>3.6587999999999852</v>
+      </c>
+      <c r="X59" s="19">
+        <f t="shared" si="4"/>
+        <v>3.6587999999999852</v>
+      </c>
+      <c r="Y59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="Z59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="AA59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="AB59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="AC59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="AD59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="AE59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="AF59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="AG59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9510999999999967</v>
+      </c>
+      <c r="AH59" s="19">
+        <f t="shared" si="4"/>
+        <v>2.9511000000000536</v>
+      </c>
+    </row>
+    <row r="60" spans="4:34" x14ac:dyDescent="0.35">
+      <c r="G60" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I60" s="19">
+        <f>I59-I58</f>
+        <v>7.4650000000000034</v>
+      </c>
+      <c r="J60" s="19">
+        <f t="shared" ref="J60:AH60" si="5">J59-J58</f>
+        <v>7.4649999999999928</v>
+      </c>
+      <c r="K60" s="19">
+        <f t="shared" si="5"/>
+        <v>7.6030000000000051</v>
+      </c>
+      <c r="L60" s="19">
+        <f t="shared" si="5"/>
+        <v>7.6030000000000015</v>
+      </c>
+      <c r="M60" s="19">
+        <f t="shared" si="5"/>
+        <v>9.8960000000000079</v>
+      </c>
+      <c r="N60" s="19">
+        <f t="shared" si="5"/>
+        <v>9.8960000000000186</v>
+      </c>
+      <c r="O60" s="19">
+        <f t="shared" si="5"/>
+        <v>9.6319999999999872</v>
+      </c>
+      <c r="P60" s="19">
+        <f t="shared" si="5"/>
+        <v>9.631999999999973</v>
+      </c>
+      <c r="Q60" s="19">
+        <f t="shared" si="5"/>
+        <v>4.7296666666666916</v>
+      </c>
+      <c r="R60" s="19">
+        <f t="shared" si="5"/>
+        <v>4.7296666666666916</v>
+      </c>
+      <c r="S60" s="19">
+        <f t="shared" si="5"/>
+        <v>4.7386666666666599</v>
+      </c>
+      <c r="T60" s="19">
+        <f t="shared" si="5"/>
+        <v>3.6550499999999815</v>
+      </c>
+      <c r="U60" s="19">
+        <f t="shared" si="5"/>
+        <v>3.6550499999999815</v>
+      </c>
+      <c r="V60" s="19">
+        <f t="shared" si="5"/>
+        <v>3.6550499999999815</v>
+      </c>
+      <c r="W60" s="19">
+        <f t="shared" si="5"/>
+        <v>3.6550499999999815</v>
+      </c>
+      <c r="X60" s="19">
+        <f t="shared" si="5"/>
+        <v>3.6587999999999852</v>
+      </c>
+      <c r="Y60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="Z60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="AA60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="AB60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="AC60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="AD60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="AE60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="AF60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="AG60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9439888888888852</v>
+      </c>
+      <c r="AH60" s="19">
+        <f t="shared" si="5"/>
+        <v>2.9511000000000536</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -1816,67 +6731,88 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!N60*About!$B$34*About!$A$30</f>
+        <v>7928.5211505922307</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!O60*About!$B$34*About!$A$30</f>
+        <v>7717.0084602368761</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!P60*About!$B$34*About!$A$30</f>
+        <v>7717.0084602368643</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!Q60*About!$B$34*About!$A$30</f>
+        <v>3789.3353073886269</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!R60*About!$B$34*About!$A$30</f>
+        <v>3789.3353073886269</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!S60*About!$B$34*About!$A$30</f>
+        <v>3796.5459672870784</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!T60*About!$B$34*About!$A$30</f>
+        <v>2928.3691624365333</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!U60*About!$B$34*About!$A$30</f>
+        <v>2928.3691624365333</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!V60*About!$B$34*About!$A$30</f>
+        <v>2928.3691624365333</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!W60*About!$B$34*About!$A$30</f>
+        <v>2928.3691624365333</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!X60*About!$B$34*About!$A$30</f>
+        <v>2931.3736040609019</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!Y60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!Z60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AA60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AB60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AC60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AD60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AE60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AF60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AG60*About!$B$34*About!$A$30</f>
+        <v>2358.6780691859344</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AH60*About!$B$34*About!$A$30</f>
+        <v>2364.3753807107028</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.35">
@@ -2740,7 +7676,7 @@
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B19">
@@ -2826,7 +7762,7 @@
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B20">
@@ -2912,7 +7848,7 @@
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B21">
@@ -2998,7 +7934,7 @@
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B22">
@@ -3084,7 +8020,7 @@
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B23">
@@ -3170,7 +8106,7 @@
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B24">
@@ -3256,7 +8192,7 @@
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B25">
@@ -3346,7 +8282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -3983,67 +8919,88 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!N60*About!$B$34*About!$A$31</f>
+        <v>1967.478849407787</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!O60*About!$B$34*About!$A$31</f>
+        <v>1914.9915397631107</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!P60*About!$B$34*About!$A$31</f>
+        <v>1914.991539763108</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!Q60*About!$B$34*About!$A$31</f>
+        <v>940.33135927806472</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!R60*About!$B$34*About!$A$31</f>
+        <v>940.33135927806472</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!S60*About!$B$34*About!$A$31</f>
+        <v>942.1206993795812</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!T60*About!$B$34*About!$A$31</f>
+        <v>726.68083756344811</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!U60*About!$B$34*About!$A$31</f>
+        <v>726.68083756344811</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!V60*About!$B$34*About!$A$31</f>
+        <v>726.68083756344811</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!W60*About!$B$34*About!$A$31</f>
+        <v>726.68083756344811</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!X60*About!$B$34*About!$A$31</f>
+        <v>727.42639593908336</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!Y60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!Z60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AA60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AB60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AC60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AD60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AE60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AF60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AG60*About!$B$34*About!$A$31</f>
+        <v>585.31081970295099</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <f>'REPEAT dist solar data'!AH60*About!$B$34*About!$A$31</f>
+        <v>586.7246192893507</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.35">
@@ -4907,7 +9864,7 @@
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B19">
@@ -4993,7 +9950,7 @@
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B20">
@@ -5079,7 +10036,7 @@
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B21">
@@ -5165,7 +10122,7 @@
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B22">
@@ -5251,7 +10208,7 @@
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B23">
@@ -5337,7 +10294,7 @@
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B24">
@@ -5423,7 +10380,7 @@
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B25">
@@ -5513,7 +10470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -7074,7 +12031,7 @@
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B19">
@@ -7160,7 +12117,7 @@
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B20">
@@ -7246,7 +12203,7 @@
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B21">
@@ -7332,7 +12289,7 @@
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B22">
@@ -7418,7 +12375,7 @@
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B23">
@@ -7504,7 +12461,7 @@
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B24">
@@ -7590,7 +12547,7 @@
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B25">
